--- a/native-auto-test/docs/test-case-report/现有Case说明.xlsx
+++ b/native-auto-test/docs/test-case-report/现有Case说明.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概览" sheetId="1" r:id="R09d54be9eee942bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case总览" sheetId="2" r:id="R4e270e4a9f444cad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="状态说明" sheetId="3" r:id="Rc7aa73ece5a54882"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概览" sheetId="1" r:id="R53c7e75f4ab64c84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case总览" sheetId="2" r:id="R61ec13b0d5dd4045"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="状态说明" sheetId="3" r:id="R14609c01a33a4113"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -189,8 +189,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CaseOverviewTable" displayName="CaseOverviewTable" ref="A2:F805" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A2:F805"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CaseOverviewTable" displayName="CaseOverviewTable" ref="A2:F801" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A2:F801"/>
   <x:tableColumns count="6">
     <x:tableColumn id="1" name="模块"/>
     <x:tableColumn id="2" name="类型"/>
@@ -433,14 +433,14 @@
         <x:v>Case 总数</x:v>
       </x:c>
       <x:c r="B4" s="28" t="n">
-        <x:f>COUNTA('Case总览'!$C$3:$C$805)</x:f>
-        <x:v>803</x:v>
+        <x:f>COUNTA('Case总览'!$C$3:$C$801)</x:f>
+        <x:v>799</x:v>
       </x:c>
       <x:c r="D4" s="28" t="str">
         <x:v>Chat</x:v>
       </x:c>
       <x:c r="E4" s="28" t="n">
-        <x:f>COUNTIF('Case总览'!$A$3:$A$805,D4)</x:f>
+        <x:f>COUNTIF('Case总览'!$A$3:$A$801,D4)</x:f>
         <x:v>261</x:v>
       </x:c>
     </x:row>
@@ -449,14 +449,14 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="B5" s="28" t="n">
-        <x:f>COUNTIF('Case总览'!$G$3:$G$805,"普通")</x:f>
-        <x:v>769</x:v>
+        <x:f>COUNTIF('Case总览'!$G$3:$G$801,"普通")</x:f>
+        <x:v>765</x:v>
       </x:c>
       <x:c r="D5" s="28" t="str">
         <x:v>ChatRoom</x:v>
       </x:c>
       <x:c r="E5" s="28" t="n">
-        <x:f>COUNTIF('Case总览'!$A$3:$A$805,D5)</x:f>
+        <x:f>COUNTIF('Case总览'!$A$3:$A$801,D5)</x:f>
         <x:v>144</x:v>
       </x:c>
     </x:row>
@@ -465,14 +465,14 @@
         <x:v>5.0 不可用</x:v>
       </x:c>
       <x:c r="B6" s="28" t="n">
-        <x:f>COUNTIF('Case总览'!$G$3:$G$805,"5.0 不可用")</x:f>
+        <x:f>COUNTIF('Case总览'!$G$3:$G$801,"5.0 不可用")</x:f>
         <x:v>34</x:v>
       </x:c>
       <x:c r="D6" s="28" t="str">
         <x:v>Client</x:v>
       </x:c>
       <x:c r="E6" s="28" t="n">
-        <x:f>COUNTIF('Case总览'!$A$3:$A$805,D6)</x:f>
+        <x:f>COUNTIF('Case总览'!$A$3:$A$801,D6)</x:f>
         <x:v>27</x:v>
       </x:c>
     </x:row>
@@ -481,7 +481,7 @@
         <x:v>Contact</x:v>
       </x:c>
       <x:c r="E7" s="28" t="n">
-        <x:f>COUNTIF('Case总览'!$A$3:$A$805,D7)</x:f>
+        <x:f>COUNTIF('Case总览'!$A$3:$A$801,D7)</x:f>
         <x:v>37</x:v>
       </x:c>
     </x:row>
@@ -490,43 +490,34 @@
         <x:v>Group</x:v>
       </x:c>
       <x:c r="E8" s="28" t="n">
-        <x:f>COUNTIF('Case总览'!$A$3:$A$805,D8)</x:f>
-        <x:v>298</x:v>
+        <x:f>COUNTIF('Case总览'!$A$3:$A$801,D8)</x:f>
+        <x:v>299</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="D9" s="28" t="str">
-        <x:v>Phase1</x:v>
+        <x:v>Presence</x:v>
       </x:c>
       <x:c r="E9" s="28" t="n">
-        <x:f>COUNTIF('Case总览'!$A$3:$A$805,D9)</x:f>
-        <x:v>5</x:v>
+        <x:f>COUNTIF('Case总览'!$A$3:$A$801,D9)</x:f>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="D10" s="28" t="str">
-        <x:v>Presence</x:v>
+        <x:v>Push</x:v>
       </x:c>
       <x:c r="E10" s="28" t="n">
-        <x:f>COUNTIF('Case总览'!$A$3:$A$805,D10)</x:f>
-        <x:v>10</x:v>
+        <x:f>COUNTIF('Case总览'!$A$3:$A$801,D10)</x:f>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="D11" s="28" t="str">
-        <x:v>Push</x:v>
+        <x:v>UserInfo</x:v>
       </x:c>
       <x:c r="E11" s="28" t="n">
-        <x:f>COUNTIF('Case总览'!$A$3:$A$805,D11)</x:f>
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="D12" s="28" t="str">
-        <x:v>UserInfo</x:v>
-      </x:c>
-      <x:c r="E12" s="28" t="n">
-        <x:f>COUNTIF('Case总览'!$A$3:$A$805,D12)</x:f>
+        <x:f>COUNTIF('Case总览'!$A$3:$A$801,D11)</x:f>
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -7464,7 +7455,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C279" s="18" t="str">
-        <x:v>白名单/禁言自查接口：roomId 为空时，按方法分别冻结 700/Chat room ID is 无效（参数：isMemberInChatRoomMuteList）</x:v>
+        <x:v>白名单/禁言自查接口：roomId 为空时返回 700；description 由平台 SDK 决定（参数：isMemberInChatRoomMuteList）</x:v>
       </x:c>
       <x:c r="D279" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -7488,7 +7479,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C280" s="18" t="str">
-        <x:v>白名单/禁言自查接口：roomId 为空时，按方法分别冻结 700/Chat room ID is 无效（参数：isMemberInChatRoomWhiteListFromServer）</x:v>
+        <x:v>白名单/禁言自查接口：roomId 为空时返回 700；description 由平台 SDK 决定（参数：isMemberInChatRoomWhiteListFromServer）</x:v>
       </x:c>
       <x:c r="D280" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -9263,7 +9254,7 @@
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备B已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E353" s="18" t="str">
-        <x:v>1. 使用空聊天室 ID 离开并验证幂等成功语义
+        <x:v>1. 使用空聊天室 ID 离开并验证参数错误码
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
       <x:c r="F353" s="24" t="str">
@@ -12493,15 +12484,41 @@
         <x:v>Group</x:v>
       </x:c>
       <x:c r="B482" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C482" s="18" t="str">
+        <x:v>B 对真实群消息发送已读回执后，A 的群已读数量变为 1</x:v>
+      </x:c>
+      <x:c r="D482" s="18" t="str">
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+      </x:c>
+      <x:c r="E482" s="18" t="str">
+        <x:v>1. A 发送一条需要群已读回执的文本消息。
+2. B 接收该群消息并发送已读回执。
+3. A 查询该消息的群已读数量，确认数量变为 1。
+验证操作结果、关键字段和相关事件符合预期。</x:v>
+      </x:c>
+      <x:c r="F482" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G482" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="483" ht="120" customHeight="1">
+      <x:c r="A483" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B483" s="21" t="str">
         <x:v>多设备</x:v>
       </x:c>
-      <x:c r="C482" s="18" t="str">
+      <x:c r="C483" s="18" t="str">
         <x:v>管理员 B 上传/删除共享文件：新增/删除事件同步到 owner 账号（A）全部在线端；B 全端收管理员提升事件</x:v>
       </x:c>
-      <x:c r="D482" s="18" t="str">
+      <x:c r="D483" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E482" s="18" t="str">
+      <x:c r="E483" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 添加群管理员
 3. 验证 添加群管理员返回的关键字段
@@ -12511,27 +12528,27 @@
 验证在线设备集合中的目标设备是否均收到一致结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F482" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G482" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="483" ht="120" customHeight="1">
-      <x:c r="A483" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B483" s="21" t="str">
+      <x:c r="F483" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G483" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="484" ht="120" customHeight="1">
+      <x:c r="A484" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B484" s="21" t="str">
         <x:v>多设备</x:v>
       </x:c>
-      <x:c r="C483" s="18" t="str">
+      <x:c r="C484" s="18" t="str">
         <x:v>管理员仍可由群主移除：移除事件同步到接收账号全部在线端</x:v>
       </x:c>
-      <x:c r="D483" s="18" t="str">
+      <x:c r="D484" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E483" s="18" t="str">
+      <x:c r="E484" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 添加群管理员
 3. 验证 添加群管理员返回的关键字段
@@ -12543,27 +12560,27 @@
 验证在线设备集合中的目标设备是否均收到一致结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F483" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G483" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="484" ht="120" customHeight="1">
-      <x:c r="A484" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B484" s="21" t="str">
+      <x:c r="F484" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G484" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="485" ht="120" customHeight="1">
+      <x:c r="A485" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B485" s="21" t="str">
         <x:v>多设备</x:v>
       </x:c>
-      <x:c r="C484" s="18" t="str">
+      <x:c r="C485" s="18" t="str">
         <x:v>批量移除忽略 owner/非成员、移除有效成员：移除事件同步到接收账号全部在线端</x:v>
       </x:c>
-      <x:c r="D484" s="18" t="str">
+      <x:c r="D485" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E484" s="18" t="str">
+      <x:c r="E485" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 移除群成员
 3. 验证群业务状态、事件与关键字段
@@ -12573,36 +12590,6 @@
 验证在线设备集合中的目标设备是否均收到一致结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F484" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G484" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="485" ht="120" customHeight="1">
-      <x:c r="A485" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B485" s="21" t="str">
-        <x:v>多设备</x:v>
-      </x:c>
-      <x:c r="C485" s="18" t="str">
-        <x:v>普通成员和管理员都不能调用 owner-only 的 updateGroupOwner（参数：成员）</x:v>
-      </x:c>
-      <x:c r="D485" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
-      </x:c>
-      <x:c r="E485" s="18" t="str">
-        <x:v>1. 测试准备：创建测试群并建立业务前置
-2. A 添加群管理员
-3. 验证 添加群管理员返回的关键字段
-4. B 转让群主
-5. 验证转让群主返回的错误码与错误文案
-6. 测试后置：销毁测试群并恢复群状态
-验证在线设备集合中的目标设备是否均收到一致结果。
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
       <x:c r="F485" s="24" t="str">
         <x:v>普通</x:v>
       </x:c>
@@ -12618,7 +12605,7 @@
         <x:v>多设备</x:v>
       </x:c>
       <x:c r="C486" s="18" t="str">
-        <x:v>普通成员和管理员都不能调用 owner-only 的 updateGroupOwner（参数：admin）</x:v>
+        <x:v>普通成员和管理员都不能调用 owner-only 的 updateGroupOwner（参数：成员）</x:v>
       </x:c>
       <x:c r="D486" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -12648,7 +12635,7 @@
         <x:v>多设备</x:v>
       </x:c>
       <x:c r="C487" s="18" t="str">
-        <x:v>普通成员无权移除其他成员；管理员移除普通成员：退出事件同步到 owner 与操作管理员账号全部在线端（参数：成员）</x:v>
+        <x:v>普通成员和管理员都不能调用 owner-only 的 updateGroupOwner（参数：admin）</x:v>
       </x:c>
       <x:c r="D487" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -12657,11 +12644,9 @@
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 添加群管理员
 3. 验证 添加群管理员返回的关键字段
-4. B 移除群成员
-5. 验证群业务状态、事件与关键字段
-6. owner 账号全部在线端收到成员退出事件
-7. 操作管理员账号全部在线端收到成员退出事件
-8. 验证 移除群成员返回的错误码与错误文案
+4. B 转让群主
+5. 验证转让群主返回的错误码与错误文案
+6. 测试后置：销毁测试群并恢复群状态
 验证在线设备集合中的目标设备是否均收到一致结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
@@ -12680,7 +12665,7 @@
         <x:v>多设备</x:v>
       </x:c>
       <x:c r="C488" s="18" t="str">
-        <x:v>普通成员无权移除其他成员；管理员移除普通成员：退出事件同步到 owner 与操作管理员账号全部在线端（参数：admin）</x:v>
+        <x:v>普通成员无权移除其他成员；管理员移除普通成员：退出事件同步到 owner 与操作管理员账号全部在线端（参数：成员）</x:v>
       </x:c>
       <x:c r="D488" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -12712,12 +12697,44 @@
         <x:v>多设备</x:v>
       </x:c>
       <x:c r="C489" s="18" t="str">
-        <x:v>前置：A 为群主，B 已入群且双方建群事件已消费</x:v>
+        <x:v>普通成员无权移除其他成员；管理员移除普通成员：退出事件同步到 owner 与操作管理员账号全部在线端（参数：admin）</x:v>
       </x:c>
       <x:c r="D489" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E489" s="18" t="str">
+        <x:v>1. 测试准备：创建测试群并建立业务前置
+2. A 添加群管理员
+3. 验证 添加群管理员返回的关键字段
+4. B 移除群成员
+5. 验证群业务状态、事件与关键字段
+6. owner 账号全部在线端收到成员退出事件
+7. 操作管理员账号全部在线端收到成员退出事件
+8. 验证 移除群成员返回的错误码与错误文案
+验证在线设备集合中的目标设备是否均收到一致结果。
+验证操作结果、关键字段和相关事件符合预期。</x:v>
+      </x:c>
+      <x:c r="F489" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G489" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="490" ht="120" customHeight="1">
+      <x:c r="A490" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B490" s="21" t="str">
+        <x:v>多设备</x:v>
+      </x:c>
+      <x:c r="C490" s="18" t="str">
+        <x:v>前置：A 为群主，B 已入群且双方建群事件已消费</x:v>
+      </x:c>
+      <x:c r="D490" s="18" t="str">
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+      </x:c>
+      <x:c r="E490" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. 所有拓扑端点消费建群和入群事件
 3. 更新群公告
@@ -12729,27 +12746,27 @@
 验证在线设备集合中的目标设备是否均收到一致结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F489" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G489" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="490" ht="120" customHeight="1">
-      <x:c r="A490" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B490" s="21" t="str">
+      <x:c r="F490" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G490" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="491" ht="120" customHeight="1">
+      <x:c r="A491" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B491" s="21" t="str">
         <x:v>多设备</x:v>
       </x:c>
-      <x:c r="C490" s="18" t="str">
+      <x:c r="C491" s="18" t="str">
         <x:v>前置：A 为群主、B 已入群；A 将 B 设置为管理员并消费管理员变更事件</x:v>
       </x:c>
-      <x:c r="D490" s="18" t="str">
+      <x:c r="D491" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E490" s="18" t="str">
+      <x:c r="E491" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. 所有拓扑端点消费建群和入群事件
 3. 添加群管理员
@@ -12761,27 +12778,27 @@
 验证在线设备集合中的目标设备是否均收到一致结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F490" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G490" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="491" ht="120" customHeight="1">
-      <x:c r="A491" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B491" s="21" t="str">
+      <x:c r="F491" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G491" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="492" ht="120" customHeight="1">
+      <x:c r="A492" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B492" s="21" t="str">
         <x:v>多设备</x:v>
       </x:c>
-      <x:c r="C491" s="18" t="str">
+      <x:c r="C492" s="18" t="str">
         <x:v>前置：A/B 已登录；B 的 autoAcceptGroupInvitation 显式设置为 true</x:v>
       </x:c>
-      <x:c r="D491" s="18" t="str">
+      <x:c r="D492" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E491" s="18" t="str">
+      <x:c r="E492" s="18" t="str">
         <x:v>1. B 开启自动接受群邀请
 2. 验证自动接受群邀请设置已更新
 3. 测试准备：创建测试群并建立业务前置
@@ -12793,27 +12810,27 @@
 验证在线设备集合中的目标设备是否均收到一致结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F491" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G491" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="492" ht="120" customHeight="1">
-      <x:c r="A492" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B492" s="21" t="str">
+      <x:c r="F492" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G492" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="493" ht="120" customHeight="1">
+      <x:c r="A493" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B493" s="21" t="str">
         <x:v>多设备</x:v>
       </x:c>
-      <x:c r="C492" s="18" t="str">
+      <x:c r="C493" s="18" t="str">
         <x:v>前置：A/B 已登录；B 的自动接受邀请基线为 true</x:v>
       </x:c>
-      <x:c r="D492" s="18" t="str">
+      <x:c r="D493" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E492" s="18" t="str">
+      <x:c r="E493" s="18" t="str">
         <x:v>1. B 关闭自动接受群邀请
 2. 验证自动接受群邀请设置已更新
 3. 测试准备：创建测试群并建立业务前置
@@ -12825,27 +12842,27 @@
 验证在线设备集合中的目标设备是否均收到一致结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F492" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G492" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="493" ht="120" customHeight="1">
-      <x:c r="A493" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B493" s="21" t="str">
+      <x:c r="F493" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G493" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="494" ht="120" customHeight="1">
+      <x:c r="A494" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B494" s="21" t="str">
         <x:v>多设备</x:v>
       </x:c>
-      <x:c r="C493" s="18" t="str">
+      <x:c r="C494" s="18" t="str">
         <x:v>前置：A/B 已登录；B 的自动接受邀请基线为 true</x:v>
       </x:c>
-      <x:c r="D493" s="18" t="str">
+      <x:c r="D494" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E493" s="18" t="str">
+      <x:c r="E494" s="18" t="str">
         <x:v>1. B 关闭自动接受群邀请
 2. 验证自动接受群邀请设置已更新
 3. 测试准备：创建测试群并建立业务前置
@@ -12857,53 +12874,53 @@
 验证在线设备集合中的目标设备是否均收到一致结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F493" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G493" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="494" ht="120" customHeight="1">
-      <x:c r="A494" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B494" s="21" t="str">
+      <x:c r="F494" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G494" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="495" ht="120" customHeight="1">
+      <x:c r="A495" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B495" s="21" t="str">
         <x:v>多设备</x:v>
       </x:c>
-      <x:c r="C494" s="18" t="str">
+      <x:c r="C495" s="18" t="str">
         <x:v>前置：B 为群主、A 已入群；B 所在测试 App 已将默认素材准备为 Android 本地文件</x:v>
       </x:c>
-      <x:c r="D494" s="18" t="str">
+      <x:c r="D495" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E494" s="18" t="str">
+      <x:c r="E495" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. 测试后置：销毁测试群并恢复群状态
 验证在线设备集合中的目标设备是否均收到一致结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F494" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G494" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="495" ht="120" customHeight="1">
-      <x:c r="A495" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B495" s="21" t="str">
+      <x:c r="F495" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G495" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="496" ht="120" customHeight="1">
+      <x:c r="A496" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B496" s="21" t="str">
         <x:v>多设备</x:v>
       </x:c>
-      <x:c r="C495" s="18" t="str">
+      <x:c r="C496" s="18" t="str">
         <x:v>群主封禁/解封成员：移除事件同步到接收账号全部在线端</x:v>
       </x:c>
-      <x:c r="D495" s="18" t="str">
+      <x:c r="D496" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E495" s="18" t="str">
+      <x:c r="E496" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 加入群黑名单
 3. 验证加入群黑名单返回的关键字段
@@ -12914,27 +12931,27 @@
 验证在线设备集合中的目标设备是否均收到一致结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F495" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G495" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="496" ht="120" customHeight="1">
-      <x:c r="A496" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B496" s="21" t="str">
+      <x:c r="F496" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G496" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="497" ht="120" customHeight="1">
+      <x:c r="A497" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B497" s="21" t="str">
         <x:v>多设备</x:v>
       </x:c>
-      <x:c r="C496" s="18" t="str">
+      <x:c r="C497" s="18" t="str">
         <x:v>群主更新群描述：变更事件同步到群成员全部在线端</x:v>
       </x:c>
-      <x:c r="D496" s="18" t="str">
+      <x:c r="D497" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E496" s="18" t="str">
+      <x:c r="E497" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 执行群组业务操作
 3. 验证执行群组业务操作返回的响应 result 与关键字段
@@ -12946,27 +12963,27 @@
 验证在线设备集合中的目标设备是否均收到一致结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F496" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G496" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="497" ht="120" customHeight="1">
-      <x:c r="A497" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B497" s="21" t="str">
+      <x:c r="F497" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G497" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="498" ht="120" customHeight="1">
+      <x:c r="A498" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B498" s="21" t="str">
         <x:v>多设备</x:v>
       </x:c>
-      <x:c r="C497" s="18" t="str">
+      <x:c r="C498" s="18" t="str">
         <x:v>群主更新群名称：变更事件同步到群成员全部在线端</x:v>
       </x:c>
-      <x:c r="D497" s="18" t="str">
+      <x:c r="D498" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E497" s="18" t="str">
+      <x:c r="E498" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 更新群名称
 3. 验证更新群名称返回的关键字段
@@ -12978,27 +12995,27 @@
 验证在线设备集合中的目标设备是否均收到一致结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F497" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G497" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="498" ht="120" customHeight="1">
-      <x:c r="A498" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B498" s="21" t="str">
+      <x:c r="F498" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G498" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="499" ht="120" customHeight="1">
+      <x:c r="A499" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B499" s="21" t="str">
         <x:v>多设备</x:v>
       </x:c>
-      <x:c r="C498" s="18" t="str">
+      <x:c r="C499" s="18" t="str">
         <x:v>群主禁言/解禁成员：禁言列表变更事件同步到接收账号全部在线端</x:v>
       </x:c>
-      <x:c r="D498" s="18" t="str">
+      <x:c r="D499" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E498" s="18" t="str">
+      <x:c r="E499" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 禁言成员
 3. 验证 禁言成员返回的关键字段
@@ -13009,27 +13026,27 @@
 验证在线设备集合中的目标设备是否均收到一致结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F498" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G498" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="499" ht="120" customHeight="1">
-      <x:c r="A499" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B499" s="21" t="str">
+      <x:c r="F499" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G499" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="500" ht="120" customHeight="1">
+      <x:c r="A500" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B500" s="21" t="str">
         <x:v>多设备</x:v>
       </x:c>
-      <x:c r="C499" s="18" t="str">
+      <x:c r="C500" s="18" t="str">
         <x:v>群主全员禁言/解禁：状态变更事件同步到接收账号全部在线端</x:v>
       </x:c>
-      <x:c r="D499" s="18" t="str">
+      <x:c r="D500" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E499" s="18" t="str">
+      <x:c r="E500" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 全员禁言
 3. 验证 全员禁言返回的关键字段
@@ -13040,27 +13057,27 @@
 验证在线设备集合中的目标设备是否均收到一致结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F499" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G499" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="500" ht="120" customHeight="1">
-      <x:c r="A500" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B500" s="21" t="str">
+      <x:c r="F500" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G500" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="501" ht="120" customHeight="1">
+      <x:c r="A501" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B501" s="21" t="str">
         <x:v>多设备</x:v>
       </x:c>
-      <x:c r="C500" s="18" t="str">
+      <x:c r="C501" s="18" t="str">
         <x:v>群主添加/移除白名单：白名单变更事件同步到接收账号全部在线端</x:v>
       </x:c>
-      <x:c r="D500" s="18" t="str">
+      <x:c r="D501" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E500" s="18" t="str">
+      <x:c r="E501" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 加入群白名单
 3. 验证加入群白名单返回的关键字段
@@ -13071,27 +13088,27 @@
 验证在线设备集合中的目标设备是否均收到一致结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F500" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G500" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="501" ht="120" customHeight="1">
-      <x:c r="A501" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B501" s="21" t="str">
+      <x:c r="F501" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G501" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="502" ht="120" customHeight="1">
+      <x:c r="A502" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B502" s="21" t="str">
         <x:v>多设备</x:v>
       </x:c>
-      <x:c r="C501" s="18" t="str">
+      <x:c r="C502" s="18" t="str">
         <x:v>群主添加/移除成员：加入与移除事件同步到收发账号全部在线端</x:v>
       </x:c>
-      <x:c r="D501" s="18" t="str">
+      <x:c r="D502" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E501" s="18" t="str">
+      <x:c r="E502" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 添加群成员
 3. 验证 添加群成员返回的关键字段
@@ -13103,35 +13120,6 @@
 验证在线设备集合中的目标设备是否均收到一致结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F501" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G501" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="502" ht="120" customHeight="1">
-      <x:c r="A502" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B502" s="21" t="str">
-        <x:v>多设备</x:v>
-      </x:c>
-      <x:c r="C502" s="18" t="str">
-        <x:v>转让给当前 owner 幂等成功；其他无效目标返回稳定错误且 owner 不变；接收账号全部在线端不触发 owner 变更事件（参数：空）</x:v>
-      </x:c>
-      <x:c r="D502" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
-      </x:c>
-      <x:c r="E502" s="18" t="str">
-        <x:v>1. 测试准备：创建测试群并建立业务前置
-2. A 转让群主
-3. 验证转让群主返回的关键字段
-4. 验证转让群主返回的错误码与错误文案
-5. 测试后置：销毁测试群并恢复群状态
-验证在线设备集合中的目标设备是否均收到一致结果。
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
       <x:c r="F502" s="24" t="str">
         <x:v>普通</x:v>
       </x:c>
@@ -13147,7 +13135,7 @@
         <x:v>多设备</x:v>
       </x:c>
       <x:c r="C503" s="18" t="str">
-        <x:v>转让给当前 owner 幂等成功；其他无效目标返回稳定错误且 owner 不变；接收账号全部在线端不触发 owner 变更事件（参数：current-owner-idempotent）</x:v>
+        <x:v>转让给当前 owner 幂等成功；其他无效目标返回稳定错误且 owner 不变；接收账号全部在线端不触发 owner 变更事件（参数：空）</x:v>
       </x:c>
       <x:c r="D503" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -13176,7 +13164,7 @@
         <x:v>多设备</x:v>
       </x:c>
       <x:c r="C504" s="18" t="str">
-        <x:v>转让给当前 owner 幂等成功；其他无效目标返回稳定错误且 owner 不变；接收账号全部在线端不触发 owner 变更事件（参数：non-成员）</x:v>
+        <x:v>转让给当前 owner 幂等成功；其他无效目标返回稳定错误且 owner 不变；接收账号全部在线端不触发 owner 变更事件（参数：current-owner-idempotent）</x:v>
       </x:c>
       <x:c r="D504" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -13205,7 +13193,7 @@
         <x:v>多设备</x:v>
       </x:c>
       <x:c r="C505" s="18" t="str">
-        <x:v>转让给当前 owner 幂等成功；其他无效目标返回稳定错误且 owner 不变；接收账号全部在线端不触发 owner 变更事件（参数：nonexistent）</x:v>
+        <x:v>转让给当前 owner 幂等成功；其他无效目标返回稳定错误且 owner 不变；接收账号全部在线端不触发 owner 变更事件（参数：non-成员）</x:v>
       </x:c>
       <x:c r="D505" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -13234,38 +13222,67 @@
         <x:v>多设备</x:v>
       </x:c>
       <x:c r="C506" s="18" t="str">
-        <x:v>A 合并同群两条真实文本消息并发送，B 全部在线端收到关联同一群会话的合并消息</x:v>
+        <x:v>转让给当前 owner 幂等成功；其他无效目标返回稳定错误且 owner 不变；接收账号全部在线端不触发 owner 变更事件（参数：nonexistent）</x:v>
       </x:c>
       <x:c r="D506" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E506" s="18" t="str">
+        <x:v>1. 测试准备：创建测试群并建立业务前置
+2. A 转让群主
+3. 验证转让群主返回的关键字段
+4. 验证转让群主返回的错误码与错误文案
+5. 测试后置：销毁测试群并恢复群状态
+验证在线设备集合中的目标设备是否均收到一致结果。
+验证操作结果、关键字段和相关事件符合预期。</x:v>
+      </x:c>
+      <x:c r="F506" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G506" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="507" ht="120" customHeight="1">
+      <x:c r="A507" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B507" s="21" t="str">
+        <x:v>多设备</x:v>
+      </x:c>
+      <x:c r="C507" s="18" t="str">
+        <x:v>A 合并同群两条真实文本消息并发送，B 全部在线端收到关联同一群会话的合并消息</x:v>
+      </x:c>
+      <x:c r="D507" s="18" t="str">
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+      </x:c>
+      <x:c r="E507" s="18" t="str">
         <x:v>1. A 发送第 条源文本消息并记录 消息 ID
 2. A 发送合并消息，并验证 B 全部在线端收到关联消息
 验证在线设备集合中的目标设备是否均收到一致结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F506" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G506" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="507" ht="120" customHeight="1">
-      <x:c r="A507" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B507" s="21" t="str">
+      <x:c r="F507" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G507" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="508" ht="120" customHeight="1">
+      <x:c r="A508" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B508" s="21" t="str">
         <x:v>多设备</x:v>
       </x:c>
-      <x:c r="C507" s="18" t="str">
+      <x:c r="C508" s="18" t="str">
         <x:v>A 将群主转让给管理员 B：B 账号在线端收到 owner 变更事件；B 成 owner，A 成普通成员</x:v>
       </x:c>
-      <x:c r="D507" s="18" t="str">
+      <x:c r="D508" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E507" s="18" t="str">
+      <x:c r="E508" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 添加群管理员
 3. 验证 添加群管理员返回的关键字段
@@ -13276,31 +13293,6 @@
 验证在线设备集合中的目标设备是否均收到一致结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F507" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G507" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="508" ht="120" customHeight="1">
-      <x:c r="A508" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B508" s="21" t="str">
-        <x:v>多设备</x:v>
-      </x:c>
-      <x:c r="C508" s="18" t="str">
-        <x:v>A 向包含 B 的群发送指定类型消息：A 全部在线端同步、B 全部在线端接收（参数：视频）</x:v>
-      </x:c>
-      <x:c r="D508" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
-      </x:c>
-      <x:c r="E508" s="18" t="str">
-        <x:v>1. A 发送 类型群消息，并验证发送端与接收端链路
-验证在线设备集合中的目标设备是否均收到一致结果。
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
       <x:c r="F508" s="24" t="str">
         <x:v>普通</x:v>
       </x:c>
@@ -13316,7 +13308,7 @@
         <x:v>多设备</x:v>
       </x:c>
       <x:c r="C509" s="18" t="str">
-        <x:v>A 向包含 B 的群发送指定类型消息：A 全部在线端同步、B 全部在线端接收（参数：图片）</x:v>
+        <x:v>A 向包含 B 的群发送指定类型消息：A 全部在线端同步、B 全部在线端接收（参数：视频）</x:v>
       </x:c>
       <x:c r="D509" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -13341,7 +13333,7 @@
         <x:v>多设备</x:v>
       </x:c>
       <x:c r="C510" s="18" t="str">
-        <x:v>A 向包含 B 的群发送指定类型消息：A 全部在线端同步、B 全部在线端接收（参数：位置）</x:v>
+        <x:v>A 向包含 B 的群发送指定类型消息：A 全部在线端同步、B 全部在线端接收（参数：图片）</x:v>
       </x:c>
       <x:c r="D510" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -13366,7 +13358,7 @@
         <x:v>多设备</x:v>
       </x:c>
       <x:c r="C511" s="18" t="str">
-        <x:v>A 向包含 B 的群发送指定类型消息：A 全部在线端同步、B 全部在线端接收（参数：文件）</x:v>
+        <x:v>A 向包含 B 的群发送指定类型消息：A 全部在线端同步、B 全部在线端接收（参数：位置）</x:v>
       </x:c>
       <x:c r="D511" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -13391,7 +13383,7 @@
         <x:v>多设备</x:v>
       </x:c>
       <x:c r="C512" s="18" t="str">
-        <x:v>A 向包含 B 的群发送指定类型消息：A 全部在线端同步、B 全部在线端接收（参数：语音）</x:v>
+        <x:v>A 向包含 B 的群发送指定类型消息：A 全部在线端同步、B 全部在线端接收（参数：文件）</x:v>
       </x:c>
       <x:c r="D512" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -13416,7 +13408,7 @@
         <x:v>多设备</x:v>
       </x:c>
       <x:c r="C513" s="18" t="str">
-        <x:v>A 向包含 B 的群发送指定类型消息：A 全部在线端同步、B 全部在线端接收（参数：自定义）</x:v>
+        <x:v>A 向包含 B 的群发送指定类型消息：A 全部在线端同步、B 全部在线端接收（参数：语音）</x:v>
       </x:c>
       <x:c r="D513" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -13441,7 +13433,7 @@
         <x:v>多设备</x:v>
       </x:c>
       <x:c r="C514" s="18" t="str">
-        <x:v>A 向包含 B 的群发送指定类型消息：A 全部在线端同步、B 全部在线端接收（参数：cmd）</x:v>
+        <x:v>A 向包含 B 的群发送指定类型消息：A 全部在线端同步、B 全部在线端接收（参数：自定义）</x:v>
       </x:c>
       <x:c r="D514" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -13466,7 +13458,7 @@
         <x:v>多设备</x:v>
       </x:c>
       <x:c r="C515" s="18" t="str">
-        <x:v>A 向包含 B 的群发送指定类型消息：A 全部在线端同步、B 全部在线端接收（参数：txt）</x:v>
+        <x:v>A 向包含 B 的群发送指定类型消息：A 全部在线端同步、B 全部在线端接收（参数：cmd）</x:v>
       </x:c>
       <x:c r="D515" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -13491,12 +13483,37 @@
         <x:v>多设备</x:v>
       </x:c>
       <x:c r="C516" s="18" t="str">
-        <x:v>A 转让给 B 后 A 失去 owner 权限：B 收到 owner 变更事件，A 收到被移除事件</x:v>
+        <x:v>A 向包含 B 的群发送指定类型消息：A 全部在线端同步、B 全部在线端接收（参数：txt）</x:v>
       </x:c>
       <x:c r="D516" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E516" s="18" t="str">
+        <x:v>1. A 发送 类型群消息，并验证发送端与接收端链路
+验证在线设备集合中的目标设备是否均收到一致结果。
+验证操作结果、关键字段和相关事件符合预期。</x:v>
+      </x:c>
+      <x:c r="F516" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G516" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="517" ht="120" customHeight="1">
+      <x:c r="A517" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B517" s="21" t="str">
+        <x:v>多设备</x:v>
+      </x:c>
+      <x:c r="C517" s="18" t="str">
+        <x:v>A 转让给 B 后 A 失去 owner 权限：B 收到 owner 变更事件，A 收到被移除事件</x:v>
+      </x:c>
+      <x:c r="D517" s="18" t="str">
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+      </x:c>
+      <x:c r="E517" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 转让群主
 3. 验证转让群主返回的关键字段
@@ -13508,27 +13525,27 @@
 验证在线设备集合中的目标设备是否均收到一致结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F516" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G516" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="517" ht="120" customHeight="1">
-      <x:c r="A517" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B517" s="21" t="str">
+      <x:c r="F517" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G517" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="518" ht="120" customHeight="1">
+      <x:c r="A518" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B518" s="21" t="str">
         <x:v>多设备</x:v>
       </x:c>
-      <x:c r="C517" s="18" t="str">
+      <x:c r="C518" s="18" t="str">
         <x:v>B 创建群并邀请 A，A 发送群消息；验证 A 副端同步、B 全部在线端接收及群回执查询</x:v>
       </x:c>
-      <x:c r="D517" s="18" t="str">
+      <x:c r="D518" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E517" s="18" t="str">
+      <x:c r="E518" s="18" t="str">
         <x:v>1. 清理参与设备的历史事件
 2. 创建群并邀请发送账号
 3. 清理建群及入群产生的历史事件
@@ -13540,27 +13557,27 @@
 验证在线设备集合中的目标设备是否均收到一致结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F517" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G517" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="518" ht="120" customHeight="1">
-      <x:c r="A518" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B518" s="21" t="str">
+      <x:c r="F518" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G518" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="519" ht="120" customHeight="1">
+      <x:c r="A519" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B519" s="21" t="str">
         <x:v>多设备</x:v>
       </x:c>
-      <x:c r="C518" s="18" t="str">
+      <x:c r="C519" s="18" t="str">
         <x:v>block 成员 non 成员</x:v>
       </x:c>
-      <x:c r="D518" s="18" t="str">
+      <x:c r="D519" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E518" s="18" t="str">
+      <x:c r="E519" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 加入群黑名单
 3. 验证加入群黑名单返回的错误码与错误文案
@@ -13568,27 +13585,27 @@
 验证在线设备集合中的目标设备是否均收到一致结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F518" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G518" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="519" ht="120" customHeight="1">
-      <x:c r="A519" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B519" s="21" t="str">
+      <x:c r="F519" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G519" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="520" ht="120" customHeight="1">
+      <x:c r="A520" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B520" s="21" t="str">
         <x:v>多设备</x:v>
       </x:c>
-      <x:c r="C519" s="18" t="str">
+      <x:c r="C520" s="18" t="str">
         <x:v>destroyChatThread：子区创建后由 owner 解散，收发账号全部在线端收到 onChatThreadDestroy 事件</x:v>
       </x:c>
-      <x:c r="D519" s="18" t="str">
+      <x:c r="D520" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E519" s="18" t="str">
+      <x:c r="E520" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立成员前置
 2. A 解散子区
 3. 验证 解散子区返回的关键字段
@@ -13596,27 +13613,27 @@
 验证在线设备集合中的目标设备是否均收到一致结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F519" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G519" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="520" ht="120" customHeight="1">
-      <x:c r="A520" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B520" s="21" t="str">
+      <x:c r="F520" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G520" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="521" ht="120" customHeight="1">
+      <x:c r="A521" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B521" s="21" t="str">
         <x:v>多设备</x:v>
       </x:c>
-      <x:c r="C520" s="18" t="str">
+      <x:c r="C521" s="18" t="str">
         <x:v>fetchChatThreadMember / fetchLast消息WithChatThreads：成员列表包含 A/B，新建子区未发线程消息时最新消息映射为空</x:v>
       </x:c>
-      <x:c r="D520" s="18" t="str">
+      <x:c r="D521" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E520" s="18" t="str">
+      <x:c r="E521" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立成员前置
 2. A 查询子区成员
 3. 验证查询子区成员返回的关键字段
@@ -13625,27 +13642,27 @@
 验证在线设备集合中的目标设备是否均收到一致结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F520" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G520" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="521" ht="120" customHeight="1">
-      <x:c r="A521" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B521" s="21" t="str">
+      <x:c r="F521" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G521" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="522" ht="120" customHeight="1">
+      <x:c r="A522" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B522" s="21" t="str">
         <x:v>多设备</x:v>
       </x:c>
-      <x:c r="C521" s="18" t="str">
+      <x:c r="C522" s="18" t="str">
         <x:v>removeMembers 单独传当前群主返回成功但状态不变；接收账号全部在线端不触发移除事件</x:v>
       </x:c>
-      <x:c r="D521" s="18" t="str">
+      <x:c r="D522" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E521" s="18" t="str">
+      <x:c r="E522" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 移除群成员
 3. 验证群业务状态、事件与关键字段
@@ -13654,27 +13671,27 @@
 验证在线设备集合中的目标设备是否均收到一致结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F521" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G521" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="522" ht="120" customHeight="1">
-      <x:c r="A522" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B522" s="21" t="str">
+      <x:c r="F522" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G522" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="523" ht="120" customHeight="1">
+      <x:c r="A523" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B523" s="21" t="str">
         <x:v>多设备</x:v>
       </x:c>
-      <x:c r="C522" s="18" t="str">
+      <x:c r="C523" s="18" t="str">
         <x:v>updateChatThreadSubject / leaveChatThread：更新子区名称后，收发账号全部在线端收到事件，B 退出子区</x:v>
       </x:c>
-      <x:c r="D522" s="18" t="str">
+      <x:c r="D523" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E522" s="18" t="str">
+      <x:c r="E523" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立成员前置
 2. A 执行子区业务操作
 3. 验证执行子区业务操作返回的响应 result 与关键字段
@@ -13686,38 +13703,6 @@
 验证在线设备集合中的目标设备是否均收到一致结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F522" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G522" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="523" ht="120" customHeight="1">
-      <x:c r="A523" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B523" s="21" t="str">
-        <x:v>离线</x:v>
-      </x:c>
-      <x:c r="C523" s="18" t="str">
-        <x:v>审批群群主 A 先离线，B 申请后 A 重登接收申请并同意或拒绝（参数：接受）</x:v>
-      </x:c>
-      <x:c r="D523" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；当前 5.0 默认拓扑中 A、B 两个账号各有两台设备；离线阶段按账号全部设备下线，重新登录后逐台校验。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
-      </x:c>
-      <x:c r="E523" s="18" t="str">
-        <x:v>1. 测试准备：创建测试群并建立业务前置
-2. 测试准备：切换账号设备在线状态
-3. 等待并校验目标业务事件
-4. 验证群业务状态、事件与关键字段
-5. A 执行群组业务操作
-6. 验证执行群组业务操作返回的响应 result 与关键字段
-7. 测试后置：测试准备：切换账号设备在线状态
-8. 测试后置：销毁测试群并恢复环境
-将目标账号的全部设备重新上线，并逐台校验补同步、本地数据和事件结果。
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
       <x:c r="F523" s="24" t="str">
         <x:v>普通</x:v>
       </x:c>
@@ -13733,7 +13718,7 @@
         <x:v>离线</x:v>
       </x:c>
       <x:c r="C524" s="18" t="str">
-        <x:v>审批群群主 A 先离线，B 申请后 A 重登接收申请并同意或拒绝（参数：拒绝）</x:v>
+        <x:v>审批群群主 A 先离线，B 申请后 A 重登接收申请并同意或拒绝（参数：接受）</x:v>
       </x:c>
       <x:c r="D524" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；当前 5.0 默认拓扑中 A、B 两个账号各有两台设备；离线阶段按账号全部设备下线，重新登录后逐台校验。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -13765,12 +13750,44 @@
         <x:v>离线</x:v>
       </x:c>
       <x:c r="C525" s="18" t="str">
-        <x:v>A 离线期间 B 修改自己的群成员属性；A 重登后按成员 ID 查询到同一属性</x:v>
+        <x:v>审批群群主 A 先离线，B 申请后 A 重登接收申请并同意或拒绝（参数：拒绝）</x:v>
       </x:c>
       <x:c r="D525" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；当前 5.0 默认拓扑中 A、B 两个账号各有两台设备；离线阶段按账号全部设备下线，重新登录后逐台校验。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E525" s="18" t="str">
+        <x:v>1. 测试准备：创建测试群并建立业务前置
+2. 测试准备：切换账号设备在线状态
+3. 等待并校验目标业务事件
+4. 验证群业务状态、事件与关键字段
+5. A 执行群组业务操作
+6. 验证执行群组业务操作返回的响应 result 与关键字段
+7. 测试后置：测试准备：切换账号设备在线状态
+8. 测试后置：销毁测试群并恢复环境
+将目标账号的全部设备重新上线，并逐台校验补同步、本地数据和事件结果。
+验证操作结果、关键字段和相关事件符合预期。</x:v>
+      </x:c>
+      <x:c r="F525" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G525" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="526" ht="120" customHeight="1">
+      <x:c r="A526" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B526" s="21" t="str">
+        <x:v>离线</x:v>
+      </x:c>
+      <x:c r="C526" s="18" t="str">
+        <x:v>A 离线期间 B 修改自己的群成员属性；A 重登后按成员 ID 查询到同一属性</x:v>
+      </x:c>
+      <x:c r="D526" s="18" t="str">
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；当前 5.0 默认拓扑中 A、B 两个账号各有两台设备；离线阶段按账号全部设备下线，重新登录后逐台校验。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+      </x:c>
+      <x:c r="E526" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立成员前置
 2. 测试准备：切换账号设备在线状态
 3. B 执行群组业务操作
@@ -13780,38 +13797,6 @@
 将目标账号的全部设备重新上线，并逐台校验补同步、本地数据和事件结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F525" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G525" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="526" ht="120" customHeight="1">
-      <x:c r="A526" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B526" s="21" t="str">
-        <x:v>离线</x:v>
-      </x:c>
-      <x:c r="C526" s="18" t="str">
-        <x:v>A 在 B 处理邀请时离线，A 重登收到接受或拒绝结果并核验成员状态（参数：接受）</x:v>
-      </x:c>
-      <x:c r="D526" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；当前 5.0 默认拓扑中 A、B 两个账号各有两台设备；离线阶段按账号全部设备下线，重新登录后逐台校验。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
-      </x:c>
-      <x:c r="E526" s="18" t="str">
-        <x:v>1. 测试准备：创建测试群并建立成员前置
-2. 等待并校验目标业务事件
-3. 验证群业务状态、事件与关键字段
-4. 测试准备：切换账号设备在线状态
-5. B 接受入群邀请
-6. 验证接受入群邀请返回的响应 result 与关键字段
-7. B 拒绝入群邀请
-8. 验证拒绝入群邀请返回的响应 result 与关键字段
-将目标账号的全部设备重新上线，并逐台校验补同步、本地数据和事件结果。
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
       <x:c r="F526" s="24" t="str">
         <x:v>普通</x:v>
       </x:c>
@@ -13827,7 +13812,7 @@
         <x:v>离线</x:v>
       </x:c>
       <x:c r="C527" s="18" t="str">
-        <x:v>A 在 B 处理邀请时离线，A 重登收到接受或拒绝结果并核验成员状态（参数：拒绝）</x:v>
+        <x:v>A 在 B 处理邀请时离线，A 重登收到接受或拒绝结果并核验成员状态（参数：接受）</x:v>
       </x:c>
       <x:c r="D527" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；当前 5.0 默认拓扑中 A、B 两个账号各有两台设备；离线阶段按账号全部设备下线，重新登录后逐台校验。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -13859,12 +13844,44 @@
         <x:v>离线</x:v>
       </x:c>
       <x:c r="C528" s="18" t="str">
-        <x:v>B 离线积压三条群文本；重登验证完整集合、未读数 3 和最新消息</x:v>
+        <x:v>A 在 B 处理邀请时离线，A 重登收到接受或拒绝结果并核验成员状态（参数：拒绝）</x:v>
       </x:c>
       <x:c r="D528" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；当前 5.0 默认拓扑中 A、B 两个账号各有两台设备；离线阶段按账号全部设备下线，重新登录后逐台校验。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E528" s="18" t="str">
+        <x:v>1. 测试准备：创建测试群并建立成员前置
+2. 等待并校验目标业务事件
+3. 验证群业务状态、事件与关键字段
+4. 测试准备：切换账号设备在线状态
+5. B 接受入群邀请
+6. 验证接受入群邀请返回的响应 result 与关键字段
+7. B 拒绝入群邀请
+8. 验证拒绝入群邀请返回的响应 result 与关键字段
+将目标账号的全部设备重新上线，并逐台校验补同步、本地数据和事件结果。
+验证操作结果、关键字段和相关事件符合预期。</x:v>
+      </x:c>
+      <x:c r="F528" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G528" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="529" ht="120" customHeight="1">
+      <x:c r="A529" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B529" s="21" t="str">
+        <x:v>离线</x:v>
+      </x:c>
+      <x:c r="C529" s="18" t="str">
+        <x:v>B 离线积压三条群文本；重登验证完整集合、未读数 3 和最新消息</x:v>
+      </x:c>
+      <x:c r="D529" s="18" t="str">
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；当前 5.0 默认拓扑中 A、B 两个账号各有两台设备；离线阶段按账号全部设备下线，重新登录后逐台校验。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+      </x:c>
+      <x:c r="E529" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立成员前置
 2. 测试准备：切换账号设备在线状态
 3. 执行群消息动作并验证发送/接收链路
@@ -13875,27 +13892,27 @@
 将目标账号的全部设备重新上线，并逐台校验补同步、本地数据和事件结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F528" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G528" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="529" ht="120" customHeight="1">
-      <x:c r="A529" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B529" s="21" t="str">
+      <x:c r="F529" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G529" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="530" ht="120" customHeight="1">
+      <x:c r="A530" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B530" s="21" t="str">
         <x:v>离线</x:v>
       </x:c>
-      <x:c r="C529" s="18" t="str">
+      <x:c r="C530" s="18" t="str">
         <x:v>B 离线期间 A 更新公告；B 重登从公告查询 API 得到同一动态值</x:v>
       </x:c>
-      <x:c r="D529" s="18" t="str">
+      <x:c r="D530" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；当前 5.0 默认拓扑中 A、B 两个账号各有两台设备；离线阶段按账号全部设备下线，重新登录后逐台校验。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E529" s="18" t="str">
+      <x:c r="E530" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立成员前置
 2. 测试准备：切换账号设备在线状态
 3. A 更新群公告
@@ -13906,27 +13923,27 @@
 将目标账号的全部设备重新上线，并逐台校验补同步、本地数据和事件结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F529" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G529" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="530" ht="120" customHeight="1">
-      <x:c r="A530" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B530" s="21" t="str">
+      <x:c r="F530" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G530" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="531" ht="120" customHeight="1">
+      <x:c r="A531" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B531" s="21" t="str">
         <x:v>离线</x:v>
       </x:c>
-      <x:c r="C530" s="18" t="str">
+      <x:c r="C531" s="18" t="str">
         <x:v>B 离线期间被加入群黑名单；重登后成员移除且服务端黑名单包含 B</x:v>
       </x:c>
-      <x:c r="D530" s="18" t="str">
+      <x:c r="D531" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；当前 5.0 默认拓扑中 A、B 两个账号各有两台设备；离线阶段按账号全部设备下线，重新登录后逐台校验。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E530" s="18" t="str">
+      <x:c r="E531" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立成员前置
 2. 测试准备：切换账号设备在线状态
 3. A 加入群黑名单
@@ -13937,27 +13954,27 @@
 将目标账号的全部设备重新上线，并逐台校验补同步、本地数据和事件结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F530" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G530" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="531" ht="120" customHeight="1">
-      <x:c r="A531" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B531" s="21" t="str">
+      <x:c r="F531" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G531" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="532" ht="120" customHeight="1">
+      <x:c r="A532" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B532" s="21" t="str">
         <x:v>离线</x:v>
       </x:c>
-      <x:c r="C531" s="18" t="str">
+      <x:c r="C532" s="18" t="str">
         <x:v>B 离线期间被禁言/解除禁言；每次重登均从服务端名单验证最终状态</x:v>
       </x:c>
-      <x:c r="D531" s="18" t="str">
+      <x:c r="D532" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；当前 5.0 默认拓扑中 A、B 两个账号各有两台设备；离线阶段按账号全部设备下线，重新登录后逐台校验。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E531" s="18" t="str">
+      <x:c r="E532" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立成员前置
 2. 测试准备：切换账号设备在线状态
 3. A 禁言成员
@@ -13968,27 +13985,27 @@
 将目标账号的全部设备重新上线，并逐台校验补同步、本地数据和事件结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F531" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G531" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="532" ht="120" customHeight="1">
-      <x:c r="A532" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B532" s="21" t="str">
+      <x:c r="F532" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G532" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="533" ht="120" customHeight="1">
+      <x:c r="A533" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B533" s="21" t="str">
         <x:v>离线</x:v>
       </x:c>
-      <x:c r="C532" s="18" t="str">
+      <x:c r="C533" s="18" t="str">
         <x:v>B 离线期间被设为/移出管理员；每次重登均验证本地角色和服务端 adminList</x:v>
       </x:c>
-      <x:c r="D532" s="18" t="str">
+      <x:c r="D533" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；当前 5.0 默认拓扑中 A、B 两个账号各有两台设备；离线阶段按账号全部设备下线，重新登录后逐台校验。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E532" s="18" t="str">
+      <x:c r="E533" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立成员前置
 2. 测试准备：切换账号设备在线状态
 3. A 添加群管理员
@@ -13999,27 +14016,27 @@
 将目标账号的全部设备重新上线，并逐台校验补同步、本地数据和事件结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F532" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G532" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="533" ht="120" customHeight="1">
-      <x:c r="A533" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B533" s="21" t="str">
+      <x:c r="F533" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G533" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="534" ht="120" customHeight="1">
+      <x:c r="A534" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B534" s="21" t="str">
         <x:v>离线</x:v>
       </x:c>
-      <x:c r="C533" s="18" t="str">
+      <x:c r="C534" s="18" t="str">
         <x:v>B 离线期间被移出；重登收到真实终态事件且本地/服务端均不再入群</x:v>
       </x:c>
-      <x:c r="D533" s="18" t="str">
+      <x:c r="D534" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；当前 5.0 默认拓扑中 A、B 两个账号各有两台设备；离线阶段按账号全部设备下线，重新登录后逐台校验。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E533" s="18" t="str">
+      <x:c r="E534" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立成员前置
 2. 测试准备：切换账号设备在线状态
 3. A 移除群成员
@@ -14028,35 +14045,6 @@
 将目标账号的全部设备重新上线，并逐台校验补同步、本地数据和事件结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F533" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G533" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="534" ht="120" customHeight="1">
-      <x:c r="A534" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B534" s="21" t="str">
-        <x:v>离线</x:v>
-      </x:c>
-      <x:c r="C534" s="18" t="str">
-        <x:v>B 离线期间更新名称/描述/头像/扩展；重登后按真实服务端字段验收（参数：avatarUrl）</x:v>
-      </x:c>
-      <x:c r="D534" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；当前 5.0 默认拓扑中 A、B 两个账号各有两台设备；离线阶段按账号全部设备下线，重新登录后逐台校验。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
-      </x:c>
-      <x:c r="E534" s="18" t="str">
-        <x:v>1. 测试准备：创建测试群并建立成员前置
-2. 测试准备：切换账号设备在线状态
-3. A 执行群组业务操作
-4. 验证执行群组业务操作返回的响应 result 与关键字段
-5. 验证群业务状态、事件与关键字段
-将目标账号的全部设备重新上线，并逐台校验补同步、本地数据和事件结果。
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
       <x:c r="F534" s="24" t="str">
         <x:v>普通</x:v>
       </x:c>
@@ -14072,7 +14060,7 @@
         <x:v>离线</x:v>
       </x:c>
       <x:c r="C535" s="18" t="str">
-        <x:v>B 离线期间更新名称/描述/头像/扩展；重登后按真实服务端字段验收（参数：desc）</x:v>
+        <x:v>B 离线期间更新名称/描述/头像/扩展；重登后按真实服务端字段验收（参数：avatarUrl）</x:v>
       </x:c>
       <x:c r="D535" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；当前 5.0 默认拓扑中 A、B 两个账号各有两台设备；离线阶段按账号全部设备下线，重新登录后逐台校验。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -14101,7 +14089,7 @@
         <x:v>离线</x:v>
       </x:c>
       <x:c r="C536" s="18" t="str">
-        <x:v>B 离线期间更新名称/描述/头像/扩展；重登后按真实服务端字段验收（参数：ext）</x:v>
+        <x:v>B 离线期间更新名称/描述/头像/扩展；重登后按真实服务端字段验收（参数：desc）</x:v>
       </x:c>
       <x:c r="D536" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；当前 5.0 默认拓扑中 A、B 两个账号各有两台设备；离线阶段按账号全部设备下线，重新登录后逐台校验。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -14130,7 +14118,7 @@
         <x:v>离线</x:v>
       </x:c>
       <x:c r="C537" s="18" t="str">
-        <x:v>B 离线期间更新名称/描述/头像/扩展；重登后按真实服务端字段验收（参数：name）</x:v>
+        <x:v>B 离线期间更新名称/描述/头像/扩展；重登后按真实服务端字段验收（参数：ext）</x:v>
       </x:c>
       <x:c r="D537" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；当前 5.0 默认拓扑中 A、B 两个账号各有两台设备；离线阶段按账号全部设备下线，重新登录后逐台校验。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -14159,12 +14147,41 @@
         <x:v>离线</x:v>
       </x:c>
       <x:c r="C538" s="18" t="str">
-        <x:v>B 离线期间加入/移出白名单；每次重登均从服务端白名单验证</x:v>
+        <x:v>B 离线期间更新名称/描述/头像/扩展；重登后按真实服务端字段验收（参数：name）</x:v>
       </x:c>
       <x:c r="D538" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；当前 5.0 默认拓扑中 A、B 两个账号各有两台设备；离线阶段按账号全部设备下线，重新登录后逐台校验。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E538" s="18" t="str">
+        <x:v>1. 测试准备：创建测试群并建立成员前置
+2. 测试准备：切换账号设备在线状态
+3. A 执行群组业务操作
+4. 验证执行群组业务操作返回的响应 result 与关键字段
+5. 验证群业务状态、事件与关键字段
+将目标账号的全部设备重新上线，并逐台校验补同步、本地数据和事件结果。
+验证操作结果、关键字段和相关事件符合预期。</x:v>
+      </x:c>
+      <x:c r="F538" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G538" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="539" ht="120" customHeight="1">
+      <x:c r="A539" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B539" s="21" t="str">
+        <x:v>离线</x:v>
+      </x:c>
+      <x:c r="C539" s="18" t="str">
+        <x:v>B 离线期间加入/移出白名单；每次重登均从服务端白名单验证</x:v>
+      </x:c>
+      <x:c r="D539" s="18" t="str">
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；当前 5.0 默认拓扑中 A、B 两个账号各有两台设备；离线阶段按账号全部设备下线，重新登录后逐台校验。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+      </x:c>
+      <x:c r="E539" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立成员前置
 2. 测试准备：切换账号设备在线状态
 3. A 执行群组业务操作
@@ -14175,27 +14192,27 @@
 将目标账号的全部设备重新上线，并逐台校验补同步、本地数据和事件结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F538" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G538" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="539" ht="120" customHeight="1">
-      <x:c r="A539" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B539" s="21" t="str">
+      <x:c r="F539" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G539" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="540" ht="120" customHeight="1">
+      <x:c r="A540" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B540" s="21" t="str">
         <x:v>离线</x:v>
       </x:c>
-      <x:c r="C539" s="18" t="str">
+      <x:c r="C540" s="18" t="str">
         <x:v>B 离线期间接任群主；重登后本地和服务端 owner/permissionType 均为新群主</x:v>
       </x:c>
-      <x:c r="D539" s="18" t="str">
+      <x:c r="D540" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；当前 5.0 默认拓扑中 A、B 两个账号各有两台设备；离线阶段按账号全部设备下线，重新登录后逐台校验。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E539" s="18" t="str">
+      <x:c r="E540" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立成员前置
 2. 测试准备：切换账号设备在线状态
 3. A 转让群主
@@ -14207,27 +14224,27 @@
 将目标账号的全部设备重新上线，并逐台校验补同步、本地数据和事件结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F539" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G539" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="540" ht="120" customHeight="1">
-      <x:c r="A540" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B540" s="21" t="str">
+      <x:c r="F540" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G540" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="541" ht="120" customHeight="1">
+      <x:c r="A541" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B541" s="21" t="str">
         <x:v>离线</x:v>
       </x:c>
-      <x:c r="C540" s="18" t="str">
+      <x:c r="C541" s="18" t="str">
         <x:v>B 离线期间全员禁言/解除；每次重登均查询 isAllMemberMuted</x:v>
       </x:c>
-      <x:c r="D540" s="18" t="str">
+      <x:c r="D541" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；当前 5.0 默认拓扑中 A、B 两个账号各有两台设备；离线阶段按账号全部设备下线，重新登录后逐台校验。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E540" s="18" t="str">
+      <x:c r="E541" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立成员前置
 2. 测试准备：切换账号设备在线状态
 3. A 执行群组业务操作
@@ -14236,27 +14253,27 @@
 将目标账号的全部设备重新上线，并逐台校验补同步、本地数据和事件结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F540" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G540" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="541" ht="120" customHeight="1">
-      <x:c r="A541" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B541" s="21" t="str">
+      <x:c r="F541" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G541" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="542" ht="120" customHeight="1">
+      <x:c r="A542" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B542" s="21" t="str">
         <x:v>离线</x:v>
       </x:c>
-      <x:c r="C541" s="18" t="str">
+      <x:c r="C542" s="18" t="str">
         <x:v>B 离线期间群被解散；重登收到解散事件且本地/服务端 joined 投影为空</x:v>
       </x:c>
-      <x:c r="D541" s="18" t="str">
+      <x:c r="D542" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；当前 5.0 默认拓扑中 A、B 两个账号各有两台设备；离线阶段按账号全部设备下线，重新登录后逐台校验。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E541" s="18" t="str">
+      <x:c r="E542" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立成员前置
 2. 测试准备：切换账号设备在线状态
 3. A 销毁测试群
@@ -14265,27 +14282,27 @@
 将目标账号的全部设备重新上线，并逐台校验补同步、本地数据和事件结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F541" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G541" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="542" ht="120" customHeight="1">
-      <x:c r="A542" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B542" s="21" t="str">
+      <x:c r="F542" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G542" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="543" ht="120" customHeight="1">
+      <x:c r="A543" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B543" s="21" t="str">
         <x:v>离线</x:v>
       </x:c>
-      <x:c r="C542" s="18" t="str">
+      <x:c r="C543" s="18" t="str">
         <x:v>B 离线期间上传/删除共享文件；每次重登均从服务端文件列表验证终态</x:v>
       </x:c>
-      <x:c r="D542" s="18" t="str">
+      <x:c r="D543" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；当前 5.0 默认拓扑中 A、B 两个账号各有两台设备；离线阶段按账号全部设备下线，重新登录后逐台校验。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E542" s="18" t="str">
+      <x:c r="E543" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立成员前置
 2. 测试准备：切换账号设备在线状态
 3. A 上传群共享文件
@@ -14297,27 +14314,27 @@
 将目标账号的全部设备重新上线，并逐台校验补同步、本地数据和事件结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F542" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G542" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="543" ht="120" customHeight="1">
-      <x:c r="A543" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B543" s="21" t="str">
+      <x:c r="F543" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G543" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="544" ht="120" customHeight="1">
+      <x:c r="A544" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B544" s="21" t="str">
         <x:v>离线</x:v>
       </x:c>
-      <x:c r="C543" s="18" t="str">
+      <x:c r="C544" s="18" t="str">
         <x:v>B 离线时 A 发群文本；B 重登收到同一真实 消息 ID 和群会话正文</x:v>
       </x:c>
-      <x:c r="D543" s="18" t="str">
+      <x:c r="D544" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；当前 5.0 默认拓扑中 A、B 两个账号各有两台设备；离线阶段按账号全部设备下线，重新登录后逐台校验。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E543" s="18" t="str">
+      <x:c r="E544" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立成员前置
 2. 测试准备：切换账号设备在线状态
 3. 执行群消息动作并验证发送/接收链路
@@ -14326,27 +14343,27 @@
 将目标账号的全部设备重新上线，并逐台校验补同步、本地数据和事件结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F543" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G543" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="544" ht="120" customHeight="1">
-      <x:c r="A544" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B544" s="21" t="str">
+      <x:c r="F544" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G544" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="545" ht="120" customHeight="1">
+      <x:c r="A545" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B545" s="21" t="str">
         <x:v>离线</x:v>
       </x:c>
-      <x:c r="C544" s="18" t="str">
+      <x:c r="C545" s="18" t="str">
         <x:v>B 离线时群 CMD 设置 deliver在线Only=true；重登无旧事件且本地无消息</x:v>
       </x:c>
-      <x:c r="D544" s="18" t="str">
+      <x:c r="D545" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；当前 5.0 默认拓扑中 A、B 两个账号各有两台设备；离线阶段按账号全部设备下线，重新登录后逐台校验。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E544" s="18" t="str">
+      <x:c r="E545" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立成员前置
 2. 测试准备：切换账号设备在线状态
 3. A 发送群消息
@@ -14357,38 +14374,6 @@
 将目标账号的全部设备重新上线，并逐台校验补同步、本地数据和事件结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F544" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G544" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="545" ht="120" customHeight="1">
-      <x:c r="A545" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B545" s="21" t="str">
-        <x:v>离线</x:v>
-      </x:c>
-      <x:c r="C545" s="18" t="str">
-        <x:v>B 申请审批群后离线，A 处理；B 重登收到审批结果并验证最终状态（参数：接受）</x:v>
-      </x:c>
-      <x:c r="D545" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；当前 5.0 默认拓扑中 A、B 两个账号各有两台设备；离线阶段按账号全部设备下线，重新登录后逐台校验。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
-      </x:c>
-      <x:c r="E545" s="18" t="str">
-        <x:v>1. 测试准备：创建测试群并建立业务前置
-2. 等待并校验目标业务事件
-3. 验证群业务状态、事件与关键字段
-4. 测试准备：切换账号设备在线状态
-5. A 执行群组业务操作
-6. 验证执行群组业务操作返回的响应 result 与关键字段
-7. 测试后置：测试准备：切换账号设备在线状态
-8. 测试后置：销毁测试群并恢复环境
-将目标账号的全部设备重新上线，并逐台校验补同步、本地数据和事件结果。
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
       <x:c r="F545" s="24" t="str">
         <x:v>普通</x:v>
       </x:c>
@@ -14404,7 +14389,7 @@
         <x:v>离线</x:v>
       </x:c>
       <x:c r="C546" s="18" t="str">
-        <x:v>B 申请审批群后离线，A 处理；B 重登收到审批结果并验证最终状态（参数：拒绝）</x:v>
+        <x:v>B 申请审批群后离线，A 处理；B 重登收到审批结果并验证最终状态（参数：接受）</x:v>
       </x:c>
       <x:c r="D546" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；当前 5.0 默认拓扑中 A、B 两个账号各有两台设备；离线阶段按账号全部设备下线，重新登录后逐台校验。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -14436,12 +14421,44 @@
         <x:v>离线</x:v>
       </x:c>
       <x:c r="C547" s="18" t="str">
-        <x:v>B 收到群消息后在 A 离线期间发送 已读回执；A 重登最终查询 count=1</x:v>
+        <x:v>B 申请审批群后离线，A 处理；B 重登收到审批结果并验证最终状态（参数：拒绝）</x:v>
       </x:c>
       <x:c r="D547" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；当前 5.0 默认拓扑中 A、B 两个账号各有两台设备；离线阶段按账号全部设备下线，重新登录后逐台校验。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E547" s="18" t="str">
+        <x:v>1. 测试准备：创建测试群并建立业务前置
+2. 等待并校验目标业务事件
+3. 验证群业务状态、事件与关键字段
+4. 测试准备：切换账号设备在线状态
+5. A 执行群组业务操作
+6. 验证执行群组业务操作返回的响应 result 与关键字段
+7. 测试后置：测试准备：切换账号设备在线状态
+8. 测试后置：销毁测试群并恢复环境
+将目标账号的全部设备重新上线，并逐台校验补同步、本地数据和事件结果。
+验证操作结果、关键字段和相关事件符合预期。</x:v>
+      </x:c>
+      <x:c r="F547" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G547" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="548" ht="120" customHeight="1">
+      <x:c r="A548" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B548" s="21" t="str">
+        <x:v>离线</x:v>
+      </x:c>
+      <x:c r="C548" s="18" t="str">
+        <x:v>B 收到群消息后在 A 离线期间发送 已读回执；A 重登最终查询 count=1</x:v>
+      </x:c>
+      <x:c r="D548" s="18" t="str">
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；当前 5.0 默认拓扑中 A、B 两个账号各有两台设备；离线阶段按账号全部设备下线，重新登录后逐台校验。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+      </x:c>
+      <x:c r="E548" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立成员前置
 2. A 发送群消息
 3. 验证发送群消息返回的关键字段
@@ -14453,27 +14470,27 @@
 将目标账号的全部设备重新上线，并逐台校验补同步、本地数据和事件结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F547" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G547" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="548" ht="120" customHeight="1">
-      <x:c r="A548" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B548" s="21" t="str">
+      <x:c r="F548" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G548" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="549" ht="120" customHeight="1">
+      <x:c r="A549" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B549" s="21" t="str">
         <x:v>离线</x:v>
       </x:c>
-      <x:c r="C548" s="18" t="str">
+      <x:c r="C549" s="18" t="str">
         <x:v>B 首次接收前 A 撤回群文本；B 重登验证撤回回放和本地最终删除</x:v>
       </x:c>
-      <x:c r="D548" s="18" t="str">
+      <x:c r="D549" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；当前 5.0 默认拓扑中 A、B 两个账号各有两台设备；离线阶段按账号全部设备下线，重新登录后逐台校验。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E548" s="18" t="str">
+      <x:c r="E549" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立成员前置
 2. 测试准备：切换账号设备在线状态
 3. 执行群消息动作并验证发送/接收链路
@@ -14484,38 +14501,6 @@
 将目标账号的全部设备重新上线，并逐台校验补同步、本地数据和事件结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F548" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G548" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="549" ht="120" customHeight="1">
-      <x:c r="A549" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B549" s="21" t="str">
-        <x:v>离线</x:v>
-      </x:c>
-      <x:c r="C549" s="18" t="str">
-        <x:v>B 先离线，重登收到群邀请并接受或拒绝，验证权限和最终成员状态（参数：接受）</x:v>
-      </x:c>
-      <x:c r="D549" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；当前 5.0 默认拓扑中 A、B 两个账号各有两台设备；离线阶段按账号全部设备下线，重新登录后逐台校验。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
-      </x:c>
-      <x:c r="E549" s="18" t="str">
-        <x:v>1. 测试准备：切换账号设备在线状态
-2. 测试准备：创建测试群并建立成员前置
-3. 验证群业务状态、事件与关键字段
-4. 等待并校验目标业务事件
-5. B 接受入群邀请
-6. 验证接受入群邀请返回的响应 result 与关键字段
-7. B 拒绝入群邀请
-8. 验证拒绝入群邀请返回的响应 result 与关键字段
-将目标账号的全部设备重新上线，并逐台校验补同步、本地数据和事件结果。
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
       <x:c r="F549" s="24" t="str">
         <x:v>普通</x:v>
       </x:c>
@@ -14531,7 +14516,7 @@
         <x:v>离线</x:v>
       </x:c>
       <x:c r="C550" s="18" t="str">
-        <x:v>B 先离线，重登收到群邀请并接受或拒绝，验证权限和最终成员状态（参数：拒绝）</x:v>
+        <x:v>B 先离线，重登收到群邀请并接受或拒绝，验证权限和最终成员状态（参数：接受）</x:v>
       </x:c>
       <x:c r="D550" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；当前 5.0 默认拓扑中 A、B 两个账号各有两台设备；离线阶段按账号全部设备下线，重新登录后逐台校验。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -14563,20 +14548,20 @@
         <x:v>离线</x:v>
       </x:c>
       <x:c r="C551" s="18" t="str">
-        <x:v>B 已收群文本后离线，A 撤回；B 重登验证撤回事件和本地最终删除</x:v>
+        <x:v>B 先离线，重登收到群邀请并接受或拒绝，验证权限和最终成员状态（参数：拒绝）</x:v>
       </x:c>
       <x:c r="D551" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；当前 5.0 默认拓扑中 A、B 两个账号各有两台设备；离线阶段按账号全部设备下线，重新登录后逐台校验。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E551" s="18" t="str">
-        <x:v>1. 测试准备：创建测试群并建立成员前置
-2. 执行群消息动作并验证发送/接收链路
-3. 等待并关联目标业务事件
-4. 验证群业务状态、事件与关键字段
-5. 测试准备：切换账号设备在线状态
-6. A 执行群消息操作
-7. 验证执行群消息操作返回的响应 result 与关键字段
-8. 动作端 执行群消息操作
+        <x:v>1. 测试准备：切换账号设备在线状态
+2. 测试准备：创建测试群并建立成员前置
+3. 验证群业务状态、事件与关键字段
+4. 等待并校验目标业务事件
+5. B 接受入群邀请
+6. 验证接受入群邀请返回的响应 result 与关键字段
+7. B 拒绝入群邀请
+8. 验证拒绝入群邀请返回的响应 result 与关键字段
 将目标账号的全部设备重新上线，并逐台校验补同步、本地数据和事件结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
@@ -14595,7 +14580,7 @@
         <x:v>离线</x:v>
       </x:c>
       <x:c r="C552" s="18" t="str">
-        <x:v>B 已收群文本后离线，A 修改正文；B 重登验证修改事件和本地最终正文</x:v>
+        <x:v>B 已收群文本后离线，A 撤回；B 重登验证撤回事件和本地最终删除</x:v>
       </x:c>
       <x:c r="D552" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；当前 5.0 默认拓扑中 A、B 两个账号各有两台设备；离线阶段按账号全部设备下线，重新登录后逐台校验。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -14627,12 +14612,44 @@
         <x:v>离线</x:v>
       </x:c>
       <x:c r="C553" s="18" t="str">
-        <x:v>B 主动退群后 logout/login；成员数、joined groups 和本地群对象保持退出终态</x:v>
+        <x:v>B 已收群文本后离线，A 修改正文；B 重登验证修改事件和本地最终正文</x:v>
       </x:c>
       <x:c r="D553" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；当前 5.0 默认拓扑中 A、B 两个账号各有两台设备；离线阶段按账号全部设备下线，重新登录后逐台校验。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E553" s="18" t="str">
+        <x:v>1. 测试准备：创建测试群并建立成员前置
+2. 执行群消息动作并验证发送/接收链路
+3. 等待并关联目标业务事件
+4. 验证群业务状态、事件与关键字段
+5. 测试准备：切换账号设备在线状态
+6. A 执行群消息操作
+7. 验证执行群消息操作返回的响应 result 与关键字段
+8. 动作端 执行群消息操作
+将目标账号的全部设备重新上线，并逐台校验补同步、本地数据和事件结果。
+验证操作结果、关键字段和相关事件符合预期。</x:v>
+      </x:c>
+      <x:c r="F553" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G553" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="554" ht="120" customHeight="1">
+      <x:c r="A554" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B554" s="21" t="str">
+        <x:v>离线</x:v>
+      </x:c>
+      <x:c r="C554" s="18" t="str">
+        <x:v>B 主动退群后 logout/login；成员数、joined groups 和本地群对象保持退出终态</x:v>
+      </x:c>
+      <x:c r="D554" s="18" t="str">
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；当前 5.0 默认拓扑中 A、B 两个账号各有两台设备；离线阶段按账号全部设备下线，重新登录后逐台校验。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+      </x:c>
+      <x:c r="E554" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立成员前置
 2. B 退出群
 3. 验证退出群返回的关键字段
@@ -14641,35 +14658,6 @@
 将目标账号的全部设备重新上线，并逐台校验补同步、本地数据和事件结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F553" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G553" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="554" ht="120" customHeight="1">
-      <x:c r="A554" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B554" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C554" s="18" t="str">
-        <x:v>`requestToJoinPublicGroup` 只允许 PublicJoinNeedApproval(style=2)（参数：private-成员）</x:v>
-      </x:c>
-      <x:c r="D554" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
-      </x:c>
-      <x:c r="E554" s="18" t="str">
-        <x:v>1. 测试准备：创建测试群并建立业务前置
-2. B 申请加入公开群
-3. 等待并校验目标业务事件
-4. 验证申请加入公开群返回的响应 result 与关键字段
-5. 验证申请加入公开群返回的错误码与错误文案
-6. 测试后置：销毁测试群并恢复群状态
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
       <x:c r="F554" s="24" t="str">
         <x:v>普通</x:v>
       </x:c>
@@ -14685,7 +14673,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C555" s="18" t="str">
-        <x:v>`requestToJoinPublicGroup` 只允许 PublicJoinNeedApproval(style=2)（参数：private-owner）</x:v>
+        <x:v>5.0 入群申请/自动入群：私有群拒绝，PublicOpenJoin(style=3) 自动入群（参数：private-成员）</x:v>
       </x:c>
       <x:c r="D555" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -14714,7 +14702,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C556" s="18" t="str">
-        <x:v>`requestToJoinPublicGroup` 只允许 PublicJoinNeedApproval(style=2)（参数：public-open）</x:v>
+        <x:v>5.0 入群申请/自动入群：私有群拒绝，PublicOpenJoin(style=3) 自动入群（参数：private-owner）</x:v>
       </x:c>
       <x:c r="D556" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -14743,46 +14731,47 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C557" s="18" t="str">
+        <x:v>5.0 入群申请/自动入群：私有群拒绝，PublicOpenJoin(style=3) 自动入群（参数：public-open）</x:v>
+      </x:c>
+      <x:c r="D557" s="18" t="str">
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+      </x:c>
+      <x:c r="E557" s="18" t="str">
+        <x:v>1. 测试准备：创建测试群并建立业务前置
+2. B 申请加入公开群
+3. 等待并校验目标业务事件
+4. 验证申请加入公开群返回的响应 result 与关键字段
+5. 验证申请加入公开群返回的错误码与错误文案
+6. 测试后置：销毁测试群并恢复群状态
+验证操作结果、关键字段和相关事件符合预期。</x:v>
+      </x:c>
+      <x:c r="F557" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G557" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="558" ht="120" customHeight="1">
+      <x:c r="A558" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B558" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C558" s="18" t="str">
         <x:v>创建 group 空 name</x:v>
       </x:c>
-      <x:c r="D557" s="18" t="str">
+      <x:c r="D558" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E557" s="18" t="str">
+      <x:c r="E558" s="18" t="str">
         <x:v>1. A 创建群
 2. 验证创建群返回的关键字段
 3. A 销毁测试群
 4. 验证销毁测试群返回的关键字段
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F557" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G557" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="558" ht="120" customHeight="1">
-      <x:c r="A558" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B558" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C558" s="18" t="str">
-        <x:v>创建 group 文本 fields additional inputs（参数：desc_multiline-desc-line1\nline2\nline3-None）</x:v>
-      </x:c>
-      <x:c r="D558" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
-      </x:c>
-      <x:c r="E558" s="18" t="str">
-        <x:v>1. A 创建群
-2. 验证创建群返回的错误码与错误文案
-3. 验证创建群返回的关键字段
-4. A 销毁测试群
-5. 验证销毁测试群返回的关键字段
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
       <x:c r="F558" s="24" t="str">
         <x:v>普通</x:v>
       </x:c>
@@ -14798,7 +14787,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C559" s="18" t="str">
-        <x:v>创建 group 文本 fields additional inputs（参数：desc_space_only-desc- -None）</x:v>
+        <x:v>创建 group 文本 fields additional inputs（参数：desc_multiline-desc-line1\nline2\nline3-None）</x:v>
       </x:c>
       <x:c r="D559" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -14826,7 +14815,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C560" s="18" t="str">
-        <x:v>创建 group 文本 fields additional inputs（参数：desc_symbols-desc-desc_!@#$%^&amp;*()[]{}&lt;&gt;?/\\|-None）</x:v>
+        <x:v>创建 group 文本 fields additional inputs（参数：desc_space_only-desc- -None）</x:v>
       </x:c>
       <x:c r="D560" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -14854,7 +14843,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C561" s="18" t="str">
-        <x:v>创建 group 文本 fields additional inputs（参数：group_name_mixed_symbols-groupName-group-name_!@#$%^&amp;*()[]{}-None）</x:v>
+        <x:v>创建 group 文本 fields additional inputs（参数：desc_symbols-desc-desc_!@#$%^&amp;*()[]{}&lt;&gt;?/\\|-None）</x:v>
       </x:c>
       <x:c r="D561" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -14882,7 +14871,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C562" s="18" t="str">
-        <x:v>创建 group 文本 fields additional inputs（参数：group_name_tabs-groupName-\tgroup\tname\t-None）</x:v>
+        <x:v>创建 group 文本 fields additional inputs（参数：group_name_mixed_symbols-groupName-group-name_!@#$%^&amp;*()[]{}-None）</x:v>
       </x:c>
       <x:c r="D562" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -14910,7 +14899,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C563" s="18" t="str">
-        <x:v>创建 group 文本 fields additional inputs（参数：invite_reason_multiline-inviteReason-reason line1\nreason line2-None）</x:v>
+        <x:v>创建 group 文本 fields additional inputs（参数：group_name_tabs-groupName-\tgroup\tname\t-None）</x:v>
       </x:c>
       <x:c r="D563" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -14938,7 +14927,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C564" s="18" t="str">
-        <x:v>创建 group 文本 fields additional inputs（参数：invite_reason_space_only-inviteReason- -None）</x:v>
+        <x:v>创建 group 文本 fields additional inputs（参数：invite_reason_multiline-inviteReason-reason line1\nreason line2-None）</x:v>
       </x:c>
       <x:c r="D564" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -14966,7 +14955,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C565" s="18" t="str">
-        <x:v>创建 group 文本 fields additional inputs（参数：invite_reason_symbols-inviteReason-reason_!@#$%^&amp;*()[]{}&lt;&gt;?/\\|-None）</x:v>
+        <x:v>创建 group 文本 fields additional inputs（参数：invite_reason_space_only-inviteReason- -None）</x:v>
       </x:c>
       <x:c r="D565" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -14994,7 +14983,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C566" s="18" t="str">
-        <x:v>创建 group desc reason 查询条件 abnormal inputs（参数：查询条件_ext_too_long_1025-overrides2-None）</x:v>
+        <x:v>创建 group 文本 fields additional inputs（参数：invite_reason_symbols-inviteReason-reason_!@#$%^&amp;*()[]{}&lt;&gt;?/\\|-None）</x:v>
       </x:c>
       <x:c r="D566" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -15022,7 +15011,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C567" s="18" t="str">
-        <x:v>创建 group desc reason 查询条件 abnormal inputs（参数：查询条件_max_count_0-overrides3-expect_error3）</x:v>
+        <x:v>创建 group desc reason 查询条件 abnormal inputs（参数：查询条件_ext_too_long_1025-overrides2-None）</x:v>
       </x:c>
       <x:c r="D567" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -15050,7 +15039,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C568" s="18" t="str">
-        <x:v>创建 group desc reason 查询条件 abnormal inputs（参数：查询条件_max_count_negative-overrides4-expect_error4）</x:v>
+        <x:v>创建 group desc reason 查询条件 abnormal inputs（参数：查询条件_max_count_0-overrides3-expect_error3）</x:v>
       </x:c>
       <x:c r="D568" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -15078,7 +15067,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C569" s="18" t="str">
-        <x:v>创建 group desc reason 查询条件 abnormal inputs（参数：查询条件_style_out_of_range-overrides5-None）</x:v>
+        <x:v>创建 group desc reason 查询条件 abnormal inputs（参数：查询条件_max_count_negative-overrides4-expect_error4）</x:v>
       </x:c>
       <x:c r="D569" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -15106,7 +15095,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C570" s="18" t="str">
-        <x:v>创建 group desc reason 查询条件 abnormal inputs（参数：desc_too_long_513-overrides0-None）</x:v>
+        <x:v>创建 group desc reason 查询条件 abnormal inputs（参数：查询条件_style_out_of_range-overrides5-None）</x:v>
       </x:c>
       <x:c r="D570" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -15134,7 +15123,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C571" s="18" t="str">
-        <x:v>创建 group desc reason 查询条件 abnormal inputs（参数：invite_reason_too_long_1025-overrides1-None）</x:v>
+        <x:v>创建 group desc reason 查询条件 abnormal inputs（参数：desc_too_long_513-overrides0-None）</x:v>
       </x:c>
       <x:c r="D571" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -15162,7 +15151,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C572" s="18" t="str">
-        <x:v>创建 group invite 成员 abnormal inputs（参数：invite_members_重复_user-invite_members0-None）</x:v>
+        <x:v>创建 group desc reason 查询条件 abnormal inputs（参数：invite_reason_too_long_1025-overrides1-None）</x:v>
       </x:c>
       <x:c r="D572" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -15190,7 +15179,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C573" s="18" t="str">
-        <x:v>创建 group invite 成员 abnormal inputs（参数：invite_members_contains_nonexistent_user-invite_members1-expect_error1）</x:v>
+        <x:v>创建 group invite 成员 abnormal inputs（参数：invite_members_重复_user-invite_members0-None）</x:v>
       </x:c>
       <x:c r="D573" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -15218,37 +15207,12 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C574" s="18" t="str">
-        <x:v>创建 group max count less than invite 成员</x:v>
+        <x:v>创建 group invite 成员 abnormal inputs（参数：invite_members_contains_nonexistent_user-invite_members1-expect_error1）</x:v>
       </x:c>
       <x:c r="D574" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E574" s="18" t="str">
-        <x:v>1. A 创建群
-2. 验证创建群返回的错误码与错误文案
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
-      <x:c r="F574" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G574" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="575" ht="120" customHeight="1">
-      <x:c r="A575" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B575" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C575" s="18" t="str">
-        <x:v>创建 group name and avatar abnormal inputs（参数：avatar_url_ftp_protocol-overrides5-None）</x:v>
-      </x:c>
-      <x:c r="D575" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
-      </x:c>
-      <x:c r="E575" s="18" t="str">
         <x:v>1. A 创建群
 2. 验证创建群返回的错误码与错误文案
 3. 验证创建群返回的关键字段
@@ -15256,6 +15220,31 @@
 5. 验证销毁测试群返回的关键字段
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
+      <x:c r="F574" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G574" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="575" ht="120" customHeight="1">
+      <x:c r="A575" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B575" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C575" s="18" t="str">
+        <x:v>创建 group max count less than invite 成员</x:v>
+      </x:c>
+      <x:c r="D575" s="18" t="str">
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+      </x:c>
+      <x:c r="E575" s="18" t="str">
+        <x:v>1. A 创建群
+2. 验证创建群返回的错误码与错误文案
+验证操作结果、关键字段和相关事件符合预期。</x:v>
+      </x:c>
       <x:c r="F575" s="24" t="str">
         <x:v>普通</x:v>
       </x:c>
@@ -15271,7 +15260,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C576" s="18" t="str">
-        <x:v>创建 group name and avatar abnormal inputs（参数：avatar_url_not_url-overrides4-None）</x:v>
+        <x:v>创建 group name and avatar abnormal inputs（参数：avatar_url_ftp_protocol-overrides5-None）</x:v>
       </x:c>
       <x:c r="D576" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -15299,7 +15288,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C577" s="18" t="str">
-        <x:v>创建 group name and avatar abnormal inputs（参数：avatar_url_too_long-overrides6-expect_error6）</x:v>
+        <x:v>创建 group name and avatar abnormal inputs（参数：avatar_url_not_url-overrides4-None）</x:v>
       </x:c>
       <x:c r="D577" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -15327,7 +15316,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C578" s="18" t="str">
-        <x:v>创建 group name and avatar abnormal inputs（参数：group_name_control_chars-overrides3-None）</x:v>
+        <x:v>创建 group name and avatar abnormal inputs（参数：avatar_url_too_long-overrides6-expect_error6）</x:v>
       </x:c>
       <x:c r="D578" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -15355,7 +15344,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C579" s="18" t="str">
-        <x:v>创建 group name and avatar abnormal inputs（参数：group_name_space_only-overrides0-None）</x:v>
+        <x:v>创建 group name and avatar abnormal inputs（参数：group_name_control_chars-overrides3-None）</x:v>
       </x:c>
       <x:c r="D579" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -15383,7 +15372,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C580" s="18" t="str">
-        <x:v>创建 group name and avatar abnormal inputs（参数：group_name_too_long_256-overrides1-None）</x:v>
+        <x:v>创建 group name and avatar abnormal inputs（参数：group_name_space_only-overrides0-None）</x:v>
       </x:c>
       <x:c r="D580" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -15411,7 +15400,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C581" s="18" t="str">
-        <x:v>创建 group name and avatar abnormal inputs（参数：group_name_too_long_512-overrides2-None）</x:v>
+        <x:v>创建 group name and avatar abnormal inputs（参数：group_name_too_long_256-overrides1-None）</x:v>
       </x:c>
       <x:c r="D581" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -15439,16 +15428,17 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C582" s="18" t="str">
-        <x:v>创建 group optional fields 空（参数：查询条件_ext_空-overrides4）</x:v>
+        <x:v>创建 group name and avatar abnormal inputs（参数：group_name_too_long_512-overrides2-None）</x:v>
       </x:c>
       <x:c r="D582" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E582" s="18" t="str">
         <x:v>1. A 创建群
-2. 验证创建群返回的关键字段
-3. A 销毁测试群
-4. 验证销毁测试群返回的关键字段
+2. 验证创建群返回的错误码与错误文案
+3. 验证创建群返回的关键字段
+4. A 销毁测试群
+5. 验证销毁测试群返回的关键字段
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
       <x:c r="F582" s="24" t="str">
@@ -15466,7 +15456,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C583" s="18" t="str">
-        <x:v>创建 group optional fields 空（参数：avatar_url_空-overrides0）</x:v>
+        <x:v>创建 group optional fields 空（参数：查询条件_ext_空-overrides4）</x:v>
       </x:c>
       <x:c r="D583" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -15493,7 +15483,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C584" s="18" t="str">
-        <x:v>创建 group optional fields 空（参数：desc_空-overrides1）</x:v>
+        <x:v>创建 group optional fields 空（参数：avatar_url_空-overrides0）</x:v>
       </x:c>
       <x:c r="D584" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -15520,7 +15510,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C585" s="18" t="str">
-        <x:v>创建 group optional fields 空（参数：invite_members_空-overrides2）</x:v>
+        <x:v>创建 group optional fields 空（参数：desc_空-overrides1）</x:v>
       </x:c>
       <x:c r="D585" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -15547,7 +15537,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C586" s="18" t="str">
-        <x:v>创建 group optional fields 空（参数：invite_reason_空-overrides3）</x:v>
+        <x:v>创建 group optional fields 空（参数：invite_members_空-overrides2）</x:v>
       </x:c>
       <x:c r="D586" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -15574,19 +15564,16 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C587" s="18" t="str">
-        <x:v>错误 inviter 处理邀请应失败，随后正确 inviter 仍可接受同一 pending（参数：接受）</x:v>
+        <x:v>创建 group optional fields 空（参数：invite_reason_空-overrides3）</x:v>
       </x:c>
       <x:c r="D587" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E587" s="18" t="str">
-        <x:v>1. 测试准备：创建测试群并建立成员前置
-2. B 执行群组业务操作
-3. B 接受入群邀请
-4. 验证接受入群邀请返回的错误码与错误文案
-5. 验证接受入群邀请返回的响应 result 与关键字段
-6. 等待并校验目标业务事件
-7. 测试后置：销毁测试群并恢复群状态
+        <x:v>1. A 创建群
+2. 验证创建群返回的关键字段
+3. A 销毁测试群
+4. 验证销毁测试群返回的关键字段
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
       <x:c r="F587" s="24" t="str">
@@ -15604,7 +15591,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C588" s="18" t="str">
-        <x:v>错误 inviter 处理邀请应失败，随后正确 inviter 仍可接受同一 pending（参数：拒绝）</x:v>
+        <x:v>错误 inviter 处理邀请应失败，随后正确 inviter 仍可接受同一 pending（参数：接受）</x:v>
       </x:c>
       <x:c r="D588" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -15634,17 +15621,19 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C589" s="18" t="str">
-        <x:v>冻结三种群角色屏蔽/取消屏蔽群消息的真实 SDK 行为（参数：成员）</x:v>
+        <x:v>错误 inviter 处理邀请应失败，随后正确 inviter 仍可接受同一 pending（参数：拒绝）</x:v>
       </x:c>
       <x:c r="D589" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E589" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立成员前置
-2. 动作端 屏蔽群消息
-3. 验证群业务状态、事件与关键字段
-4. 动作端 取消屏蔽群消息
-5. 测试后置：销毁测试群并恢复群状态
+2. B 执行群组业务操作
+3. B 接受入群邀请
+4. 验证接受入群邀请返回的错误码与错误文案
+5. 验证接受入群邀请返回的响应 result 与关键字段
+6. 等待并校验目标业务事件
+7. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
       <x:c r="F589" s="24" t="str">
@@ -15662,7 +15651,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C590" s="18" t="str">
-        <x:v>冻结三种群角色屏蔽/取消屏蔽群消息的真实 SDK 行为（参数：admin）</x:v>
+        <x:v>冻结三种群角色屏蔽/取消屏蔽群消息的真实 SDK 行为（参数：成员）</x:v>
       </x:c>
       <x:c r="D590" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -15690,7 +15679,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C591" s="18" t="str">
-        <x:v>冻结三种群角色屏蔽/取消屏蔽群消息的真实 SDK 行为（参数：owner）</x:v>
+        <x:v>冻结三种群角色屏蔽/取消屏蔽群消息的真实 SDK 行为（参数：admin）</x:v>
       </x:c>
       <x:c r="D591" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -15718,13 +15707,17 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C592" s="18" t="str">
-        <x:v>防止 3000 场景漏传给建群请求，或覆盖 maxCount=2 的容量边界用例</x:v>
+        <x:v>冻结三种群角色屏蔽/取消屏蔽群消息的真实 SDK 行为（参数：owner）</x:v>
       </x:c>
       <x:c r="D592" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；测试账号已创建并登录，当前 Case 所需的基础数据已准备。；服务端所需权限及目标对象已准备。</x:v>
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E592" s="18" t="str">
-        <x:v>1. 验证本用例的关键业务结果
+        <x:v>1. 测试准备：创建测试群并建立成员前置
+2. 动作端 屏蔽群消息
+3. 验证群业务状态、事件与关键字段
+4. 动作端 取消屏蔽群消息
+5. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
       <x:c r="F592" s="24" t="str">
@@ -15742,13 +15735,13 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C593" s="18" t="str">
-        <x:v>防止错误的运行参数创建无效容量群并污染真实测试环境（参数：-1）</x:v>
+        <x:v>防止 3000 场景漏传给建群请求，或覆盖 maxCount=2 的容量边界用例</x:v>
       </x:c>
       <x:c r="D593" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；测试账号已创建并登录，当前 Case 所需的基础数据已准备。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E593" s="18" t="str">
-        <x:v>1. 验证非法容量 被拒绝并返回 ValueError
+        <x:v>1. 验证本用例的关键业务结果
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
       <x:c r="F593" s="24" t="str">
@@ -15766,7 +15759,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C594" s="18" t="str">
-        <x:v>防止错误的运行参数创建无效容量群并污染真实测试环境（参数：0）</x:v>
+        <x:v>防止错误的运行参数创建无效容量群并污染真实测试环境（参数：-1）</x:v>
       </x:c>
       <x:c r="D594" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；测试账号已创建并登录，当前 Case 所需的基础数据已准备。；服务端所需权限及目标对象已准备。</x:v>
@@ -15790,13 +15783,13 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C595" s="18" t="str">
-        <x:v>防止默认群容量漂移，或扩容场景没有将常规建群容量切换为 3000</x:v>
+        <x:v>防止错误的运行参数创建无效容量群并污染真实测试环境（参数：0）</x:v>
       </x:c>
       <x:c r="D595" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；测试账号已创建并登录，当前 Case 所需的基础数据已准备。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E595" s="18" t="str">
-        <x:v>1. 验证本用例的关键业务结果
+        <x:v>1. 验证非法容量 被拒绝并返回 ValueError
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
       <x:c r="F595" s="24" t="str">
@@ -15814,7 +15807,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C596" s="18" t="str">
-        <x:v>防止未传 max_user_count_value 的群快照断言在 3000 场景退回 200</x:v>
+        <x:v>防止默认群容量漂移，或扩容场景没有将常规建群容量切换为 3000</x:v>
       </x:c>
       <x:c r="D596" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；测试账号已创建并登录，当前 Case 所需的基础数据已准备。；服务端所需权限及目标对象已准备。</x:v>
@@ -15838,17 +15831,13 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C597" s="18" t="str">
-        <x:v>非成员不能处理其他用户的有效 pending 申请（参数：接受）</x:v>
+        <x:v>防止未传 max_user_count_value 的群快照断言在 3000 场景退回 200</x:v>
       </x:c>
       <x:c r="D597" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；测试账号已创建并登录，当前 Case 所需的基础数据已准备。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E597" s="18" t="str">
-        <x:v>1. 测试准备：创建测试群并建立业务前置
-2. A 执行群组业务操作
-3. 验证执行群组业务操作返回的错误码与错误文案
-4. 验证执行群组业务操作返回的响应 result 与关键字段
-5. 测试后置：销毁测试群并恢复群状态
+        <x:v>1. 验证本用例的关键业务结果
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
       <x:c r="F597" s="24" t="str">
@@ -15866,7 +15855,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C598" s="18" t="str">
-        <x:v>非成员不能处理其他用户的有效 pending 申请（参数：拒绝）</x:v>
+        <x:v>非成员不能处理其他用户的有效 pending 申请（参数：接受）</x:v>
       </x:c>
       <x:c r="D598" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -15894,14 +15883,17 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C599" s="18" t="str">
-        <x:v>服务端 state list nonexistent group（参数：getGroupBlockListFromServer）</x:v>
+        <x:v>非成员不能处理其他用户的有效 pending 申请（参数：拒绝）</x:v>
       </x:c>
       <x:c r="D599" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E599" s="18" t="str">
-        <x:v>1. A 执行群组业务操作
-2. 验证执行群组业务操作返回的错误码与错误文案
+        <x:v>1. 测试准备：创建测试群并建立业务前置
+2. A 执行群组业务操作
+3. 验证执行群组业务操作返回的错误码与错误文案
+4. 验证执行群组业务操作返回的响应 result 与关键字段
+5. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
       <x:c r="F599" s="24" t="str">
@@ -15919,7 +15911,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C600" s="18" t="str">
-        <x:v>服务端 state list nonexistent group（参数：getGroupMuteListFromServer）</x:v>
+        <x:v>服务端 state list nonexistent group（参数：getGroupBlockListFromServer）</x:v>
       </x:c>
       <x:c r="D600" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -15944,7 +15936,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C601" s="18" t="str">
-        <x:v>服务端 state list nonexistent group（参数：getGroupWhiteListFromServer）</x:v>
+        <x:v>服务端 state list nonexistent group（参数：getGroupMuteListFromServer）</x:v>
       </x:c>
       <x:c r="D601" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -15969,7 +15961,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C602" s="18" t="str">
-        <x:v>服务端 state list nonexistent group（参数：isMemberInWhiteListFromServer）</x:v>
+        <x:v>服务端 state list nonexistent group（参数：getGroupWhiteListFromServer）</x:v>
       </x:c>
       <x:c r="D602" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -15994,12 +15986,37 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C603" s="18" t="str">
+        <x:v>服务端 state list nonexistent group（参数：isMemberInWhiteListFromServer）</x:v>
+      </x:c>
+      <x:c r="D603" s="18" t="str">
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+      </x:c>
+      <x:c r="E603" s="18" t="str">
+        <x:v>1. A 执行群组业务操作
+2. 验证执行群组业务操作返回的错误码与错误文案
+验证操作结果、关键字段和相关事件符合预期。</x:v>
+      </x:c>
+      <x:c r="F603" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G603" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="604" ht="120" customHeight="1">
+      <x:c r="A604" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B604" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C604" s="18" t="str">
         <x:v>复现流程： 1) 邀请别人入群（addMembers） 2) getGroupWithId（本地）读取人数 3) getGroupSpecificationFromServer（服务端）读取人数 4) 再次 getGroupWithId（本地）读取人数，验证与服务端一致 说明： - 若本地人数与服务端人数不一致，则判定“复现到问题”； - 若未出现不一致，则该环境下未复现，使用 skip 标记</x:v>
       </x:c>
-      <x:c r="D603" s="18" t="str">
+      <x:c r="D604" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E603" s="18" t="str">
+      <x:c r="E604" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 添加群成员
 3. 验证 添加群成员返回的关键字段
@@ -16010,27 +16027,27 @@
 8. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F603" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G603" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="604" ht="120" customHeight="1">
-      <x:c r="A604" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B604" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C604" s="18" t="str">
+      <x:c r="F604" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G604" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="605" ht="120" customHeight="1">
+      <x:c r="A605" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B605" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C605" s="18" t="str">
         <x:v>更新本人昵称/头像后，fetchGroupMembersInfo 返回的本人 EMGroupMemberInfo 字段保持一致</x:v>
       </x:c>
-      <x:c r="D604" s="18" t="str">
+      <x:c r="D605" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E604" s="18" t="str">
+      <x:c r="E605" s="18" t="str">
         <x:v>1. A 查询用户资料
 2. 验证查询用户资料返回的响应 result 与关键字段
 3. 测试准备：创建测试群并建立业务前置
@@ -16040,33 +16057,6 @@
 7. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F604" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G604" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="605" ht="120" customHeight="1">
-      <x:c r="A605" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B605" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C605" s="18" t="str">
-        <x:v>管理员和普通成员不能解散群，失败后群仍可由群主查询和清理（参数：成员）</x:v>
-      </x:c>
-      <x:c r="D605" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
-      </x:c>
-      <x:c r="E605" s="18" t="str">
-        <x:v>1. 测试准备：创建测试群并建立成员前置
-2. B 销毁测试群
-3. 验证销毁测试群返回的错误码与错误文案
-4. 测试后置：销毁测试群并恢复群状态
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
       <x:c r="F605" s="24" t="str">
         <x:v>普通</x:v>
       </x:c>
@@ -16082,7 +16072,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C606" s="18" t="str">
-        <x:v>管理员和普通成员不能解散群，失败后群仍可由群主查询和清理（参数：admin）</x:v>
+        <x:v>管理员和普通成员不能解散群，失败后群仍可由群主查询和清理（参数：成员）</x:v>
       </x:c>
       <x:c r="D606" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -16109,19 +16099,16 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C607" s="18" t="str">
-        <x:v>管理员可修改群名称、描述、扩展；普通成员返回群字段权限错误（参数：成员）</x:v>
+        <x:v>管理员和普通成员不能解散群，失败后群仍可由群主查询和清理（参数：admin）</x:v>
       </x:c>
       <x:c r="D607" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E607" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立成员前置
-2. B 执行群组业务操作
-3. 验证执行群组业务操作返回的错误码与错误文案
-4. 验证群业务状态、事件与关键字段
-5. 验证执行群组业务操作返回的响应 result 与关键字段
-6. 等待并校验目标业务事件
-7. 测试后置：销毁测试群并恢复群状态
+2. B 销毁测试群
+3. 验证销毁测试群返回的错误码与错误文案
+4. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
       <x:c r="F607" s="24" t="str">
@@ -16139,7 +16126,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C608" s="18" t="str">
-        <x:v>管理员可修改群名称、描述、扩展；普通成员返回群字段权限错误（参数：admin）</x:v>
+        <x:v>管理员可修改群名称、描述、扩展；普通成员返回群字段权限错误（参数：成员）</x:v>
       </x:c>
       <x:c r="D608" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -16169,18 +16156,18 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C609" s="18" t="str">
-        <x:v>管理员可增删群黑名单；普通成员返回管理员权限错误且状态不变（参数：成员）</x:v>
+        <x:v>管理员可修改群名称、描述、扩展；普通成员返回群字段权限错误（参数：admin）</x:v>
       </x:c>
       <x:c r="D609" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E609" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立成员前置
-2. 将目标成员加入群黑名单
-3. 验证移出群黑名单返回的错误码与错误文案
+2. B 执行群组业务操作
+3. 验证执行群组业务操作返回的错误码与错误文案
 4. 验证群业务状态、事件与关键字段
-5. 等待并校验目标业务事件
-6. 将目标成员移出群黑名单
+5. 验证执行群组业务操作返回的响应 result 与关键字段
+6. 等待并校验目标业务事件
 7. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
@@ -16199,7 +16186,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C610" s="18" t="str">
-        <x:v>管理员可增删群黑名单；普通成员返回管理员权限错误且状态不变（参数：admin）</x:v>
+        <x:v>管理员可增删群黑名单；普通成员返回管理员权限错误且状态不变（参数：成员）</x:v>
       </x:c>
       <x:c r="D610" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -16229,14 +16216,19 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C611" s="18" t="str">
-        <x:v>获取 成员 属性 nonexistent group</x:v>
+        <x:v>管理员可增删群黑名单；普通成员返回管理员权限错误且状态不变（参数：admin）</x:v>
       </x:c>
       <x:c r="D611" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E611" s="18" t="str">
-        <x:v>1. A 执行群组业务操作
-2. 验证执行群组业务操作返回的响应 result 与关键字段
+        <x:v>1. 测试准备：创建测试群并建立成员前置
+2. 将目标成员加入群黑名单
+3. 验证移出群黑名单返回的错误码与错误文案
+4. 验证群业务状态、事件与关键字段
+5. 等待并校验目标业务事件
+6. 将目标成员移出群黑名单
+7. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
       <x:c r="F611" s="24" t="str">
@@ -16279,69 +16271,68 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C613" s="18" t="str">
-        <x:v>获取 announcement nonexistent group</x:v>
+        <x:v>获取 成员 属性 nonexistent group</x:v>
       </x:c>
       <x:c r="D613" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E613" s="18" t="str">
+        <x:v>1. A 执行群组业务操作
+2. 验证执行群组业务操作返回的响应 result 与关键字段
+验证操作结果、关键字段和相关事件符合预期。</x:v>
+      </x:c>
+      <x:c r="F613" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G613" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="614" ht="120" customHeight="1">
+      <x:c r="A614" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B614" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C614" s="18" t="str">
+        <x:v>获取 announcement nonexistent group</x:v>
+      </x:c>
+      <x:c r="D614" s="18" t="str">
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+      </x:c>
+      <x:c r="E614" s="18" t="str">
         <x:v>1. A 查询群公告
 2. 验证查询群公告返回的错误码与错误文案
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F613" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G613" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="614" ht="120" customHeight="1">
-      <x:c r="A614" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B614" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C614" s="18" t="str">
+      <x:c r="F614" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G614" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="615" ht="120" customHeight="1">
+      <x:c r="A615" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B615" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C615" s="18" t="str">
         <x:v>获取 group 成员 list 从服务端 成功</x:v>
       </x:c>
-      <x:c r="D614" s="18" t="str">
+      <x:c r="D615" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E614" s="18" t="str">
+      <x:c r="E615" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 查询服务端成员列表
 3. 验证查询服务端成员列表返回的关键字段
 4. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F614" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G614" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="615" ht="120" customHeight="1">
-      <x:c r="A615" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B615" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C615" s="18" t="str">
-        <x:v>获取 group 成员 list 从服务端 无效 paging（参数：-1-20）</x:v>
-      </x:c>
-      <x:c r="D615" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
-      </x:c>
-      <x:c r="E615" s="18" t="str">
-        <x:v>1. A 查询服务端成员列表
-2. 验证查询服务端成员列表返回的关键字段
-3. 验证查询服务端成员列表返回的错误码与错误文案
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
       <x:c r="F615" s="24" t="str">
         <x:v>普通</x:v>
       </x:c>
@@ -16357,7 +16348,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C616" s="18" t="str">
-        <x:v>获取 group 成员 list 从服务端 无效 paging（参数：0-20）</x:v>
+        <x:v>获取 group 成员 list 从服务端 无效 paging（参数：-1-20）</x:v>
       </x:c>
       <x:c r="D616" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -16383,7 +16374,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C617" s="18" t="str">
-        <x:v>获取 group 成员 list 从服务端 无效 paging（参数：1--1）</x:v>
+        <x:v>获取 group 成员 list 从服务端 无效 paging（参数：0-20）</x:v>
       </x:c>
       <x:c r="D617" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -16409,7 +16400,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C618" s="18" t="str">
-        <x:v>获取 group 成员 list 从服务端 无效 paging（参数：1-0）</x:v>
+        <x:v>获取 group 成员 list 从服务端 无效 paging（参数：1--1）</x:v>
       </x:c>
       <x:c r="D618" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -16435,14 +16426,15 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C619" s="18" t="str">
-        <x:v>获取 group 成员 list 从服务端 nonexistent group</x:v>
+        <x:v>获取 group 成员 list 从服务端 无效 paging（参数：1-0）</x:v>
       </x:c>
       <x:c r="D619" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E619" s="18" t="str">
         <x:v>1. A 查询服务端成员列表
-2. 验证查询服务端成员列表返回的错误码与错误文案
+2. 验证查询服务端成员列表返回的关键字段
+3. 验证查询服务端成员列表返回的错误码与错误文案
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
       <x:c r="F619" s="24" t="str">
@@ -16460,147 +16452,147 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C620" s="18" t="str">
+        <x:v>获取 group 成员 list 从服务端 nonexistent group</x:v>
+      </x:c>
+      <x:c r="D620" s="18" t="str">
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+      </x:c>
+      <x:c r="E620" s="18" t="str">
+        <x:v>1. A 查询服务端成员列表
+2. 验证查询服务端成员列表返回的错误码与错误文案
+验证操作结果、关键字段和相关事件符合预期。</x:v>
+      </x:c>
+      <x:c r="F620" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G620" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="621" ht="120" customHeight="1">
+      <x:c r="A621" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B621" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C621" s="18" t="str">
         <x:v>获取 group 从服务端</x:v>
       </x:c>
-      <x:c r="D620" s="18" t="str">
+      <x:c r="D621" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E620" s="18" t="str">
+      <x:c r="E621" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 查询服务端群详情
 3. 验证查询服务端群详情返回的关键字段
 4. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F620" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G620" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="621" ht="120" customHeight="1">
-      <x:c r="A621" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B621" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C621" s="18" t="str">
+      <x:c r="F621" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G621" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="622" ht="120" customHeight="1">
+      <x:c r="A622" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B622" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C622" s="18" t="str">
         <x:v>获取 group 从服务端 after destroy</x:v>
       </x:c>
-      <x:c r="D621" s="18" t="str">
+      <x:c r="D622" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E621" s="18" t="str">
+      <x:c r="E622" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. 测试后置：销毁测试群并恢复群状态
 3. A 查询服务端群详情
 4. 验证查询服务端群详情返回的错误码与错误文案
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F621" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G621" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="622" ht="120" customHeight="1">
-      <x:c r="A622" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B622" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C622" s="18" t="str">
+      <x:c r="F622" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G622" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="623" ht="120" customHeight="1">
+      <x:c r="A623" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B623" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C623" s="18" t="str">
         <x:v>获取 group 从服务端 nonexistent</x:v>
       </x:c>
-      <x:c r="D622" s="18" t="str">
+      <x:c r="D623" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E622" s="18" t="str">
+      <x:c r="E623" s="18" t="str">
         <x:v>1. A 查询服务端群详情
 2. 验证查询服务端群详情返回的错误码与错误文案
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F622" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G622" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="623" ht="120" customHeight="1">
-      <x:c r="A623" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B623" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C623" s="18" t="str">
+      <x:c r="F623" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G623" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="624" ht="120" customHeight="1">
+      <x:c r="A624" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B624" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C624" s="18" t="str">
         <x:v>获取 group 带 id nonexistent</x:v>
       </x:c>
-      <x:c r="D623" s="18" t="str">
+      <x:c r="D624" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E623" s="18" t="str">
+      <x:c r="E624" s="18" t="str">
         <x:v>1. A 查询本地群详情
 2. 验证查询本地群详情返回的关键字段
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F623" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G623" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="624" ht="120" customHeight="1">
-      <x:c r="A624" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B624" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C624" s="18" t="str">
+      <x:c r="F624" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G624" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="625" ht="120" customHeight="1">
+      <x:c r="A625" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B625" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C625" s="18" t="str">
         <x:v>获取 group 文件 list 从服务端 成功</x:v>
       </x:c>
-      <x:c r="D624" s="18" t="str">
+      <x:c r="D625" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E624" s="18" t="str">
+      <x:c r="E625" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 查询群共享文件列表
 3. 验证查询群共享文件列表返回的关键字段
 4. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F624" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G624" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="625" ht="120" customHeight="1">
-      <x:c r="A625" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B625" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C625" s="18" t="str">
-        <x:v>获取 group 文件 list 从服务端 nonexistent group（参数：0-20）</x:v>
-      </x:c>
-      <x:c r="D625" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
-      </x:c>
-      <x:c r="E625" s="18" t="str">
-        <x:v>1. A 查询群共享文件列表
-2. 验证查询群共享文件列表返回的错误码与错误文案
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
       <x:c r="F625" s="24" t="str">
         <x:v>普通</x:v>
       </x:c>
@@ -16616,7 +16608,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C626" s="18" t="str">
-        <x:v>获取 group 文件 list 从服务端 nonexistent group（参数：1-0）</x:v>
+        <x:v>获取 group 文件 list 从服务端 nonexistent group（参数：0-20）</x:v>
       </x:c>
       <x:c r="D626" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -16641,7 +16633,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C627" s="18" t="str">
-        <x:v>获取 group 文件 list 从服务端 nonexistent group（参数：1-20）</x:v>
+        <x:v>获取 group 文件 list 从服务端 nonexistent group（参数：1-0）</x:v>
       </x:c>
       <x:c r="D627" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -16666,66 +16658,91 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C628" s="18" t="str">
+        <x:v>获取 group 文件 list 从服务端 nonexistent group（参数：1-20）</x:v>
+      </x:c>
+      <x:c r="D628" s="18" t="str">
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+      </x:c>
+      <x:c r="E628" s="18" t="str">
+        <x:v>1. A 查询群共享文件列表
+2. 验证查询群共享文件列表返回的错误码与错误文案
+验证操作结果、关键字段和相关事件符合预期。</x:v>
+      </x:c>
+      <x:c r="F628" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G628" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="629" ht="120" customHeight="1">
+      <x:c r="A629" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B629" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C629" s="18" t="str">
         <x:v>获取 group block list 从服务端 成功</x:v>
       </x:c>
-      <x:c r="D628" s="18" t="str">
+      <x:c r="D629" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E628" s="18" t="str">
+      <x:c r="E629" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 查询群黑名单
 3. 验证查询群黑名单返回的关键字段
 4. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F628" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G628" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="629" ht="120" customHeight="1">
-      <x:c r="A629" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B629" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C629" s="18" t="str">
+      <x:c r="F629" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G629" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="630" ht="120" customHeight="1">
+      <x:c r="A630" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B630" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C630" s="18" t="str">
         <x:v>获取 group mute list 从服务端 成功</x:v>
       </x:c>
-      <x:c r="D629" s="18" t="str">
+      <x:c r="D630" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E629" s="18" t="str">
+      <x:c r="E630" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 查询群禁言列表
 3. 验证查询群禁言列表返回的关键字段
 4. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F629" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G629" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="630" ht="120" customHeight="1">
-      <x:c r="A630" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B630" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C630" s="18" t="str">
+      <x:c r="F630" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G630" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="631" ht="120" customHeight="1">
+      <x:c r="A631" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B631" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C631" s="18" t="str">
         <x:v>获取 group white list and 成员 check 成功</x:v>
       </x:c>
-      <x:c r="D630" s="18" t="str">
+      <x:c r="D631" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E630" s="18" t="str">
+      <x:c r="E631" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 查询群白名单
 3. 验证查询群白名单返回的关键字段
@@ -16734,107 +16751,81 @@
 6. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F630" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G630" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="631" ht="120" customHeight="1">
-      <x:c r="A631" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B631" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C631" s="18" t="str">
+      <x:c r="F631" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G631" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="632" ht="120" customHeight="1">
+      <x:c r="A632" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B632" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C632" s="18" t="str">
         <x:v>获取 joined group count 带扩展信息</x:v>
       </x:c>
-      <x:c r="D631" s="18" t="str">
+      <x:c r="D632" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E631" s="18" t="str">
+      <x:c r="E632" s="18" t="str">
         <x:v>1. A 查询已加入群数量
 2. 验证查询已加入群数量返回的关键字段
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F631" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G631" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="632" ht="120" customHeight="1">
-      <x:c r="A632" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B632" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C632" s="18" t="str">
+      <x:c r="F632" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G632" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="633" ht="120" customHeight="1">
+      <x:c r="A633" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B633" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C633" s="18" t="str">
         <x:v>获取 joined groups 从服务端 带扩展信息</x:v>
       </x:c>
-      <x:c r="D632" s="18" t="str">
+      <x:c r="D633" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E632" s="18" t="str">
+      <x:c r="E633" s="18" t="str">
         <x:v>1. A 查询服务端已加入群列表
 2. 验证查询服务端已加入群列表返回的关键字段
 5.0 说明：移除 getJoinedGroupsFromServer（残留，改本地 getJoinedGroups）</x:v>
       </x:c>
-      <x:c r="F632" s="25" t="str">
+      <x:c r="F633" s="25" t="str">
         <x:v>5.0 不可用</x:v>
       </x:c>
-      <x:c r="G632" t="str">
+      <x:c r="G633" t="str">
         <x:v>5.0 不可用</x:v>
       </x:c>
     </x:row>
-    <x:row r="633" ht="120" customHeight="1">
-      <x:c r="A633" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B633" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C633" s="18" t="str">
+    <x:row r="634" ht="120" customHeight="1">
+      <x:c r="A634" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B634" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C634" s="18" t="str">
         <x:v>获取 joined groups 带扩展信息</x:v>
       </x:c>
-      <x:c r="D633" s="18" t="str">
+      <x:c r="D634" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E633" s="18" t="str">
+      <x:c r="E634" s="18" t="str">
         <x:v>1. A 查询本地已加入群列表
 2. 验证查询本地已加入群列表返回的关键字段
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F633" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G633" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="634" ht="120" customHeight="1">
-      <x:c r="A634" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B634" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C634" s="18" t="str">
-        <x:v>获取 public groups 从服务端 无效 paging（参数：-1-20）</x:v>
-      </x:c>
-      <x:c r="D634" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
-      </x:c>
-      <x:c r="E634" s="18" t="str">
-        <x:v>1. A 查询公开群列表
-2. 验证查询公开群列表返回的关键字段
-3. 验证群业务状态、事件与关键字段
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
       <x:c r="F634" s="24" t="str">
         <x:v>普通</x:v>
       </x:c>
@@ -16850,7 +16841,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C635" s="18" t="str">
-        <x:v>获取 public groups 从服务端 无效 paging（参数：0-20）</x:v>
+        <x:v>获取 public groups 从服务端 无效 paging（参数：-1-20）</x:v>
       </x:c>
       <x:c r="D635" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -16876,7 +16867,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C636" s="18" t="str">
-        <x:v>获取 public groups 从服务端 无效 paging（参数：1--1）</x:v>
+        <x:v>获取 public groups 从服务端 无效 paging（参数：0-20）</x:v>
       </x:c>
       <x:c r="D636" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -16902,7 +16893,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C637" s="18" t="str">
-        <x:v>获取 public groups 从服务端 无效 paging（参数：1-0）</x:v>
+        <x:v>获取 public groups 从服务端 无效 paging（参数：1--1）</x:v>
       </x:c>
       <x:c r="D637" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -16928,16 +16919,15 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C638" s="18" t="str">
-        <x:v>即使 style=1 允许成员邀请，非成员仍不能调用任一邀请 API（参数：添加-成员）</x:v>
+        <x:v>获取 public groups 从服务端 无效 paging（参数：1-0）</x:v>
       </x:c>
       <x:c r="D638" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E638" s="18" t="str">
-        <x:v>1. 测试准备：创建测试群并建立业务前置
-2. B 执行群组业务操作
-3. 验证执行群组业务操作返回的错误码与错误文案
-4. 测试后置：销毁测试群并恢复群状态
+        <x:v>1. A 查询公开群列表
+2. 验证查询公开群列表返回的关键字段
+3. 验证群业务状态、事件与关键字段
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
       <x:c r="F638" s="24" t="str">
@@ -16955,7 +16945,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C639" s="18" t="str">
-        <x:v>即使 style=1 允许成员邀请，非成员仍不能调用任一邀请 API（参数：inviter-user）</x:v>
+        <x:v>即使 style=1 允许成员邀请，非成员仍不能调用任一邀请 API（参数：添加-成员）</x:v>
       </x:c>
       <x:c r="D639" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -16982,139 +16972,166 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C640" s="18" t="str">
+        <x:v>即使 style=1 允许成员邀请，非成员仍不能调用任一邀请 API（参数：inviter-user）</x:v>
+      </x:c>
+      <x:c r="D640" s="18" t="str">
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+      </x:c>
+      <x:c r="E640" s="18" t="str">
+        <x:v>1. 测试准备：创建测试群并建立业务前置
+2. B 执行群组业务操作
+3. 验证执行群组业务操作返回的错误码与错误文案
+4. 测试后置：销毁测试群并恢复群状态
+验证操作结果、关键字段和相关事件符合预期。</x:v>
+      </x:c>
+      <x:c r="F640" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G640" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="641" ht="120" customHeight="1">
+      <x:c r="A641" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B641" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C641" s="18" t="str">
         <x:v>接受 邀请 从 group 没有待处理邀请</x:v>
       </x:c>
-      <x:c r="D640" s="18" t="str">
+      <x:c r="D641" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备B已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E640" s="18" t="str">
+      <x:c r="E641" s="18" t="str">
         <x:v>1. B 接受入群邀请
 2. 验证接受入群邀请返回的错误码与错误文案
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F640" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G640" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="641" ht="120" customHeight="1">
-      <x:c r="A641" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B641" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C641" s="18" t="str">
+      <x:c r="F641" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G641" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="642" ht="120" customHeight="1">
+      <x:c r="A642" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B642" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C642" s="18" t="str">
         <x:v>接受 join application nonexistent group</x:v>
       </x:c>
-      <x:c r="D641" s="18" t="str">
+      <x:c r="D642" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E641" s="18" t="str">
+      <x:c r="E642" s="18" t="str">
         <x:v>1. A 同意入群申请
 2. 验证同意入群申请返回的错误码与错误文案
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F641" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G641" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="642" ht="120" customHeight="1">
-      <x:c r="A642" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B642" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C642" s="18" t="str">
+      <x:c r="F642" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G642" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="643" ht="120" customHeight="1">
+      <x:c r="A643" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B643" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C643" s="18" t="str">
         <x:v>接受 join application nonexistent user</x:v>
       </x:c>
-      <x:c r="D642" s="18" t="str">
+      <x:c r="D643" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E642" s="18" t="str">
+      <x:c r="E643" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 同意入群申请
 3. 验证同意入群申请返回的错误码与错误文案
 4. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F642" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G642" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="643" ht="120" customHeight="1">
-      <x:c r="A643" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B643" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C643" s="18" t="str">
+      <x:c r="F643" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G643" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="644" ht="120" customHeight="1">
+      <x:c r="A644" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B644" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C644" s="18" t="str">
         <x:v>拒绝 邀请 从 group 没有待处理邀请</x:v>
       </x:c>
-      <x:c r="D643" s="18" t="str">
+      <x:c r="D644" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备B已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E643" s="18" t="str">
+      <x:c r="E644" s="18" t="str">
         <x:v>1. B 拒绝入群邀请
 2. 验证拒绝入群邀请返回的错误码与错误文案
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F643" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G643" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="644" ht="120" customHeight="1">
-      <x:c r="A644" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B644" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C644" s="18" t="str">
+      <x:c r="F644" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G644" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="645" ht="120" customHeight="1">
+      <x:c r="A645" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B645" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C645" s="18" t="str">
         <x:v>拒绝 join application nonexistent group</x:v>
       </x:c>
-      <x:c r="D644" s="18" t="str">
+      <x:c r="D645" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E644" s="18" t="str">
+      <x:c r="E645" s="18" t="str">
         <x:v>1. A 拒绝入群申请
 2. 验证拒绝入群申请返回的错误码与错误文案
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F644" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G644" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="645" ht="120" customHeight="1">
-      <x:c r="A645" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B645" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C645" s="18" t="str">
+      <x:c r="F645" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G645" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="646" ht="120" customHeight="1">
+      <x:c r="A646" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B646" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C646" s="18" t="str">
         <x:v>空申请原因应被服务端规范化，并且 pending 仍可被正常拒绝</x:v>
       </x:c>
-      <x:c r="D645" s="18" t="str">
+      <x:c r="D646" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E645" s="18" t="str">
+      <x:c r="E646" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. B 申请加入公开群
 3. 验证群业务状态、事件与关键字段
@@ -17123,27 +17140,27 @@
 6. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F645" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G645" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="646" ht="120" customHeight="1">
-      <x:c r="A646" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B646" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C646" s="18" t="str">
+      <x:c r="F646" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G646" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="647" ht="120" customHeight="1">
+      <x:c r="A647" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B647" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C647" s="18" t="str">
         <x:v>链路： 1) A 建群并邀请 B 2) B 在群里发父消息 3) A 用父消息创建子区并让 B 加入 4) A 把 B 从子区移除 5) 查询子区成员，断言 A 仍在且 B 已被移除 当前 Android 实测 removeMemberFromChatThread 成功后不派发 onUserKickOutOfChatThread，因此按 SDK 可查询的真实成员状态验收移除结果</x:v>
       </x:c>
-      <x:c r="D646" s="18" t="str">
+      <x:c r="D647" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E646" s="18" t="str">
+      <x:c r="E647" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. B 发送群消息
 3. 验证发送群消息返回的关键字段
@@ -17154,37 +17171,6 @@
 8. A 查询子区成员
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F646" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G646" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="647" ht="120" customHeight="1">
-      <x:c r="A647" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B647" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C647" s="18" t="str">
-        <x:v>普通成员不能处理申请；管理员按原生权限接收并处理申请（参数：成员-接受）</x:v>
-      </x:c>
-      <x:c r="D647" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
-      </x:c>
-      <x:c r="E647" s="18" t="str">
-        <x:v>1. 测试准备：创建测试群并建立业务前置
-2. A 添加群管理员
-3. 验证 添加群管理员返回的关键字段
-4. A 申请加入公开群
-5. 验证群业务状态、事件与关键字段
-6. 等待并校验目标业务事件
-7. B 执行群组业务操作
-8. 验证执行群组业务操作返回的错误码与错误文案
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
       <x:c r="F647" s="24" t="str">
         <x:v>普通</x:v>
       </x:c>
@@ -17200,7 +17186,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C648" s="18" t="str">
-        <x:v>普通成员不能处理申请；管理员按原生权限接收并处理申请（参数：成员-拒绝）</x:v>
+        <x:v>普通成员不能处理申请；管理员按原生权限接收并处理申请（参数：成员-接受）</x:v>
       </x:c>
       <x:c r="D648" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -17231,7 +17217,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C649" s="18" t="str">
-        <x:v>普通成员不能处理申请；管理员按原生权限接收并处理申请（参数：admin-接受）</x:v>
+        <x:v>普通成员不能处理申请；管理员按原生权限接收并处理申请（参数：成员-拒绝）</x:v>
       </x:c>
       <x:c r="D649" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -17262,7 +17248,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C650" s="18" t="str">
-        <x:v>普通成员不能处理申请；管理员按原生权限接收并处理申请（参数：admin-拒绝）</x:v>
+        <x:v>普通成员不能处理申请；管理员按原生权限接收并处理申请（参数：admin-接受）</x:v>
       </x:c>
       <x:c r="D650" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -17293,114 +17279,145 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C651" s="18" t="str">
+        <x:v>普通成员不能处理申请；管理员按原生权限接收并处理申请（参数：admin-拒绝）</x:v>
+      </x:c>
+      <x:c r="D651" s="18" t="str">
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+      </x:c>
+      <x:c r="E651" s="18" t="str">
+        <x:v>1. 测试准备：创建测试群并建立业务前置
+2. A 添加群管理员
+3. 验证 添加群管理员返回的关键字段
+4. A 申请加入公开群
+5. 验证群业务状态、事件与关键字段
+6. 等待并校验目标业务事件
+7. B 执行群组业务操作
+8. 验证执行群组业务操作返回的错误码与错误文案
+验证操作结果、关键字段和相关事件符合预期。</x:v>
+      </x:c>
+      <x:c r="F651" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G651" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="652" ht="120" customHeight="1">
+      <x:c r="A652" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B652" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C652" s="18" t="str">
         <x:v>前置：使用固定不存在的 groupId 和 fileId</x:v>
       </x:c>
-      <x:c r="D651" s="18" t="str">
+      <x:c r="D652" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E651" s="18" t="str">
+      <x:c r="E652" s="18" t="str">
         <x:v>1. A 执行群组业务操作
 2. 验证执行群组业务操作返回的错误码与错误文案
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F651" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G651" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="652" ht="120" customHeight="1">
-      <x:c r="A652" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B652" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C652" s="18" t="str">
+      <x:c r="F652" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G652" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="653" ht="120" customHeight="1">
+      <x:c r="A653" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B653" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C653" s="18" t="str">
         <x:v>前置：使用固定不存在的 groupId 和显式 Android 不可读路径</x:v>
       </x:c>
-      <x:c r="D652" s="18" t="str">
+      <x:c r="D653" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E652" s="18" t="str">
+      <x:c r="E653" s="18" t="str">
         <x:v>1. A 上传群共享文件
 2. 验证 上传群共享文件返回的错误码与错误文案
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F652" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G652" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="653" ht="120" customHeight="1">
-      <x:c r="A653" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B653" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C653" s="18" t="str">
+      <x:c r="F653" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G653" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="654" ht="120" customHeight="1">
+      <x:c r="A654" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B654" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C654" s="18" t="str">
         <x:v>前置：使用固定不存在的 groupId/fileId 和宿主机保存路径</x:v>
       </x:c>
-      <x:c r="D653" s="18" t="str">
+      <x:c r="D654" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E653" s="18" t="str">
+      <x:c r="E654" s="18" t="str">
         <x:v>1. A 下载群共享文件
 2. 验证 下载群共享文件返回的关键字段
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F653" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G653" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="654" ht="120" customHeight="1">
-      <x:c r="A654" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B654" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C654" s="18" t="str">
+      <x:c r="F654" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G654" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="655" ht="120" customHeight="1">
+      <x:c r="A655" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B655" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C655" s="18" t="str">
         <x:v>前置：A 为群主，显式设备路径在 Android 中不存在</x:v>
       </x:c>
-      <x:c r="D654" s="18" t="str">
+      <x:c r="D655" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E654" s="18" t="str">
+      <x:c r="E655" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 上传群共享文件
 3. 验证 上传群共享文件返回的错误码与错误文案
 4. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F654" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G654" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="655" ht="120" customHeight="1">
-      <x:c r="A655" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B655" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C655" s="18" t="str">
+      <x:c r="F655" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G655" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="656" ht="120" customHeight="1">
+      <x:c r="A656" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B656" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C656" s="18" t="str">
         <x:v>前置：A 为群主，B 初始不是目标群成员，B 的自动接受邀请开关为 true</x:v>
       </x:c>
-      <x:c r="D655" s="18" t="str">
+      <x:c r="D656" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E655" s="18" t="str">
+      <x:c r="E656" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. 等待并校验目标业务事件
 3. 验证群业务状态、事件与关键字段
@@ -17411,105 +17428,105 @@
 8. 验证 添加群成员返回的关键字段
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F655" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G655" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="656" ht="120" customHeight="1">
-      <x:c r="A656" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B656" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C656" s="18" t="str">
+      <x:c r="F656" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G656" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="657" ht="120" customHeight="1">
+      <x:c r="A657" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B657" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C657" s="18" t="str">
         <x:v>前置：A 为群主；传入的 `/private/tmp/...` 是 macOS 宿主机路径，不存在于 Android</x:v>
       </x:c>
-      <x:c r="D656" s="18" t="str">
+      <x:c r="D657" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E656" s="18" t="str">
+      <x:c r="E657" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 上传群共享文件
 3. 验证 上传群共享文件返回的错误码与错误文案
 4. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F656" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G656" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="657" ht="120" customHeight="1">
-      <x:c r="A657" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B657" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C657" s="18" t="str">
+      <x:c r="F657" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G657" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="658" ht="120" customHeight="1">
+      <x:c r="A658" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B658" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C658" s="18" t="str">
         <x:v>前置：A 已登录，当前账号可能已加入零个或多个共享环境群组</x:v>
       </x:c>
-      <x:c r="D657" s="18" t="str">
+      <x:c r="D658" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E657" s="18" t="str">
+      <x:c r="E658" s="18" t="str">
         <x:v>1. A 查询已加入群数量
 2. 验证查询已加入群数量返回的关键字段
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F657" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G657" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="658" ht="120" customHeight="1">
-      <x:c r="A658" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B658" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C658" s="18" t="str">
+      <x:c r="F658" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G658" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="659" ht="120" customHeight="1">
+      <x:c r="A659" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B659" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C659" s="18" t="str">
         <x:v>前置：A 已登录，公开群列表允许包含共享环境已有数据</x:v>
       </x:c>
-      <x:c r="D658" s="18" t="str">
+      <x:c r="D659" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E658" s="18" t="str">
+      <x:c r="E659" s="18" t="str">
         <x:v>1. A 查询公开群列表
 2. 验证查询公开群列表返回的关键字段
 3. 验证群业务状态、事件与关键字段
 5.0 说明：移除服务端拉公开群（getPublicGroupsFromServer 残留，无公开群列表）</x:v>
       </x:c>
-      <x:c r="F658" s="25" t="str">
+      <x:c r="F659" s="25" t="str">
         <x:v>5.0 不可用</x:v>
       </x:c>
-      <x:c r="G658" t="str">
+      <x:c r="G659" t="str">
         <x:v>5.0 不可用</x:v>
       </x:c>
     </x:row>
-    <x:row r="659" ht="120" customHeight="1">
-      <x:c r="A659" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B659" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C659" s="18" t="str">
+    <x:row r="660" ht="120" customHeight="1">
+      <x:c r="A660" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B660" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C660" s="18" t="str">
         <x:v>前置：A 已登录；测试依次创建两个名称唯一的 PublicOpenJoin（style=3）公开群</x:v>
       </x:c>
-      <x:c r="D659" s="18" t="str">
+      <x:c r="D660" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E659" s="18" t="str">
+      <x:c r="E660" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 查询公开群列表
 3. 验证查询公开群列表返回的关键字段
@@ -17517,38 +17534,11 @@
 5. 测试后置：销毁测试群并恢复群状态
 5.0 说明：移除服务端拉公开群（getPublicGroupsFromServer 残留，无公开群列表）</x:v>
       </x:c>
-      <x:c r="F659" s="25" t="str">
+      <x:c r="F660" s="25" t="str">
         <x:v>5.0 不可用</x:v>
       </x:c>
-      <x:c r="G659" t="str">
+      <x:c r="G660" t="str">
         <x:v>5.0 不可用</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="660" ht="120" customHeight="1">
-      <x:c r="A660" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B660" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C660" s="18" t="str">
-        <x:v>前置：A 已登录且尚未创建本 case 的目标群</x:v>
-      </x:c>
-      <x:c r="D660" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
-      </x:c>
-      <x:c r="E660" s="18" t="str">
-        <x:v>1. 测试准备：创建测试群并建立业务前置
-2. A 查询本地已加入群列表
-3. 验证查询本地已加入群列表返回的关键字段
-4. 测试后置：销毁测试群并恢复群状态
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
-      <x:c r="F660" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G660" t="str">
-        <x:v>普通</x:v>
       </x:c>
     </x:row>
     <x:row r="661" ht="120" customHeight="1">
@@ -17586,49 +17576,45 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C662" s="18" t="str">
+        <x:v>前置：A 已登录且尚未创建本 case 的目标群</x:v>
+      </x:c>
+      <x:c r="D662" s="18" t="str">
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+      </x:c>
+      <x:c r="E662" s="18" t="str">
+        <x:v>1. 测试准备：创建测试群并建立业务前置
+2. A 查询本地已加入群列表
+3. 验证查询本地已加入群列表返回的关键字段
+4. 测试后置：销毁测试群并恢复群状态
+验证操作结果、关键字段和相关事件符合预期。</x:v>
+      </x:c>
+      <x:c r="F662" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G662" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="663" ht="120" customHeight="1">
+      <x:c r="A663" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B663" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C663" s="18" t="str">
         <x:v>前置：A/B 已登录，A 创建 PrivateMemberCanInvite（style=1）私有群，B 不是成员</x:v>
       </x:c>
-      <x:c r="D662" s="18" t="str">
+      <x:c r="D663" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E662" s="18" t="str">
+      <x:c r="E663" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. B 加入公开群
 3. 验证加入公开群返回的错误码与错误文案
 4. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F662" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G662" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="663" ht="120" customHeight="1">
-      <x:c r="A663" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B663" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C663" s="18" t="str">
-        <x:v>群主/管理员可禁言与解除禁言；普通成员被拒绝且状态不变（参数：成员）</x:v>
-      </x:c>
-      <x:c r="D663" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
-      </x:c>
-      <x:c r="E663" s="18" t="str">
-        <x:v>1. 测试准备：创建测试群并建立成员前置
-2. 动作端 禁言成员
-3. 验证解除成员禁言返回的错误码与错误文案
-4. 验证 禁言成员返回的关键字段
-5. 等待并校验目标业务事件
-6. 验证群业务状态、事件与关键字段
-7. 动作端 解除成员禁言
-8. 验证解除成员禁言返回的关键字段
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
       <x:c r="F663" s="24" t="str">
         <x:v>普通</x:v>
       </x:c>
@@ -17644,7 +17630,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C664" s="18" t="str">
-        <x:v>群主/管理员可禁言与解除禁言；普通成员被拒绝且状态不变（参数：admin）</x:v>
+        <x:v>群主/管理员可禁言与解除禁言；普通成员被拒绝且状态不变（参数：成员）</x:v>
       </x:c>
       <x:c r="D664" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -17675,7 +17661,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C665" s="18" t="str">
-        <x:v>群主/管理员可禁言与解除禁言；普通成员被拒绝且状态不变（参数：owner）</x:v>
+        <x:v>群主/管理员可禁言与解除禁言；普通成员被拒绝且状态不变（参数：admin）</x:v>
       </x:c>
       <x:c r="D665" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -17706,20 +17692,20 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C666" s="18" t="str">
-        <x:v>群主/管理员可切换全员禁言；普通成员被拒绝且状态不变（参数：成员）</x:v>
+        <x:v>群主/管理员可禁言与解除禁言；普通成员被拒绝且状态不变（参数：owner）</x:v>
       </x:c>
       <x:c r="D666" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E666" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立成员前置
-2. 动作端 全员禁言
-3. 验证解除全员禁言返回的错误码与错误文案
-4. 验证 全员禁言返回的关键字段
+2. 动作端 禁言成员
+3. 验证解除成员禁言返回的错误码与错误文案
+4. 验证 禁言成员返回的关键字段
 5. 等待并校验目标业务事件
 6. 验证群业务状态、事件与关键字段
-7. 动作端 解除全员禁言
-8. 验证解除全员禁言返回的关键字段
+7. 动作端 解除成员禁言
+8. 验证解除成员禁言返回的关键字段
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
       <x:c r="F666" s="24" t="str">
@@ -17737,7 +17723,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C667" s="18" t="str">
-        <x:v>群主/管理员可切换全员禁言；普通成员被拒绝且状态不变（参数：admin）</x:v>
+        <x:v>群主/管理员可切换全员禁言；普通成员被拒绝且状态不变（参数：成员）</x:v>
       </x:c>
       <x:c r="D667" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -17768,7 +17754,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C668" s="18" t="str">
-        <x:v>群主/管理员可切换全员禁言；普通成员被拒绝且状态不变（参数：owner）</x:v>
+        <x:v>群主/管理员可切换全员禁言；普通成员被拒绝且状态不变（参数：admin）</x:v>
       </x:c>
       <x:c r="D668" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -17799,20 +17785,20 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C669" s="18" t="str">
-        <x:v>群主/管理员可增删白名单；普通成员被拒绝且白名单保持为空（参数：成员）</x:v>
+        <x:v>群主/管理员可切换全员禁言；普通成员被拒绝且状态不变（参数：owner）</x:v>
       </x:c>
       <x:c r="D669" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E669" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立成员前置
-2. 动作端 加入群白名单
-3. 验证移出群白名单返回的错误码与错误文案
-4. 验证群业务状态、事件与关键字段
+2. 动作端 全员禁言
+3. 验证解除全员禁言返回的错误码与错误文案
+4. 验证 全员禁言返回的关键字段
 5. 等待并校验目标业务事件
-6. 动作端 查询白名单成员状态
-7. 动作端 移出群白名单
-8. 测试后置：销毁测试群并恢复群状态
+6. 验证群业务状态、事件与关键字段
+7. 动作端 解除全员禁言
+8. 验证解除全员禁言返回的关键字段
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
       <x:c r="F669" s="24" t="str">
@@ -17830,7 +17816,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C670" s="18" t="str">
-        <x:v>群主/管理员可增删白名单；普通成员被拒绝且白名单保持为空（参数：admin）</x:v>
+        <x:v>群主/管理员可增删白名单；普通成员被拒绝且白名单保持为空（参数：成员）</x:v>
       </x:c>
       <x:c r="D670" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -17861,7 +17847,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C671" s="18" t="str">
-        <x:v>群主/管理员可增删白名单；普通成员被拒绝且白名单保持为空（参数：owner）</x:v>
+        <x:v>群主/管理员可增删白名单；普通成员被拒绝且白名单保持为空（参数：admin）</x:v>
       </x:c>
       <x:c r="D671" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -17892,12 +17878,43 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C672" s="18" t="str">
-        <x:v>删除 成员 属性 成功</x:v>
+        <x:v>群主/管理员可增删白名单；普通成员被拒绝且白名单保持为空（参数：owner）</x:v>
       </x:c>
       <x:c r="D672" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E672" s="18" t="str">
+        <x:v>1. 测试准备：创建测试群并建立成员前置
+2. 动作端 加入群白名单
+3. 验证移出群白名单返回的错误码与错误文案
+4. 验证群业务状态、事件与关键字段
+5. 等待并校验目标业务事件
+6. 动作端 查询白名单成员状态
+7. 动作端 移出群白名单
+8. 测试后置：销毁测试群并恢复群状态
+验证操作结果、关键字段和相关事件符合预期。</x:v>
+      </x:c>
+      <x:c r="F672" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G672" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="673" ht="120" customHeight="1">
+      <x:c r="A673" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B673" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C673" s="18" t="str">
+        <x:v>删除 成员 属性 成功</x:v>
+      </x:c>
+      <x:c r="D673" s="18" t="str">
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+      </x:c>
+      <x:c r="E673" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. B 执行群组业务操作
 3. 验证执行群组业务操作返回的响应 result 与关键字段
@@ -17908,297 +17925,268 @@
 8. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F672" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G672" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="673" ht="120" customHeight="1">
-      <x:c r="A673" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B673" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C673" s="18" t="str">
+      <x:c r="F673" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G673" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="674" ht="120" customHeight="1">
+      <x:c r="A674" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B674" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C674" s="18" t="str">
         <x:v>删除 成员 属性 空 keys</x:v>
       </x:c>
-      <x:c r="D673" s="18" t="str">
+      <x:c r="D674" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E673" s="18" t="str">
+      <x:c r="E674" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 删除成员属性
 3. 验证删除成员属性返回的错误码与错误文案
 4. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F673" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G673" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="674" ht="120" customHeight="1">
-      <x:c r="A674" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B674" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C674" s="18" t="str">
+      <x:c r="F674" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G674" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="675" ht="120" customHeight="1">
+      <x:c r="A675" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B675" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C675" s="18" t="str">
         <x:v>删除 成员 属性 nonexistent group</x:v>
       </x:c>
-      <x:c r="D674" s="18" t="str">
+      <x:c r="D675" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E674" s="18" t="str">
+      <x:c r="E675" s="18" t="str">
         <x:v>1. A 删除成员属性
 2. 验证删除成员属性返回的关键字段
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F674" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G674" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="675" ht="120" customHeight="1">
-      <x:c r="A675" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B675" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C675" s="18" t="str">
+      <x:c r="F675" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G675" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="676" ht="120" customHeight="1">
+      <x:c r="A676" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B676" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C676" s="18" t="str">
         <x:v>删除 成员 属性 nonexistent key</x:v>
       </x:c>
-      <x:c r="D675" s="18" t="str">
+      <x:c r="D676" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E675" s="18" t="str">
+      <x:c r="E676" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 删除成员属性
 3. 验证删除成员属性返回的关键字段
 4. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F675" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G675" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="676" ht="120" customHeight="1">
-      <x:c r="A676" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B676" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C676" s="18" t="str">
+      <x:c r="F676" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G676" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="677" ht="120" customHeight="1">
+      <x:c r="A677" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B677" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C677" s="18" t="str">
         <x:v>删除 成员 non 成员</x:v>
       </x:c>
-      <x:c r="D676" s="18" t="str">
+      <x:c r="D677" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E676" s="18" t="str">
+      <x:c r="E677" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 移除群成员
 3. 验证 移除群成员返回的错误码与错误文案
 4. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F676" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G676" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="677" ht="120" customHeight="1">
-      <x:c r="A677" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B677" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C677" s="18" t="str">
+      <x:c r="F677" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G677" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="678" ht="120" customHeight="1">
+      <x:c r="A678" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B678" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C678" s="18" t="str">
         <x:v>删除 admin nonexistent group</x:v>
       </x:c>
-      <x:c r="D677" s="18" t="str">
+      <x:c r="D678" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E677" s="18" t="str">
+      <x:c r="E678" s="18" t="str">
         <x:v>1. A 移除群管理员
 2. 验证 移除群管理员返回的错误码与错误文案
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F677" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G677" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="678" ht="120" customHeight="1">
-      <x:c r="A678" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B678" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C678" s="18" t="str">
+      <x:c r="F678" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G678" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="679" ht="120" customHeight="1">
+      <x:c r="A679" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B679" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C679" s="18" t="str">
         <x:v>添加 成员 空 成员</x:v>
       </x:c>
-      <x:c r="D678" s="18" t="str">
+      <x:c r="D679" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E678" s="18" t="str">
+      <x:c r="E679" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 添加群成员
 3. 验证 添加群成员返回的关键字段
 4. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F678" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G678" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="679" ht="120" customHeight="1">
-      <x:c r="A679" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B679" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C679" s="18" t="str">
+      <x:c r="F679" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G679" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="680" ht="120" customHeight="1">
+      <x:c r="A680" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B680" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C680" s="18" t="str">
         <x:v>添加 成员 nonexistent group</x:v>
       </x:c>
-      <x:c r="D679" s="18" t="str">
+      <x:c r="D680" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E679" s="18" t="str">
+      <x:c r="E680" s="18" t="str">
         <x:v>1. A 添加群成员
 2. 验证 添加群成员返回的错误码与错误文案
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F679" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G679" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="680" ht="120" customHeight="1">
-      <x:c r="A680" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B680" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C680" s="18" t="str">
+      <x:c r="F680" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G680" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="681" ht="120" customHeight="1">
+      <x:c r="A681" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B681" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C681" s="18" t="str">
         <x:v>添加 成员 nonexistent user</x:v>
       </x:c>
-      <x:c r="D680" s="18" t="str">
+      <x:c r="D681" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E680" s="18" t="str">
+      <x:c r="E681" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 添加群成员
 3. 验证 添加群成员返回的错误码与错误文案
 4. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F680" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G680" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="681" ht="120" customHeight="1">
-      <x:c r="A681" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B681" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C681" s="18" t="str">
+      <x:c r="F681" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G681" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="682" ht="120" customHeight="1">
+      <x:c r="A682" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B682" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C682" s="18" t="str">
         <x:v>添加 admin non 成员</x:v>
       </x:c>
-      <x:c r="D681" s="18" t="str">
+      <x:c r="D682" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E681" s="18" t="str">
+      <x:c r="E682" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 添加群管理员
 3. 验证 添加群管理员返回的错误码与错误文案
 4. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F681" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G681" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="682" ht="120" customHeight="1">
-      <x:c r="A682" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B682" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C682" s="18" t="str">
+      <x:c r="F682" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G682" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="683" ht="120" customHeight="1">
+      <x:c r="A683" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B683" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C683" s="18" t="str">
         <x:v>添加 admin nonexistent group</x:v>
       </x:c>
-      <x:c r="D682" s="18" t="str">
+      <x:c r="D683" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E682" s="18" t="str">
+      <x:c r="E683" s="18" t="str">
         <x:v>1. A 添加群管理员
 2. 验证 添加群管理员返回的错误码与错误文案
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F682" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G682" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="683" ht="120" customHeight="1">
-      <x:c r="A683" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B683" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C683" s="18" t="str">
-        <x:v>通用 inviterUser API 应覆盖 style=1/2/3 的群主邀请链路（参数：private-成员-添加-成员）</x:v>
-      </x:c>
-      <x:c r="D683" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
-      </x:c>
-      <x:c r="E683" s="18" t="str">
-        <x:v>1. 测试准备：创建测试群并建立业务前置
-2. A 执行群组业务操作
-3. 验证群业务状态、事件与关键字段
-4. 等待并校验目标业务事件
-5. 验证执行群组业务操作返回的响应 result 与关键字段
-6. 测试后置：销毁测试群并恢复群状态
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
       <x:c r="F683" s="24" t="str">
         <x:v>普通</x:v>
       </x:c>
@@ -18214,7 +18202,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C684" s="18" t="str">
-        <x:v>通用 inviterUser API 应覆盖 style=1/2/3 的群主邀请链路（参数：private-成员-inviter-user）</x:v>
+        <x:v>通用 inviterUser API 应覆盖 style=1/2/3 的群主邀请链路（参数：private-成员-添加-成员）</x:v>
       </x:c>
       <x:c r="D684" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -18243,7 +18231,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C685" s="18" t="str">
-        <x:v>通用 inviterUser API 应覆盖 style=1/2/3 的群主邀请链路（参数：public-approval-添加-成员）</x:v>
+        <x:v>通用 inviterUser API 应覆盖 style=1/2/3 的群主邀请链路（参数：private-成员-inviter-user）</x:v>
       </x:c>
       <x:c r="D685" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -18272,7 +18260,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C686" s="18" t="str">
-        <x:v>通用 inviterUser API 应覆盖 style=1/2/3 的群主邀请链路（参数：public-approval-inviter-user）</x:v>
+        <x:v>通用 inviterUser API 应覆盖 style=1/2/3 的群主邀请链路（参数：public-approval-添加-成员）</x:v>
       </x:c>
       <x:c r="D686" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -18301,7 +18289,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C687" s="18" t="str">
-        <x:v>通用 inviterUser API 应覆盖 style=1/2/3 的群主邀请链路（参数：public-open-添加-成员）</x:v>
+        <x:v>通用 inviterUser API 应覆盖 style=1/2/3 的群主邀请链路（参数：public-approval-inviter-user）</x:v>
       </x:c>
       <x:c r="D687" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -18330,7 +18318,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C688" s="18" t="str">
-        <x:v>通用 inviterUser API 应覆盖 style=1/2/3 的群主邀请链路（参数：public-open-inviter-user）</x:v>
+        <x:v>通用 inviterUser API 应覆盖 style=1/2/3 的群主邀请链路（参数：public-open-添加-成员）</x:v>
       </x:c>
       <x:c r="D688" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -18359,12 +18347,41 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C689" s="18" t="str">
-        <x:v>同一用户重复申请时，两次通知可见，但只保留一个可处理的 pending</x:v>
+        <x:v>通用 inviterUser API 应覆盖 style=1/2/3 的群主邀请链路（参数：public-open-inviter-user）</x:v>
       </x:c>
       <x:c r="D689" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E689" s="18" t="str">
+        <x:v>1. 测试准备：创建测试群并建立业务前置
+2. A 执行群组业务操作
+3. 验证群业务状态、事件与关键字段
+4. 等待并校验目标业务事件
+5. 验证执行群组业务操作返回的响应 result 与关键字段
+6. 测试后置：销毁测试群并恢复群状态
+验证操作结果、关键字段和相关事件符合预期。</x:v>
+      </x:c>
+      <x:c r="F689" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G689" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="690" ht="120" customHeight="1">
+      <x:c r="A690" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B690" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C690" s="18" t="str">
+        <x:v>同一用户重复申请时，两次通知可见，但只保留一个可处理的 pending</x:v>
+      </x:c>
+      <x:c r="D690" s="18" t="str">
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+      </x:c>
+      <x:c r="E690" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 拒绝入群申请
 3. 验证群业务状态、事件与关键字段
@@ -18372,27 +18389,27 @@
 5. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F689" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G689" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="690" ht="120" customHeight="1">
-      <x:c r="A690" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B690" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C690" s="18" t="str">
+      <x:c r="F690" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G690" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="691" ht="120" customHeight="1">
+      <x:c r="A691" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B691" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C691" s="18" t="str">
         <x:v>校验新事件名： - onMembersJoinedFromGroup - onMembersExitedFromGroup</x:v>
       </x:c>
-      <x:c r="D690" s="18" t="str">
+      <x:c r="D691" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E690" s="18" t="str">
+      <x:c r="E691" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 添加群成员
 3. 验证 添加群成员返回的关键字段
@@ -18402,36 +18419,6 @@
 7. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F690" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G690" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="691" ht="120" customHeight="1">
-      <x:c r="A691" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B691" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C691" s="18" t="str">
-        <x:v>邀请首次处理后 pending 消失，重复或反向处理应失败且不改变首次结果（参数：接受-then-拒绝）</x:v>
-      </x:c>
-      <x:c r="D691" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
-      </x:c>
-      <x:c r="E691" s="18" t="str">
-        <x:v>1. 测试准备：创建测试群并建立成员前置
-2. B 执行群组业务操作
-3. 验证执行群组业务操作返回的响应 result 与关键字段
-4. 等待并校验目标业务事件
-5. 验证群业务状态、事件与关键字段
-6. 验证执行群组业务操作返回的错误码与错误文案
-7. 测试后置：销毁测试群并恢复群状态
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
       <x:c r="F691" s="24" t="str">
         <x:v>普通</x:v>
       </x:c>
@@ -18447,7 +18434,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C692" s="18" t="str">
-        <x:v>邀请首次处理后 pending 消失，重复或反向处理应失败且不改变首次结果（参数：接受-twice）</x:v>
+        <x:v>邀请首次处理后 pending 消失，重复或反向处理应失败且不改变首次结果（参数：接受-then-拒绝）</x:v>
       </x:c>
       <x:c r="D692" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -18477,7 +18464,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C693" s="18" t="str">
-        <x:v>邀请首次处理后 pending 消失，重复或反向处理应失败且不改变首次结果（参数：拒绝-then-接受）</x:v>
+        <x:v>邀请首次处理后 pending 消失，重复或反向处理应失败且不改变首次结果（参数：接受-twice）</x:v>
       </x:c>
       <x:c r="D693" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -18507,7 +18494,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C694" s="18" t="str">
-        <x:v>邀请首次处理后 pending 消失，重复或反向处理应失败且不改变首次结果（参数：拒绝-twice）</x:v>
+        <x:v>邀请首次处理后 pending 消失，重复或反向处理应失败且不改变首次结果（参数：拒绝-then-接受）</x:v>
       </x:c>
       <x:c r="D694" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -18537,18 +18524,19 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C695" s="18" t="str">
-        <x:v>一个 pending 申请只能处理一次，重复或反向处理不得改变首次结果（参数：接受-then-拒绝）</x:v>
+        <x:v>邀请首次处理后 pending 消失，重复或反向处理应失败且不改变首次结果（参数：拒绝-twice）</x:v>
       </x:c>
       <x:c r="D695" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E695" s="18" t="str">
-        <x:v>1. 测试准备：创建测试群并建立业务前置
-2. A 执行群组业务操作
-3. 验证群业务状态、事件与关键字段
+        <x:v>1. 测试准备：创建测试群并建立成员前置
+2. B 执行群组业务操作
+3. 验证执行群组业务操作返回的响应 result 与关键字段
 4. 等待并校验目标业务事件
-5. 验证执行群组业务操作返回的错误码与错误文案
-6. 测试后置：销毁测试群并恢复群状态
+5. 验证群业务状态、事件与关键字段
+6. 验证执行群组业务操作返回的错误码与错误文案
+7. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
       <x:c r="F695" s="24" t="str">
@@ -18566,7 +18554,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C696" s="18" t="str">
-        <x:v>一个 pending 申请只能处理一次，重复或反向处理不得改变首次结果（参数：接受-twice）</x:v>
+        <x:v>一个 pending 申请只能处理一次，重复或反向处理不得改变首次结果（参数：接受-then-拒绝）</x:v>
       </x:c>
       <x:c r="D696" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -18595,7 +18583,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C697" s="18" t="str">
-        <x:v>一个 pending 申请只能处理一次，重复或反向处理不得改变首次结果（参数：拒绝-then-接受）</x:v>
+        <x:v>一个 pending 申请只能处理一次，重复或反向处理不得改变首次结果（参数：接受-twice）</x:v>
       </x:c>
       <x:c r="D697" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -18624,7 +18612,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C698" s="18" t="str">
-        <x:v>一个 pending 申请只能处理一次，重复或反向处理不得改变首次结果（参数：拒绝-twice）</x:v>
+        <x:v>一个 pending 申请只能处理一次，重复或反向处理不得改变首次结果（参数：拒绝-then-接受）</x:v>
       </x:c>
       <x:c r="D698" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -18653,16 +18641,18 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C699" s="18" t="str">
-        <x:v>有效群中没有待处理邀请时，接受和拒绝都返回稳定错误（参数：接受）</x:v>
+        <x:v>一个 pending 申请只能处理一次，重复或反向处理不得改变首次结果（参数：拒绝-twice）</x:v>
       </x:c>
       <x:c r="D699" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E699" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
-2. B 执行群组业务操作
-3. 验证执行群组业务操作返回的错误码与错误文案
-4. 测试后置：销毁测试群并恢复群状态
+2. A 执行群组业务操作
+3. 验证群业务状态、事件与关键字段
+4. 等待并校验目标业务事件
+5. 验证执行群组业务操作返回的错误码与错误文案
+6. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
       <x:c r="F699" s="24" t="str">
@@ -18680,7 +18670,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C700" s="18" t="str">
-        <x:v>有效群中没有待处理邀请时，接受和拒绝都返回稳定错误（参数：拒绝）</x:v>
+        <x:v>有效群中没有待处理邀请时，接受和拒绝都返回稳定错误（参数：接受）</x:v>
       </x:c>
       <x:c r="D700" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -18707,14 +18697,14 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C701" s="18" t="str">
-        <x:v>有效审批群中不存在 pending 申请时，同意和拒绝都应返回稳定错误（参数：接受）</x:v>
+        <x:v>有效群中没有待处理邀请时，接受和拒绝都返回稳定错误（参数：拒绝）</x:v>
       </x:c>
       <x:c r="D701" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E701" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
-2. A 执行群组业务操作
+2. B 执行群组业务操作
 3. 验证执行群组业务操作返回的错误码与错误文案
 4. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
@@ -18734,7 +18724,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C702" s="18" t="str">
-        <x:v>有效审批群中不存在 pending 申请时，同意和拒绝都应返回稳定错误（参数：拒绝）</x:v>
+        <x:v>有效审批群中不存在 pending 申请时，同意和拒绝都应返回稳定错误（参数：接受）</x:v>
       </x:c>
       <x:c r="D702" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -18761,13 +18751,16 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C703" s="18" t="str">
-        <x:v>A 向空或不存在 groupId 发送群文本时应失败，B 不得收到目标消息（参数：空）</x:v>
+        <x:v>有效审批群中不存在 pending 申请时，同意和拒绝都应返回稳定错误（参数：拒绝）</x:v>
       </x:c>
       <x:c r="D703" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E703" s="18" t="str">
-        <x:v>1. A 向 群目标发送文本并验证失败终态
+        <x:v>1. 测试准备：创建测试群并建立业务前置
+2. A 执行群组业务操作
+3. 验证执行群组业务操作返回的错误码与错误文案
+4. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
       <x:c r="F703" s="24" t="str">
@@ -18785,7 +18778,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C704" s="18" t="str">
-        <x:v>A 向空或不存在 groupId 发送群文本时应失败，B 不得收到目标消息（参数：nonexistent）</x:v>
+        <x:v>A 向空或不存在 groupId 发送群文本时应失败，B 不得收到目标消息（参数：空）</x:v>
       </x:c>
       <x:c r="D704" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -18809,12 +18802,36 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C705" s="18" t="str">
-        <x:v>B 被移入群黑名单并移出后，不得通过 PublicOpenJoin 重新加入</x:v>
+        <x:v>A 向空或不存在 groupId 发送群文本时应失败，B 不得收到目标消息（参数：nonexistent）</x:v>
       </x:c>
       <x:c r="D705" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E705" s="18" t="str">
+        <x:v>1. A 向 群目标发送文本并验证失败终态
+验证操作结果、关键字段和相关事件符合预期。</x:v>
+      </x:c>
+      <x:c r="F705" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G705" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="706" ht="120" customHeight="1">
+      <x:c r="A706" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B706" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C706" s="18" t="str">
+        <x:v>B 被移入群黑名单并移出后，不得通过 PublicOpenJoin 重新加入</x:v>
+      </x:c>
+      <x:c r="D706" s="18" t="str">
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+      </x:c>
+      <x:c r="E706" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 加入群黑名单
 3. 验证加入群黑名单返回的关键字段
@@ -18825,27 +18842,27 @@
 8. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F705" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G705" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="706" ht="120" customHeight="1">
-      <x:c r="A706" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B706" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C706" s="18" t="str">
+      <x:c r="F706" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G706" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="707" ht="120" customHeight="1">
+      <x:c r="A707" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B707" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C707" s="18" t="str">
         <x:v>B 成功加入 PublicOpenJoin 后再次 join，不得重复增加成员或重复发送加入事件</x:v>
       </x:c>
-      <x:c r="D706" s="18" t="str">
+      <x:c r="D707" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E706" s="18" t="str">
+      <x:c r="E707" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. B 加入公开群
 3. 验证群业务状态、事件与关键字段
@@ -18855,37 +18872,6 @@
 7. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F706" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G706" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="707" ht="120" customHeight="1">
-      <x:c r="A707" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B707" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C707" s="18" t="str">
-        <x:v>B 从未入群、主动退出或被移除后发送群文本均应失败，群主 A 不得收到消息（参数：left）</x:v>
-      </x:c>
-      <x:c r="D707" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
-      </x:c>
-      <x:c r="E707" s="18" t="str">
-        <x:v>1. 测试准备：创建测试群并建立业务前置
-2. B 退出群
-3. 验证退出群返回的关键字段
-4. 验证群业务状态、事件与关键字段
-5. A 移除群成员
-6. 验证 移除群成员返回的关键字段
-7. 等待并校验目标业务事件
-8. A 查询服务端群详情
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
       <x:c r="F707" s="24" t="str">
         <x:v>普通</x:v>
       </x:c>
@@ -18901,7 +18887,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C708" s="18" t="str">
-        <x:v>B 从未入群、主动退出或被移除后发送群文本均应失败，群主 A 不得收到消息（参数：never-成员）</x:v>
+        <x:v>B 从未入群、主动退出或被移除后发送群文本均应失败，群主 A 不得收到消息（参数：left）</x:v>
       </x:c>
       <x:c r="D708" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -18932,7 +18918,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C709" s="18" t="str">
-        <x:v>B 从未入群、主动退出或被移除后发送群文本均应失败，群主 A 不得收到消息（参数：removed）</x:v>
+        <x:v>B 从未入群、主动退出或被移除后发送群文本均应失败，群主 A 不得收到消息（参数：never-成员）</x:v>
       </x:c>
       <x:c r="D709" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -18963,12 +18949,43 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C710" s="18" t="str">
+        <x:v>B 从未入群、主动退出或被移除后发送群文本均应失败，群主 A 不得收到消息（参数：removed）</x:v>
+      </x:c>
+      <x:c r="D710" s="18" t="str">
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+      </x:c>
+      <x:c r="E710" s="18" t="str">
+        <x:v>1. 测试准备：创建测试群并建立业务前置
+2. B 退出群
+3. 验证退出群返回的关键字段
+4. 验证群业务状态、事件与关键字段
+5. A 移除群成员
+6. 验证 移除群成员返回的关键字段
+7. 等待并校验目标业务事件
+8. A 查询服务端群详情
+验证操作结果、关键字段和相关事件符合预期。</x:v>
+      </x:c>
+      <x:c r="F710" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G710" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="711" ht="120" customHeight="1">
+      <x:c r="A711" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B711" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C711" s="18" t="str">
         <x:v>block idempotent</x:v>
       </x:c>
-      <x:c r="D710" s="18" t="str">
+      <x:c r="D711" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E710" s="18" t="str">
+      <x:c r="E711" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 屏蔽群消息
 3. 验证屏蔽群消息返回的关键字段
@@ -18976,52 +18993,52 @@
 5. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F710" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G710" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="711" ht="120" customHeight="1">
-      <x:c r="A711" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B711" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C711" s="18" t="str">
+      <x:c r="F711" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G711" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="712" ht="120" customHeight="1">
+      <x:c r="A712" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B712" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C712" s="18" t="str">
         <x:v>block nonexistent group</x:v>
       </x:c>
-      <x:c r="D711" s="18" t="str">
+      <x:c r="D712" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E711" s="18" t="str">
+      <x:c r="E712" s="18" t="str">
         <x:v>1. A 屏蔽群消息
 2. 验证屏蔽群消息返回的错误码与错误文案
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F711" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G711" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="712" ht="120" customHeight="1">
-      <x:c r="A712" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B712" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C712" s="18" t="str">
+      <x:c r="F712" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G712" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="713" ht="120" customHeight="1">
+      <x:c r="A713" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B713" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C713" s="18" t="str">
         <x:v>block then unblock 成功</x:v>
       </x:c>
-      <x:c r="D712" s="18" t="str">
+      <x:c r="D713" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E712" s="18" t="str">
+      <x:c r="E713" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 屏蔽群消息
 3. 验证屏蔽群消息返回的关键字段
@@ -19031,31 +19048,6 @@
 7. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F712" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G712" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="713" ht="120" customHeight="1">
-      <x:c r="A713" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B713" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C713" s="18" t="str">
-        <x:v>block unblock 成员 nonexistent group（参数：blockMembers）</x:v>
-      </x:c>
-      <x:c r="D713" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
-      </x:c>
-      <x:c r="E713" s="18" t="str">
-        <x:v>1. A 执行群组业务操作
-2. 验证执行群组业务操作返回的错误码与错误文案
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
       <x:c r="F713" s="24" t="str">
         <x:v>普通</x:v>
       </x:c>
@@ -19071,7 +19063,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C714" s="18" t="str">
-        <x:v>block unblock 成员 nonexistent group（参数：unblockMembers）</x:v>
+        <x:v>block unblock 成员 nonexistent group（参数：blockMembers）</x:v>
       </x:c>
       <x:c r="D714" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -19096,43 +19088,41 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C715" s="18" t="str">
+        <x:v>block unblock 成员 nonexistent group（参数：unblockMembers）</x:v>
+      </x:c>
+      <x:c r="D715" s="18" t="str">
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+      </x:c>
+      <x:c r="E715" s="18" t="str">
+        <x:v>1. A 执行群组业务操作
+2. 验证执行群组业务操作返回的错误码与错误文案
+验证操作结果、关键字段和相关事件符合预期。</x:v>
+      </x:c>
+      <x:c r="F715" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G715" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="716" ht="120" customHeight="1">
+      <x:c r="A716" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B716" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C716" s="18" t="str">
         <x:v>clearAllGroupsFromLocal：清理本地群缓存，实测成功返回 None</x:v>
       </x:c>
-      <x:c r="D715" s="18" t="str">
+      <x:c r="D716" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E715" s="18" t="str">
+      <x:c r="E716" s="18" t="str">
         <x:v>1. A 清理本地群数据
 2. 验证清理本地群数据返回的响应 result 与关键字段
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F715" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G715" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="716" ht="120" customHeight="1">
-      <x:c r="A716" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B716" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C716" s="18" t="str">
-        <x:v>createGroup.inviteMembers 应覆盖 style=1/2/3 的直接邀请入群链路（参数：private-成员）</x:v>
-      </x:c>
-      <x:c r="D716" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
-      </x:c>
-      <x:c r="E716" s="18" t="str">
-        <x:v>1. 测试准备：创建测试群并建立业务前置
-2. 等待并校验目标业务事件
-3. 验证本用例的关键业务结果
-4. 测试后置：销毁测试群并恢复群状态
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
       <x:c r="F716" s="24" t="str">
         <x:v>普通</x:v>
       </x:c>
@@ -19148,7 +19138,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C717" s="18" t="str">
-        <x:v>createGroup.inviteMembers 应覆盖 style=1/2/3 的直接邀请入群链路（参数：public-approval）</x:v>
+        <x:v>createGroup.inviteMembers 应覆盖 style=1/2/3 的直接邀请入群链路（参数：private-成员）</x:v>
       </x:c>
       <x:c r="D717" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -19175,7 +19165,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C718" s="18" t="str">
-        <x:v>createGroup.inviteMembers 应覆盖 style=1/2/3 的直接邀请入群链路（参数：public-open）</x:v>
+        <x:v>createGroup.inviteMembers 应覆盖 style=1/2/3 的直接邀请入群链路（参数：public-approval）</x:v>
       </x:c>
       <x:c r="D718" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -19202,14 +19192,16 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C719" s="18" t="str">
-        <x:v>destroy group 空 group id</x:v>
+        <x:v>createGroup.inviteMembers 应覆盖 style=1/2/3 的直接邀请入群链路（参数：public-open）</x:v>
       </x:c>
       <x:c r="D719" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E719" s="18" t="str">
-        <x:v>1. A 销毁测试群
-2. 验证销毁测试群返回的错误码与错误文案
+        <x:v>1. 测试准备：创建测试群并建立业务前置
+2. 等待并校验目标业务事件
+3. 验证本用例的关键业务结果
+4. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
       <x:c r="F719" s="24" t="str">
@@ -19227,7 +19219,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C720" s="18" t="str">
-        <x:v>destroy group nonexistent</x:v>
+        <x:v>destroy group 空 group id</x:v>
       </x:c>
       <x:c r="D720" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -19252,12 +19244,37 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C721" s="18" t="str">
+        <x:v>destroy group nonexistent</x:v>
+      </x:c>
+      <x:c r="D721" s="18" t="str">
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+      </x:c>
+      <x:c r="E721" s="18" t="str">
+        <x:v>1. A 销毁测试群
+2. 验证销毁测试群返回的错误码与错误文案
+验证操作结果、关键字段和相关事件符合预期。</x:v>
+      </x:c>
+      <x:c r="F721" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G721" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="722" ht="120" customHeight="1">
+      <x:c r="A722" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B722" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C722" s="18" t="str">
         <x:v>fetchChatThreadDetail/getThread会话/joined/parent 列表：创建并加入子区后校验详情、线程会话和列表</x:v>
       </x:c>
-      <x:c r="D721" s="18" t="str">
+      <x:c r="D722" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E721" s="18" t="str">
+      <x:c r="E722" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立成员前置
 2. A 查询子区详情
 3. 验证查询子区详情返回的关键字段
@@ -19268,52 +19285,52 @@
 8. 验证群业务状态、事件与关键字段
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F721" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G721" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="722" ht="120" customHeight="1">
-      <x:c r="A722" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B722" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C722" s="18" t="str">
+      <x:c r="F722" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G722" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="723" ht="120" customHeight="1">
+      <x:c r="A723" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B723" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C723" s="18" t="str">
         <x:v>fetchGroupMembersInfo：groupId 为空字符串时，冻结真实错误返回</x:v>
       </x:c>
-      <x:c r="D722" s="18" t="str">
+      <x:c r="D723" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E722" s="18" t="str">
+      <x:c r="E723" s="18" t="str">
         <x:v>1. A 查询群成员信息
 2. 验证群业务状态、事件与关键字段
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F722" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G722" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="723" ht="120" customHeight="1">
-      <x:c r="A723" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B723" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C723" s="18" t="str">
+      <x:c r="F723" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G723" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="724" ht="120" customHeight="1">
+      <x:c r="A724" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B724" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C724" s="18" t="str">
         <x:v>fetchGroupMembersInfo：limit=0 的分页边界，并比对成员资料与当前用户资料一致</x:v>
       </x:c>
-      <x:c r="D723" s="18" t="str">
+      <x:c r="D724" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E723" s="18" t="str">
+      <x:c r="E724" s="18" t="str">
         <x:v>1. A 查询用户资料
 2. 验证查询用户资料返回的响应 result 与关键字段
 3. 测试准备：创建测试群并建立业务前置
@@ -19322,27 +19339,27 @@
 6. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F723" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G723" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="724" ht="120" customHeight="1">
-      <x:c r="A724" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B724" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C724" s="18" t="str">
+      <x:c r="F724" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G724" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="725" ht="120" customHeight="1">
+      <x:c r="A725" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B725" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C725" s="18" t="str">
         <x:v>inviteNeedConfirm=false 时，即使 B 关闭自动接受，也应由服务端直接加入</x:v>
       </x:c>
-      <x:c r="D724" s="18" t="str">
+      <x:c r="D725" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E724" s="18" t="str">
+      <x:c r="E725" s="18" t="str">
         <x:v>1. B 关闭自动接受群邀请
 2. 验证自动接受群邀请设置已更新
 3. 测试准备：创建测试群并建立业务前置
@@ -19353,27 +19370,27 @@
 8. 测试后置：恢复 B 的自动接受群邀请设置
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F724" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G724" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="725" ht="120" customHeight="1">
-      <x:c r="A725" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B725" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C725" s="18" t="str">
+      <x:c r="F725" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G725" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="726" ht="120" customHeight="1">
+      <x:c r="A726" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B726" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C726" s="18" t="str">
         <x:v>inviter user 成功</x:v>
       </x:c>
-      <x:c r="D725" s="18" t="str">
+      <x:c r="D726" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E725" s="18" t="str">
+      <x:c r="E726" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 邀请成员
 3. 验证邀请成员返回的响应 result 与关键字段
@@ -19383,106 +19400,106 @@
 7. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F725" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G725" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="726" ht="120" customHeight="1">
-      <x:c r="A726" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B726" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C726" s="18" t="str">
+      <x:c r="F726" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G726" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="727" ht="120" customHeight="1">
+      <x:c r="A727" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B727" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C727" s="18" t="str">
         <x:v>inviter user 空 成员</x:v>
       </x:c>
-      <x:c r="D726" s="18" t="str">
+      <x:c r="D727" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E726" s="18" t="str">
+      <x:c r="E727" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 邀请成员
 3. 验证邀请成员返回的响应 result 与关键字段
 4. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F726" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G726" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="727" ht="120" customHeight="1">
-      <x:c r="A727" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B727" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C727" s="18" t="str">
+      <x:c r="F727" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G727" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="728" ht="120" customHeight="1">
+      <x:c r="A728" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B728" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C728" s="18" t="str">
         <x:v>inviter user nonexistent group</x:v>
       </x:c>
-      <x:c r="D727" s="18" t="str">
+      <x:c r="D728" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E727" s="18" t="str">
+      <x:c r="E728" s="18" t="str">
         <x:v>1. A 邀请成员
 2. 验证邀请成员返回的错误码与错误文案
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F727" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G727" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="728" ht="120" customHeight="1">
-      <x:c r="A728" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B728" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C728" s="18" t="str">
+      <x:c r="F728" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G728" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="729" ht="120" customHeight="1">
+      <x:c r="A729" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B729" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C729" s="18" t="str">
         <x:v>inviter user nonexistent user</x:v>
       </x:c>
-      <x:c r="D728" s="18" t="str">
+      <x:c r="D729" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E728" s="18" t="str">
+      <x:c r="E729" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 邀请成员
 3. 验证邀请成员返回的错误码与错误文案
 4. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F728" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G728" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="729" ht="120" customHeight="1">
-      <x:c r="A729" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B729" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C729" s="18" t="str">
+      <x:c r="F729" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G729" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="730" ht="120" customHeight="1">
+      <x:c r="A730" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B730" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C730" s="18" t="str">
         <x:v>is 成员 in white list and mute list 成功</x:v>
       </x:c>
-      <x:c r="D729" s="18" t="str">
+      <x:c r="D730" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E729" s="18" t="str">
+      <x:c r="E730" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 查询白名单成员状态
 3. 验证查询白名单成员状态返回的关键字段
@@ -19491,59 +19508,31 @@
 6. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F729" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G729" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="730" ht="120" customHeight="1">
-      <x:c r="A730" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B730" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C730" s="18" t="str">
+      <x:c r="F730" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G730" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="731" ht="120" customHeight="1">
+      <x:c r="A731" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B731" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C731" s="18" t="str">
         <x:v>is 成员 in white list and mute list nonexistent group</x:v>
       </x:c>
-      <x:c r="D730" s="18" t="str">
+      <x:c r="D731" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E730" s="18" t="str">
+      <x:c r="E731" s="18" t="str">
         <x:v>1. A 执行群组业务操作
 2. 验证执行群组业务操作返回的错误码与错误文案
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F730" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G730" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="731" ht="120" customHeight="1">
-      <x:c r="A731" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B731" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C731" s="18" t="str">
-        <x:v>joinPublicGroup 拒绝私有群（style 0/1，603）；public-approval(style=2)/public-open(style=3) 5.0 允许加入（公开群）（参数：private-成员）</x:v>
-      </x:c>
-      <x:c r="D731" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
-      </x:c>
-      <x:c r="E731" s="18" t="str">
-        <x:v>1. 测试准备：创建测试群并建立业务前置
-2. B 加入公开群
-3. 验证加入公开群返回的错误码与错误文案
-4. 验证加入公开群返回的关键字段
-5. 测试后置：销毁测试群并恢复群状态
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
       <x:c r="F731" s="24" t="str">
         <x:v>普通</x:v>
       </x:c>
@@ -19559,7 +19548,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C732" s="18" t="str">
-        <x:v>joinPublicGroup 拒绝私有群（style 0/1，603）；public-approval(style=2)/public-open(style=3) 5.0 允许加入（公开群）（参数：private-owner）</x:v>
+        <x:v>joinPublicGroup 拒绝私有群（style 0/1，603）；public-approval(style=2)/public-open(style=3) 5.0 允许加入（公开群）（参数：private-成员）</x:v>
       </x:c>
       <x:c r="D732" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -19587,37 +19576,12 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C733" s="18" t="str">
-        <x:v>leave group non 成员</x:v>
+        <x:v>joinPublicGroup 拒绝私有群（style 0/1，603）；public-approval(style=2)/public-open(style=3) 5.0 允许加入（公开群）（参数：private-owner）</x:v>
       </x:c>
       <x:c r="D733" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备B已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E733" s="18" t="str">
-        <x:v>1. B 退出群
-2. 验证退出群返回的错误码与错误文案
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
-      <x:c r="F733" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G733" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="734" ht="120" customHeight="1">
-      <x:c r="A734" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B734" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C734" s="18" t="str">
-        <x:v>maxCount=2 的公开自由群已包含 A+B 时，C 不得加入</x:v>
-      </x:c>
-      <x:c r="D734" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
-      </x:c>
-      <x:c r="E734" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. B 加入公开群
 3. 验证加入公开群返回的错误码与错误文案
@@ -19625,6 +19589,31 @@
 5. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
+      <x:c r="F733" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G733" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="734" ht="120" customHeight="1">
+      <x:c r="A734" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B734" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C734" s="18" t="str">
+        <x:v>leave group non 成员</x:v>
+      </x:c>
+      <x:c r="D734" s="18" t="str">
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备B已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+      </x:c>
+      <x:c r="E734" s="18" t="str">
+        <x:v>1. B 退出群
+2. 验证退出群返回的错误码与错误文案
+验证操作结果、关键字段和相关事件符合预期。</x:v>
+      </x:c>
       <x:c r="F734" s="24" t="str">
         <x:v>普通</x:v>
       </x:c>
@@ -19640,14 +19629,17 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C735" s="18" t="str">
-        <x:v>moderation nonexistent group errors（参数：addWhiteList-info4-600-do not find this group）</x:v>
+        <x:v>maxCount=2 的公开自由群已包含 A+B 时，C 不得加入</x:v>
       </x:c>
       <x:c r="D735" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E735" s="18" t="str">
-        <x:v>1. A 执行群组业务操作
-2. 验证执行群组业务操作返回的错误码与错误文案
+        <x:v>1. 测试准备：创建测试群并建立业务前置
+2. B 加入公开群
+3. 验证加入公开群返回的错误码与错误文案
+4. 验证加入公开群返回的关键字段
+5. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
       <x:c r="F735" s="24" t="str">
@@ -19665,7 +19657,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C736" s="18" t="str">
-        <x:v>moderation nonexistent group errors（参数：muteAllMembers-info2-600-do not find this group）</x:v>
+        <x:v>moderation nonexistent group errors（参数：addWhiteList-info4-600-do not find this group）</x:v>
       </x:c>
       <x:c r="D736" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -19690,7 +19682,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C737" s="18" t="str">
-        <x:v>moderation nonexistent group errors（参数：muteMembers-info0-600-do not find this group）</x:v>
+        <x:v>moderation nonexistent group errors（参数：muteAllMembers-info2-600-do not find this group）</x:v>
       </x:c>
       <x:c r="D737" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -19715,7 +19707,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C738" s="18" t="str">
-        <x:v>moderation nonexistent group errors（参数：removeWhiteList-info5-600-do not find this group）</x:v>
+        <x:v>moderation nonexistent group errors（参数：muteMembers-info0-600-do not find this group）</x:v>
       </x:c>
       <x:c r="D738" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -19740,7 +19732,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C739" s="18" t="str">
-        <x:v>moderation nonexistent group errors（参数：unMuteAllMembers-info3-600-do not find this group）</x:v>
+        <x:v>moderation nonexistent group errors（参数：removeWhiteList-info5-600-do not find this group）</x:v>
       </x:c>
       <x:c r="D739" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -19765,7 +19757,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C740" s="18" t="str">
-        <x:v>moderation nonexistent group errors（参数：unMuteMembers-info1-600-do not find this group）</x:v>
+        <x:v>moderation nonexistent group errors（参数：unMuteAllMembers-info3-600-do not find this group）</x:v>
       </x:c>
       <x:c r="D740" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -19790,7 +19782,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C741" s="18" t="str">
-        <x:v>moderation nonexistent group errors（参数：updateGroupExt-info6-600-do not find this group）</x:v>
+        <x:v>moderation nonexistent group errors（参数：unMuteMembers-info1-600-do not find this group）</x:v>
       </x:c>
       <x:c r="D741" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -19815,89 +19807,114 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C742" s="18" t="str">
+        <x:v>moderation nonexistent group errors（参数：updateGroupExt-info6-600-do not find this group）</x:v>
+      </x:c>
+      <x:c r="D742" s="18" t="str">
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+      </x:c>
+      <x:c r="E742" s="18" t="str">
+        <x:v>1. A 执行群组业务操作
+2. 验证执行群组业务操作返回的错误码与错误文案
+验证操作结果、关键字段和相关事件符合预期。</x:v>
+      </x:c>
+      <x:c r="F742" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G742" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="743" ht="120" customHeight="1">
+      <x:c r="A743" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B743" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C743" s="18" t="str">
         <x:v>request to join public group nonexistent group</x:v>
       </x:c>
-      <x:c r="D742" s="18" t="str">
+      <x:c r="D743" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备B已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E742" s="18" t="str">
+      <x:c r="E743" s="18" t="str">
         <x:v>1. B 申请加入公开群
 2. 验证申请加入公开群返回的错误码与错误文案
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F742" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G742" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="743" ht="120" customHeight="1">
-      <x:c r="A743" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B743" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C743" s="18" t="str">
+      <x:c r="F743" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G743" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="744" ht="120" customHeight="1">
+      <x:c r="A744" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B744" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C744" s="18" t="str">
         <x:v>set 成员 属性 空 属性</x:v>
       </x:c>
-      <x:c r="D743" s="18" t="str">
+      <x:c r="D744" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E743" s="18" t="str">
+      <x:c r="E744" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 执行群组业务操作
 3. 验证执行群组业务操作返回的错误码与错误文案
 4. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F743" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G743" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="744" ht="120" customHeight="1">
-      <x:c r="A744" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B744" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C744" s="18" t="str">
+      <x:c r="F744" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G744" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="745" ht="120" customHeight="1">
+      <x:c r="A745" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B745" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C745" s="18" t="str">
         <x:v>set 成员 属性 nonexistent group</x:v>
       </x:c>
-      <x:c r="D744" s="18" t="str">
+      <x:c r="D745" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E744" s="18" t="str">
+      <x:c r="E745" s="18" t="str">
         <x:v>1. A 执行群组业务操作
 2. 验证执行群组业务操作返回的响应 result 与关键字段
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F744" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G744" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="745" ht="120" customHeight="1">
-      <x:c r="A745" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B745" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C745" s="18" t="str">
+      <x:c r="F745" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G745" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="746" ht="120" customHeight="1">
+      <x:c r="A746" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B746" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C746" s="18" t="str">
         <x:v>set and 获取 成员 属性 成功</x:v>
       </x:c>
-      <x:c r="D745" s="18" t="str">
+      <x:c r="D746" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E745" s="18" t="str">
+      <x:c r="E746" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. B 执行群组业务操作
 3. 验证执行群组业务操作返回的响应 result 与关键字段
@@ -19906,37 +19923,6 @@
 6. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F745" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G745" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="746" ht="120" customHeight="1">
-      <x:c r="A746" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B746" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C746" s="18" t="str">
-        <x:v>style=0 仅群主可邀请；style=1 的普通成员和管理员均可邀请（参数：添加-成员-private-成员-admin-allowed）</x:v>
-      </x:c>
-      <x:c r="D746" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
-      </x:c>
-      <x:c r="E746" s="18" t="str">
-        <x:v>1. 测试准备：创建测试群并建立业务前置
-2. A 添加群管理员
-3. 验证 添加群管理员返回的关键字段
-4. B 执行群组业务操作
-5. 验证群业务状态、事件与关键字段
-6. 等待并校验目标业务事件
-7. 验证执行群组业务操作返回的错误码与错误文案
-8. 测试后置：销毁测试群并恢复群状态
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
       <x:c r="F746" s="24" t="str">
         <x:v>普通</x:v>
       </x:c>
@@ -19952,7 +19938,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C747" s="18" t="str">
-        <x:v>style=0 仅群主可邀请；style=1 的普通成员和管理员均可邀请（参数：添加-成员-private-成员-normal-成员-allowed）</x:v>
+        <x:v>style=0 仅群主可邀请；style=1 的普通成员和管理员均可邀请（参数：添加-成员-private-成员-admin-allowed）</x:v>
       </x:c>
       <x:c r="D747" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -19983,7 +19969,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C748" s="18" t="str">
-        <x:v>style=0 仅群主可邀请；style=1 的普通成员和管理员均可邀请（参数：添加-成员-private-owner-admin-denied）</x:v>
+        <x:v>style=0 仅群主可邀请；style=1 的普通成员和管理员均可邀请（参数：添加-成员-private-成员-normal-成员-allowed）</x:v>
       </x:c>
       <x:c r="D748" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -20014,7 +20000,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C749" s="18" t="str">
-        <x:v>style=0 仅群主可邀请；style=1 的普通成员和管理员均可邀请（参数：添加-成员-private-owner-normal-成员-denied）</x:v>
+        <x:v>style=0 仅群主可邀请；style=1 的普通成员和管理员均可邀请（参数：添加-成员-private-owner-admin-denied）</x:v>
       </x:c>
       <x:c r="D749" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -20045,7 +20031,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C750" s="18" t="str">
-        <x:v>style=0 仅群主可邀请；style=1 的普通成员和管理员均可邀请（参数：inviter-user-private-成员-admin-allowed）</x:v>
+        <x:v>style=0 仅群主可邀请；style=1 的普通成员和管理员均可邀请（参数：添加-成员-private-owner-normal-成员-denied）</x:v>
       </x:c>
       <x:c r="D750" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -20076,7 +20062,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C751" s="18" t="str">
-        <x:v>style=0 仅群主可邀请；style=1 的普通成员和管理员均可邀请（参数：inviter-user-private-成员-normal-成员-allowed）</x:v>
+        <x:v>style=0 仅群主可邀请；style=1 的普通成员和管理员均可邀请（参数：inviter-user-private-成员-admin-allowed）</x:v>
       </x:c>
       <x:c r="D751" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -20107,7 +20093,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C752" s="18" t="str">
-        <x:v>style=0 仅群主可邀请；style=1 的普通成员和管理员均可邀请（参数：inviter-user-private-owner-admin-denied）</x:v>
+        <x:v>style=0 仅群主可邀请；style=1 的普通成员和管理员均可邀请（参数：inviter-user-private-成员-normal-成员-allowed）</x:v>
       </x:c>
       <x:c r="D752" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -20138,7 +20124,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C753" s="18" t="str">
-        <x:v>style=0 仅群主可邀请；style=1 的普通成员和管理员均可邀请（参数：inviter-user-private-owner-normal-成员-denied）</x:v>
+        <x:v>style=0 仅群主可邀请；style=1 的普通成员和管理员均可邀请（参数：inviter-user-private-owner-admin-denied）</x:v>
       </x:c>
       <x:c r="D753" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -20169,64 +20155,95 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C754" s="18" t="str">
+        <x:v>style=0 仅群主可邀请；style=1 的普通成员和管理员均可邀请（参数：inviter-user-private-owner-normal-成员-denied）</x:v>
+      </x:c>
+      <x:c r="D754" s="18" t="str">
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+      </x:c>
+      <x:c r="E754" s="18" t="str">
+        <x:v>1. 测试准备：创建测试群并建立业务前置
+2. A 添加群管理员
+3. 验证 添加群管理员返回的关键字段
+4. B 执行群组业务操作
+5. 验证群业务状态、事件与关键字段
+6. 等待并校验目标业务事件
+7. 验证执行群组业务操作返回的错误码与错误文案
+8. 测试后置：销毁测试群并恢复群状态
+验证操作结果、关键字段和相关事件符合预期。</x:v>
+      </x:c>
+      <x:c r="F754" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G754" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="755" ht="120" customHeight="1">
+      <x:c r="A755" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B755" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C755" s="18" t="str">
         <x:v>unblock idempotent</x:v>
       </x:c>
-      <x:c r="D754" s="18" t="str">
+      <x:c r="D755" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E754" s="18" t="str">
+      <x:c r="E755" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 取消屏蔽群消息
 3. 验证取消屏蔽群消息返回的关键字段
 4. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F754" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G754" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="755" ht="120" customHeight="1">
-      <x:c r="A755" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B755" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C755" s="18" t="str">
+      <x:c r="F755" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G755" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="756" ht="120" customHeight="1">
+      <x:c r="A756" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B756" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C756" s="18" t="str">
         <x:v>unblock nonexistent group</x:v>
       </x:c>
-      <x:c r="D755" s="18" t="str">
+      <x:c r="D756" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E755" s="18" t="str">
+      <x:c r="E756" s="18" t="str">
         <x:v>1. A 取消屏蔽群消息
 2. 验证取消屏蔽群消息返回的错误码与错误文案
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F755" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G755" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="756" ht="120" customHeight="1">
-      <x:c r="A756" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B756" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C756" s="18" t="str">
+      <x:c r="F756" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G756" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="757" ht="120" customHeight="1">
+      <x:c r="A757" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B757" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C757" s="18" t="str">
         <x:v>update announcement 空</x:v>
       </x:c>
-      <x:c r="D756" s="18" t="str">
+      <x:c r="D757" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E756" s="18" t="str">
+      <x:c r="E757" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 更新群公告
 3. 验证更新群公告返回的关键字段
@@ -20235,58 +20252,31 @@
 6. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F756" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G756" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="757" ht="120" customHeight="1">
-      <x:c r="A757" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B757" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C757" s="18" t="str">
+      <x:c r="F757" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G757" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="758" ht="120" customHeight="1">
+      <x:c r="A758" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B758" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C758" s="18" t="str">
         <x:v>update announcement nonexistent group</x:v>
       </x:c>
-      <x:c r="D757" s="18" t="str">
+      <x:c r="D758" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E757" s="18" t="str">
+      <x:c r="E758" s="18" t="str">
         <x:v>1. A 更新群公告
 2. 验证更新群公告返回的错误码与错误文案
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F757" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G757" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="758" ht="120" customHeight="1">
-      <x:c r="A758" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B758" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C758" s="18" t="str">
-        <x:v>update avatar abnormal values</x:v>
-      </x:c>
-      <x:c r="D758" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
-      </x:c>
-      <x:c r="E758" s="18" t="str">
-        <x:v>1. 测试准备：创建测试群并建立业务前置
-2. A 更新群头像
-3. 验证更新群头像返回的关键字段
-4. 测试后置：销毁测试群并恢复群状态
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
       <x:c r="F758" s="24" t="str">
         <x:v>普通</x:v>
       </x:c>
@@ -20302,7 +20292,7 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C759" s="18" t="str">
-        <x:v>update avatar abnormal values（参数：https://example.com/aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa）</x:v>
+        <x:v>update avatar abnormal values</x:v>
       </x:c>
       <x:c r="D759" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
@@ -20329,279 +20319,280 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C760" s="18" t="str">
-        <x:v>update description 空</x:v>
+        <x:v>update avatar abnormal values（参数：https://example.com/aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa）</x:v>
       </x:c>
       <x:c r="D760" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
       <x:c r="E760" s="18" t="str">
+        <x:v>1. 测试准备：创建测试群并建立业务前置
+2. A 更新群头像
+3. 验证更新群头像返回的关键字段
+4. 测试后置：销毁测试群并恢复群状态
+验证操作结果、关键字段和相关事件符合预期。</x:v>
+      </x:c>
+      <x:c r="F760" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G760" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="761" ht="120" customHeight="1">
+      <x:c r="A761" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B761" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C761" s="18" t="str">
+        <x:v>update description 空</x:v>
+      </x:c>
+      <x:c r="D761" s="18" t="str">
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
+      </x:c>
+      <x:c r="E761" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 执行群组业务操作
 3. 验证执行群组业务操作返回的响应 result 与关键字段
 4. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F760" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G760" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="761" ht="120" customHeight="1">
-      <x:c r="A761" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B761" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C761" s="18" t="str">
+      <x:c r="F761" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G761" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="762" ht="120" customHeight="1">
+      <x:c r="A762" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B762" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C762" s="18" t="str">
         <x:v>update description nonexistent group</x:v>
       </x:c>
-      <x:c r="D761" s="18" t="str">
+      <x:c r="D762" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E761" s="18" t="str">
+      <x:c r="E762" s="18" t="str">
         <x:v>1. A 执行群组业务操作
 2. 验证执行群组业务操作返回的错误码与错误文案
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F761" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G761" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="762" ht="120" customHeight="1">
-      <x:c r="A762" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B762" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C762" s="18" t="str">
+      <x:c r="F762" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G762" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="763" ht="120" customHeight="1">
+      <x:c r="A763" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B763" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C763" s="18" t="str">
         <x:v>update description too long</x:v>
       </x:c>
-      <x:c r="D762" s="18" t="str">
+      <x:c r="D763" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E762" s="18" t="str">
+      <x:c r="E763" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 执行群组业务操作
 3. 验证执行群组业务操作返回的响应 result 与关键字段
 4. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F762" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G762" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="763" ht="120" customHeight="1">
-      <x:c r="A763" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B763" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C763" s="18" t="str">
+      <x:c r="F763" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G763" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="764" ht="120" customHeight="1">
+      <x:c r="A764" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B764" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C764" s="18" t="str">
         <x:v>update group ext 成功</x:v>
       </x:c>
-      <x:c r="D763" s="18" t="str">
+      <x:c r="D764" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E763" s="18" t="str">
+      <x:c r="E764" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 更新群扩展信息
 3. 验证更新群扩展信息返回的关键字段
 4. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F763" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G763" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="764" ht="120" customHeight="1">
-      <x:c r="A764" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B764" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C764" s="18" t="str">
+      <x:c r="F764" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G764" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="765" ht="120" customHeight="1">
+      <x:c r="A765" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B765" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C765" s="18" t="str">
         <x:v>update owner nonexistent group</x:v>
       </x:c>
-      <x:c r="D764" s="18" t="str">
+      <x:c r="D765" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E764" s="18" t="str">
+      <x:c r="E765" s="18" t="str">
         <x:v>1. A 转让群主
 2. 验证转让群主返回的错误码与错误文案
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F764" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G764" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="765" ht="120" customHeight="1">
-      <x:c r="A765" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B765" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C765" s="18" t="str">
+      <x:c r="F765" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G765" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="766" ht="120" customHeight="1">
+      <x:c r="A766" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B766" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C766" s="18" t="str">
         <x:v>update subject 空</x:v>
       </x:c>
-      <x:c r="D765" s="18" t="str">
+      <x:c r="D766" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E765" s="18" t="str">
+      <x:c r="E766" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 更新群名称
 3. 验证更新群名称返回的关键字段
 4. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F765" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G765" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="766" ht="120" customHeight="1">
-      <x:c r="A766" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B766" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C766" s="18" t="str">
+      <x:c r="F766" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G766" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="767" ht="120" customHeight="1">
+      <x:c r="A767" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B767" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C767" s="18" t="str">
         <x:v>update subject nonexistent group</x:v>
       </x:c>
-      <x:c r="D766" s="18" t="str">
+      <x:c r="D767" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E766" s="18" t="str">
+      <x:c r="E767" s="18" t="str">
         <x:v>1. A 更新群名称
 2. 验证更新群名称返回的错误码与错误文案
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F766" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G766" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="767" ht="120" customHeight="1">
-      <x:c r="A767" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B767" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C767" s="18" t="str">
+      <x:c r="F767" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G767" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="768" ht="120" customHeight="1">
+      <x:c r="A768" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B768" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C768" s="18" t="str">
         <x:v>update subject too long</x:v>
       </x:c>
-      <x:c r="D767" s="18" t="str">
+      <x:c r="D768" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E767" s="18" t="str">
+      <x:c r="E768" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 更新群名称
 3. 验证更新群名称返回的关键字段
 4. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F767" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G767" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="768" ht="120" customHeight="1">
-      <x:c r="A768" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B768" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C768" s="18" t="str">
+      <x:c r="F768" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G768" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="769" ht="120" customHeight="1">
+      <x:c r="A769" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B769" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C769" s="18" t="str">
         <x:v>updateGroupAvatar：群主更新群头像 URL，返回群对象中 avatarUrl 为新值</x:v>
       </x:c>
-      <x:c r="D768" s="18" t="str">
+      <x:c r="D769" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E768" s="18" t="str">
+      <x:c r="E769" s="18" t="str">
         <x:v>1. 测试准备：创建测试群并建立业务前置
 2. A 更新群头像
 3. 验证更新群头像返回的关键字段
 4. 测试后置：销毁测试群并恢复群状态
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F768" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G768" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="769" ht="120" customHeight="1">
-      <x:c r="A769" s="21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="B769" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C769" s="18" t="str">
+      <x:c r="F769" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G769" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="770" ht="120" customHeight="1">
+      <x:c r="A770" s="21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="B770" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C770" s="18" t="str">
         <x:v>updateGroupAvatar：groupId 为空字符串时，冻结真实错误返回</x:v>
       </x:c>
-      <x:c r="D769" s="18" t="str">
+      <x:c r="D770" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。；服务端所需权限及目标对象已准备。</x:v>
       </x:c>
-      <x:c r="E769" s="18" t="str">
+      <x:c r="E770" s="18" t="str">
         <x:v>1. A 更新群头像
 2. 验证群业务状态、事件与关键字段
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F769" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G769" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="770" ht="120" customHeight="1">
-      <x:c r="A770" s="21" t="str">
-        <x:v>Phase1</x:v>
-      </x:c>
-      <x:c r="B770" s="21" t="str">
-        <x:v>多设备</x:v>
-      </x:c>
-      <x:c r="C770" s="18" t="str">
-        <x:v>同账号多端：A 修改服务端属性，A 全部在线端最终读取到同一结果</x:v>
-      </x:c>
-      <x:c r="D770" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；接口响应与事件断言工具已初始化。</x:v>
-      </x:c>
-      <x:c r="E770" s="18" t="str">
-        <x:v>1. A 更新用户昵称并验证请求成功
-2. A 全部在线端查询用户资料并验证昵称同步
-验证在线设备集合中的目标设备是否均收到一致结果。
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
       <x:c r="F770" s="24" t="str">
         <x:v>普通</x:v>
       </x:c>
@@ -20611,125 +20602,18 @@
     </x:row>
     <x:row r="771" ht="120" customHeight="1">
       <x:c r="A771" s="21" t="str">
-        <x:v>Phase1</x:v>
+        <x:v>Presence</x:v>
       </x:c>
       <x:c r="B771" s="21" t="str">
         <x:v>多设备</x:v>
       </x:c>
       <x:c r="C771" s="18" t="str">
-        <x:v>组合拓扑：B 发给 A，A 的全部在线端都收到同一条消息</x:v>
+        <x:v>多端拓扑：A 发布 presence（动作端）；B 订阅 A，订阅关系为账号级 → B 全部在线端查询订阅列表一致； B 取消订阅后全部端查询为空</x:v>
       </x:c>
       <x:c r="D771" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；接口响应与事件断言工具已初始化。</x:v>
       </x:c>
       <x:c r="E771" s="18" t="str">
-        <x:v>1. 测试准备：清理相关设备的历史事件
-2. B 向 A 发送文本消息并验证发送成功
-3. A 全部在线端分别接收消息并验证 消息 ID 一致
-4. A 主端和副端分别接收消息并验证 消息 ID 一致
-验证在线设备集合中的目标设备是否均收到一致结果。
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
-      <x:c r="F771" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G771" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="772" ht="120" customHeight="1">
-      <x:c r="A772" s="21" t="str">
-        <x:v>Phase1</x:v>
-      </x:c>
-      <x:c r="B772" s="21" t="str">
-        <x:v>离线</x:v>
-      </x:c>
-      <x:c r="C772" s="18" t="str">
-        <x:v>离线 消息 sync 保留 case event cursor</x:v>
-      </x:c>
-      <x:c r="D772" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。；本 Case 仅验证指定设备的离线/重登结果，不代表多设备校验。</x:v>
-      </x:c>
-      <x:c r="E772" s="18" t="str">
-        <x:v>1. 测试准备：清理收发设备历史事件
-2. A 断开网络并验证进入离线状态
-3. B 向离线的 A 发送文本消息并验证发送成功
-4. A 恢复网络并验证重新连接
-5. A 恢复后接收离线消息并验证消息内容
-恢复指定设备在线或重新登录，校验离线同步结果；本 Case 不覆盖多设备校验。
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
-      <x:c r="F772" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G772" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="773" ht="120" customHeight="1">
-      <x:c r="A773" s="21" t="str">
-        <x:v>Phase1</x:v>
-      </x:c>
-      <x:c r="B773" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C773" s="18" t="str">
-        <x:v>同一 case：4.10 在调用前 Skip，4.14 调用真实新增 API 并成功</x:v>
-      </x:c>
-      <x:c r="D773" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。</x:v>
-      </x:c>
-      <x:c r="E773" s="18" t="str">
-        <x:v>1. 确认设备支持成员详情能力并创建测试群
-2. 查询群成员详情并验证分页结果结构
-3. 测试后置：销毁能力验证测试群
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
-      <x:c r="F773" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G773" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="774" ht="120" customHeight="1">
-      <x:c r="A774" s="21" t="str">
-        <x:v>Phase1</x:v>
-      </x:c>
-      <x:c r="B774" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C774" s="18" t="str">
-        <x:v>Android 4.23 → 5.0 覆盖安装（同 application_id）：验证升级后消息数据保留</x:v>
-      </x:c>
-      <x:c r="D774" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；测试账号已创建并登录，当前 Case 所需的基础数据已准备。</x:v>
-      </x:c>
-      <x:c r="E774" s="18" t="str">
-        <x:v>1. 执行 4.23 到 5.0 覆盖升级并验证消息数据保留
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
-      <x:c r="F774" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G774" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="775" ht="120" customHeight="1">
-      <x:c r="A775" s="21" t="str">
-        <x:v>Presence</x:v>
-      </x:c>
-      <x:c r="B775" s="21" t="str">
-        <x:v>多设备</x:v>
-      </x:c>
-      <x:c r="C775" s="18" t="str">
-        <x:v>多端拓扑：A 发布 presence（动作端）；B 订阅 A，订阅关系为账号级 → B 全部在线端查询订阅列表一致； B 取消订阅后全部端查询为空</x:v>
-      </x:c>
-      <x:c r="D775" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；接口响应与事件断言工具已初始化。</x:v>
-      </x:c>
-      <x:c r="E775" s="18" t="str">
         <x:v>1. 测试准备：清理收发账号全部端的历史事件
 2. 发布在线状态 在线
 3. 确认发布请求已提交
@@ -20741,27 +20625,27 @@
 验证在线设备集合中的目标设备是否均收到一致结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F775" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G775" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="776" ht="120" customHeight="1">
-      <x:c r="A776" s="21" t="str">
+      <x:c r="F771" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G771" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="772" ht="120" customHeight="1">
+      <x:c r="A772" s="21" t="str">
         <x:v>Presence</x:v>
       </x:c>
-      <x:c r="B776" s="21" t="str">
+      <x:c r="B772" s="21" t="str">
         <x:v>多设备</x:v>
       </x:c>
-      <x:c r="C776" s="18" t="str">
+      <x:c r="C772" s="18" t="str">
         <x:v>多端拓扑：A 发布空 desc 在线状态；A 全部端查询状态 desc 为空；B 订阅后，B 全部端查询 A 状态 desc 也为空</x:v>
       </x:c>
-      <x:c r="D776" s="18" t="str">
+      <x:c r="D772" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；用例所需的设备拓扑、账号和在线设备集合已准备。；接口响应与事件断言工具已初始化。</x:v>
       </x:c>
-      <x:c r="E776" s="18" t="str">
+      <x:c r="E772" s="18" t="str">
         <x:v>1. 测试准备：清理收发账号全部端的历史事件
 2. 发布空 desc 的在线状态
 3. 确认发布请求已提交
@@ -20772,6 +20656,104 @@
 验证在线设备集合中的目标设备是否均收到一致结果。
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
+      <x:c r="F772" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G772" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="773" ht="120" customHeight="1">
+      <x:c r="A773" s="21" t="str">
+        <x:v>Presence</x:v>
+      </x:c>
+      <x:c r="B773" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C773" s="18" t="str">
+        <x:v>订阅不存在用户：B 对不存在用户发起 presenceSubscribe</x:v>
+      </x:c>
+      <x:c r="D773" s="18" t="str">
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。</x:v>
+      </x:c>
+      <x:c r="E773" s="18" t="str">
+        <x:v>1. 订阅不存在用户并验证当前服务端返回语义
+验证操作结果、关键字段和相关事件符合预期。</x:v>
+      </x:c>
+      <x:c r="F773" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G773" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="774" ht="120" customHeight="1">
+      <x:c r="A774" s="21" t="str">
+        <x:v>Presence</x:v>
+      </x:c>
+      <x:c r="B774" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C774" s="18" t="str">
+        <x:v>订阅超过 100 个用户：presenceSubscribe 传入超过 100 个 成员，预期返回错误</x:v>
+      </x:c>
+      <x:c r="D774" s="18" t="str">
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。</x:v>
+      </x:c>
+      <x:c r="E774" s="18" t="str">
+        <x:v>1. 订阅超过数量上限的用户并验证数量错误
+验证操作结果、关键字段和相关事件符合预期。</x:v>
+      </x:c>
+      <x:c r="F774" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G774" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="775" ht="120" customHeight="1">
+      <x:c r="A775" s="21" t="str">
+        <x:v>Presence</x:v>
+      </x:c>
+      <x:c r="B775" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C775" s="18" t="str">
+        <x:v>订阅存在用户但过期时间大于 30 天：B 订阅 A，expiry 设为超过 30 天，预期返回错误</x:v>
+      </x:c>
+      <x:c r="D775" s="18" t="str">
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。</x:v>
+      </x:c>
+      <x:c r="E775" s="18" t="str">
+        <x:v>1. A 发布在线状态作为订阅前置
+2. B 使用超过 30 天的有效期订阅并验证边界错误
+验证操作结果、关键字段和相关事件符合预期。</x:v>
+      </x:c>
+      <x:c r="F775" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G775" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="776" ht="120" customHeight="1">
+      <x:c r="A776" s="21" t="str">
+        <x:v>Presence</x:v>
+      </x:c>
+      <x:c r="B776" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C776" s="18" t="str">
+        <x:v>非法分页参数：pageNum=0 或 pageSize=0，预期返回错误</x:v>
+      </x:c>
+      <x:c r="D776" s="18" t="str">
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。</x:v>
+      </x:c>
+      <x:c r="E776" s="18" t="str">
+        <x:v>1. 使用 pageNum=0 查询订阅列表并验证边界语义
+2. 使用 pageSize=0 查询订阅列表并验证边界错误
+验证操作结果、关键字段和相关事件符合预期。</x:v>
+      </x:c>
       <x:c r="F776" s="24" t="str">
         <x:v>普通</x:v>
       </x:c>
@@ -20787,13 +20769,15 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C777" s="18" t="str">
-        <x:v>订阅不存在用户：B 对不存在用户发起 presenceSubscribe</x:v>
+        <x:v>分页 pageSize=1：第 1 页 1 条，第 2 页 0 条</x:v>
       </x:c>
       <x:c r="D777" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。</x:v>
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。</x:v>
       </x:c>
       <x:c r="E777" s="18" t="str">
-        <x:v>1. 订阅不存在用户并验证当前服务端返回语义
+        <x:v>1. 创建在线状态并建立订阅前置
+2. 按 pageSize=1 查询第一页并验证包含 A
+3. 按 pageSize=1 查询第二页并验证为空
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
       <x:c r="F777" s="24" t="str">
@@ -20811,13 +20795,15 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C778" s="18" t="str">
-        <x:v>订阅超过 100 个用户：presenceSubscribe 传入超过 100 个 成员，预期返回错误</x:v>
+        <x:v>分页查询订阅列表：B 订阅 A 后，第 1 页有数据，第 2 页为空</x:v>
       </x:c>
       <x:c r="D778" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。</x:v>
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。</x:v>
       </x:c>
       <x:c r="E778" s="18" t="str">
-        <x:v>1. 订阅超过数量上限的用户并验证数量错误
+        <x:v>1. 创建在线状态并建立订阅前置
+2. 查询第一页订阅列表并验证包含 A
+3. 查询第二页订阅列表并验证为空
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
       <x:c r="F778" s="24" t="str">
@@ -20835,14 +20821,13 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C779" s="18" t="str">
-        <x:v>订阅存在用户但过期时间大于 30 天：B 订阅 A，expiry 设为超过 30 天，预期返回错误</x:v>
+        <x:v>取消订阅超过 100 个用户：presenceUnsubscribe 传入超过 100 个 成员，预期返回错误</x:v>
       </x:c>
       <x:c r="D779" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。</x:v>
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备B已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。</x:v>
       </x:c>
       <x:c r="E779" s="18" t="str">
-        <x:v>1. A 发布在线状态作为订阅前置
-2. B 使用超过 30 天的有效期订阅并验证边界错误
+        <x:v>1. 取消超过数量上限的订阅并验证数量错误
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
       <x:c r="F779" s="24" t="str">
@@ -20860,14 +20845,13 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C780" s="18" t="str">
-        <x:v>非法分页参数：pageNum=0 或 pageSize=0，预期返回错误</x:v>
+        <x:v>A 发布 128KB 大小 desc 的在线状态</x:v>
       </x:c>
       <x:c r="D780" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。</x:v>
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。</x:v>
       </x:c>
       <x:c r="E780" s="18" t="str">
-        <x:v>1. 使用 pageNum=0 查询订阅列表并验证边界语义
-2. 使用 pageSize=0 查询订阅列表并验证边界错误
+        <x:v>1. A 发布超长在线状态描述并验证长度错误
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
       <x:c r="F780" s="24" t="str">
@@ -20879,177 +20863,174 @@
     </x:row>
     <x:row r="781" ht="120" customHeight="1">
       <x:c r="A781" s="21" t="str">
-        <x:v>Presence</x:v>
+        <x:v>Push</x:v>
       </x:c>
       <x:c r="B781" s="21" t="str">
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C781" s="18" t="str">
-        <x:v>分页 pageSize=1：第 1 页 1 条，第 2 页 0 条</x:v>
+        <x:v>fetchPushConfigsFromServer / updatePushNickname / updatePushDisplayStyle：拉取推送配置并更新昵称和展示样式</x:v>
       </x:c>
       <x:c r="D781" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。</x:v>
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。</x:v>
       </x:c>
       <x:c r="E781" s="18" t="str">
-        <x:v>1. 创建在线状态并建立订阅前置
-2. 按 pageSize=1 查询第一页并验证包含 A
-3. 按 pageSize=1 查询第二页并验证为空
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
-      <x:c r="F781" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G781" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="782" ht="120" customHeight="1">
-      <x:c r="A782" s="21" t="str">
-        <x:v>Presence</x:v>
-      </x:c>
-      <x:c r="B782" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C782" s="18" t="str">
-        <x:v>分页查询订阅列表：B 订阅 A 后，第 1 页有数据，第 2 页为空</x:v>
-      </x:c>
-      <x:c r="D782" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。</x:v>
-      </x:c>
-      <x:c r="E782" s="18" t="str">
-        <x:v>1. 创建在线状态并建立订阅前置
-2. 查询第一页订阅列表并验证包含 A
-3. 查询第二页订阅列表并验证为空
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
-      <x:c r="F782" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G782" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="783" ht="120" customHeight="1">
-      <x:c r="A783" s="21" t="str">
-        <x:v>Presence</x:v>
-      </x:c>
-      <x:c r="B783" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C783" s="18" t="str">
-        <x:v>取消订阅超过 100 个用户：presenceUnsubscribe 传入超过 100 个 成员，预期返回错误</x:v>
-      </x:c>
-      <x:c r="D783" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备B已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。</x:v>
-      </x:c>
-      <x:c r="E783" s="18" t="str">
-        <x:v>1. 取消超过数量上限的订阅并验证数量错误
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
-      <x:c r="F783" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G783" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="784" ht="120" customHeight="1">
-      <x:c r="A784" s="21" t="str">
-        <x:v>Presence</x:v>
-      </x:c>
-      <x:c r="B784" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C784" s="18" t="str">
-        <x:v>A 发布 128KB 大小 desc 的在线状态</x:v>
-      </x:c>
-      <x:c r="D784" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A、设备B已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。</x:v>
-      </x:c>
-      <x:c r="E784" s="18" t="str">
-        <x:v>1. A 发布超长在线状态描述并验证长度错误
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
-      <x:c r="F784" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G784" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="785" ht="120" customHeight="1">
-      <x:c r="A785" s="21" t="str">
-        <x:v>Push</x:v>
-      </x:c>
-      <x:c r="B785" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C785" s="18" t="str">
-        <x:v>fetchPushConfigsFromServer / updatePushNickname / updatePushDisplayStyle：拉取推送配置并更新昵称和展示样式</x:v>
-      </x:c>
-      <x:c r="D785" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。</x:v>
-      </x:c>
-      <x:c r="E785" s="18" t="str">
         <x:v>1. 查询服务端推送配置并验证返回结构
 2. 更新推送昵称并验证配置更新结果
 3. 更新推送展示样式并验证配置更新结果
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F785" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G785" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="786" ht="120" customHeight="1">
-      <x:c r="A786" s="21" t="str">
+      <x:c r="F781" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G781" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="782" ht="120" customHeight="1">
+      <x:c r="A782" s="21" t="str">
         <x:v>Push</x:v>
       </x:c>
-      <x:c r="B786" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C786" s="18" t="str">
+      <x:c r="B782" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C782" s="18" t="str">
         <x:v>set/获取/删除会话列表ilentMode：对单聊会话设置、查询、移除离线推送设置</x:v>
       </x:c>
-      <x:c r="D786" s="18" t="str">
+      <x:c r="D782" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。</x:v>
       </x:c>
-      <x:c r="E786" s="18" t="str">
+      <x:c r="E782" s="18" t="str">
         <x:v>1. 设置单聊会话免打扰并验证成功
 2. 查询单聊会话免打扰设置并验证配置
 3. 批量查询会话免打扰设置并验证目标会话
 4. 移除单聊会话免打扰设置并验证成功
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F786" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G786" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="787" ht="120" customHeight="1">
-      <x:c r="A787" s="21" t="str">
+      <x:c r="F782" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G782" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="783" ht="120" customHeight="1">
+      <x:c r="A783" s="21" t="str">
         <x:v>Push</x:v>
       </x:c>
-      <x:c r="B787" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C787" s="18" t="str">
+      <x:c r="B783" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C783" s="18" t="str">
         <x:v>set/fetchPreferredNotification语言 与 set/getPushTemplate：设置并查询推送语言和模板名称</x:v>
       </x:c>
-      <x:c r="D787" s="18" t="str">
+      <x:c r="D783" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。</x:v>
       </x:c>
-      <x:c r="E787" s="18" t="str">
+      <x:c r="E783" s="18" t="str">
         <x:v>1. 设置首选通知语言并验证保存成功
 2. 查询首选通知语言并验证为英语
 3. 设置推送模板并验证保存成功
 4. 查询推送模板并验证模板名称
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
+      <x:c r="F783" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G783" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="784" ht="120" customHeight="1">
+      <x:c r="A784" s="21" t="str">
+        <x:v>Push</x:v>
+      </x:c>
+      <x:c r="B784" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C784" s="18" t="str">
+        <x:v>setSilentModeForAll / fetchSilentModeForAll：设置全局离线推送提醒类型，并拉取全局设置</x:v>
+      </x:c>
+      <x:c r="D784" s="18" t="str">
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。</x:v>
+      </x:c>
+      <x:c r="E784" s="18" t="str">
+        <x:v>1. 设置全局离线推送提醒类型并验证成功
+2. 查询全局离线推送设置并验证配置字段
+验证操作结果、关键字段和相关事件符合预期。</x:v>
+      </x:c>
+      <x:c r="F784" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G784" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="785" ht="120" customHeight="1">
+      <x:c r="A785" s="21" t="str">
+        <x:v>Push</x:v>
+      </x:c>
+      <x:c r="B785" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C785" s="18" t="str">
+        <x:v>syncSilentModels：同步所有会话免打扰信息，冻结当前模拟器返回语义</x:v>
+      </x:c>
+      <x:c r="D785" s="18" t="str">
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。</x:v>
+      </x:c>
+      <x:c r="E785" s="18" t="str">
+        <x:v>1. 同步所有会话免打扰设置并验证返回结构
+验证操作结果、关键字段和相关事件符合预期。</x:v>
+      </x:c>
+      <x:c r="F785" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G785" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="786" ht="120" customHeight="1">
+      <x:c r="A786" s="21" t="str">
+        <x:v>Push</x:v>
+      </x:c>
+      <x:c r="B786" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C786" s="18" t="str">
+        <x:v>update*PushToken / bindDeviceToken：使用测试 token 调用，冻结当前模拟器环境下的真实返回语义（参数：bindDeviceToken-info2-None）</x:v>
+      </x:c>
+      <x:c r="D786" s="18" t="str">
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。</x:v>
+      </x:c>
+      <x:c r="E786" s="18" t="str">
+        <x:v>1. 更新厂商推送令牌并验证当前环境返回语义
+验证操作结果、关键字段和相关事件符合预期。</x:v>
+      </x:c>
+      <x:c r="F786" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G786" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="787" ht="120" customHeight="1">
+      <x:c r="A787" s="21" t="str">
+        <x:v>Push</x:v>
+      </x:c>
+      <x:c r="B787" s="21" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C787" s="18" t="str">
+        <x:v>update*PushToken / bindDeviceToken：使用测试 token 调用，冻结当前模拟器环境下的真实返回语义（参数：updateFCMPushToken-info1-expected_result1）</x:v>
+      </x:c>
+      <x:c r="D787" s="18" t="str">
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。</x:v>
+      </x:c>
+      <x:c r="E787" s="18" t="str">
+        <x:v>1. 更新厂商推送令牌并验证当前环境返回语义
+验证操作结果、关键字段和相关事件符合预期。</x:v>
+      </x:c>
       <x:c r="F787" s="24" t="str">
         <x:v>普通</x:v>
       </x:c>
@@ -21065,14 +21046,13 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C788" s="18" t="str">
-        <x:v>setSilentModeForAll / fetchSilentModeForAll：设置全局离线推送提醒类型，并拉取全局设置</x:v>
+        <x:v>update*PushToken / bindDeviceToken：使用测试 token 调用，冻结当前模拟器环境下的真实返回语义（参数：updateHMSPushToken-info0-hms-token-api-coverage）</x:v>
       </x:c>
       <x:c r="D788" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。</x:v>
       </x:c>
       <x:c r="E788" s="18" t="str">
-        <x:v>1. 设置全局离线推送提醒类型并验证成功
-2. 查询全局离线推送设置并验证配置字段
+        <x:v>1. 更新厂商推送令牌并验证当前环境返回语义
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
       <x:c r="F788" s="24" t="str">
@@ -21090,13 +21070,13 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C789" s="18" t="str">
-        <x:v>syncSilentModels：同步所有会话免打扰信息，冻结当前模拟器返回语义</x:v>
+        <x:v>updateAPNsPushToken：仅在 Android 验证 缺失Plugin，iOS 不执行该平台缺口用例</x:v>
       </x:c>
       <x:c r="D789" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。</x:v>
       </x:c>
       <x:c r="E789" s="18" t="str">
-        <x:v>1. 同步所有会话免打扰设置并验证返回结构
+        <x:v>1. 调用 Android 不适用的 APNs 令牌接口并记录平台缺口
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
       <x:c r="F789" s="24" t="str">
@@ -21108,19 +21088,20 @@
     </x:row>
     <x:row r="790" ht="120" customHeight="1">
       <x:c r="A790" s="21" t="str">
-        <x:v>Push</x:v>
+        <x:v>UserInfo</x:v>
       </x:c>
       <x:c r="B790" s="21" t="str">
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C790" s="18" t="str">
-        <x:v>update*PushToken / bindDeviceToken：使用测试 token 调用，冻结当前模拟器环境下的真实返回语义（参数：bindDeviceToken-info2-None）</x:v>
+        <x:v>先 updateOwnUserInfo，再用 fetchUserInfoById 拉当前用户（全量字段，与 fetchOwnInfo 语义等价）</x:v>
       </x:c>
       <x:c r="D790" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。</x:v>
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。</x:v>
       </x:c>
       <x:c r="E790" s="18" t="str">
-        <x:v>1. 更新厂商推送令牌并验证当前环境返回语义
+        <x:v>1. 设置用于查询验证的用户资料
+2. 按用户 ID 查询资料并验证全部字段
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
       <x:c r="F790" s="24" t="str">
@@ -21132,19 +21113,20 @@
     </x:row>
     <x:row r="791" ht="120" customHeight="1">
       <x:c r="A791" s="21" t="str">
-        <x:v>Push</x:v>
+        <x:v>UserInfo</x:v>
       </x:c>
       <x:c r="B791" s="21" t="str">
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C791" s="18" t="str">
-        <x:v>update*PushToken / bindDeviceToken：使用测试 token 调用，冻结当前模拟器环境下的真实返回语义（参数：updateFCMPushToken-info1-expected_result1）</x:v>
+        <x:v>先 updateOwnUserInfo，再用 fetchUserInfoByIdWithType 按类型拉取（仅 nick + sign；按类型返回时未必含 mail）</x:v>
       </x:c>
       <x:c r="D791" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。</x:v>
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。</x:v>
       </x:c>
       <x:c r="E791" s="18" t="str">
-        <x:v>1. 更新厂商推送令牌并验证当前环境返回语义
+        <x:v>1. 设置按类型查询所需的用户资料
+2. 按资料类型查询用户并验证昵称和签名
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
       <x:c r="F791" s="24" t="str">
@@ -21156,19 +21138,21 @@
     </x:row>
     <x:row r="792" ht="120" customHeight="1">
       <x:c r="A792" s="21" t="str">
-        <x:v>Push</x:v>
+        <x:v>UserInfo</x:v>
       </x:c>
       <x:c r="B792" s="21" t="str">
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C792" s="18" t="str">
-        <x:v>update*PushToken / bindDeviceToken：使用测试 token 调用，冻结当前模拟器环境下的真实返回语义（参数：updateHMSPushToken-info0-hms-token-api-coverage）</x:v>
+        <x:v>一次更新后：先 fetchUserInfoById（全量），再 fetchUserInfoByIdWithType（nick+sign），字段一致</x:v>
       </x:c>
       <x:c r="D792" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。</x:v>
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。</x:v>
       </x:c>
       <x:c r="E792" s="18" t="str">
-        <x:v>1. 更新厂商推送令牌并验证当前环境返回语义
+        <x:v>1. 设置统一的用户资料用于多接口查询
+2. 按用户 ID 查询全量资料并验证字段
+3. 按资料类型查询并验证部分字段一致
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
       <x:c r="F792" s="24" t="str">
@@ -21180,19 +21164,20 @@
     </x:row>
     <x:row r="793" ht="120" customHeight="1">
       <x:c r="A793" s="21" t="str">
-        <x:v>Push</x:v>
+        <x:v>UserInfo</x:v>
       </x:c>
       <x:c r="B793" s="21" t="str">
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C793" s="18" t="str">
-        <x:v>updateAPNsPushToken：仅在 Android 验证 缺失Plugin，iOS 不执行该平台缺口用例</x:v>
+        <x:v>fetchOwnInfo：更新当前用户属性后拉取自己的用户属性</x:v>
       </x:c>
       <x:c r="D793" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。</x:v>
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。</x:v>
       </x:c>
       <x:c r="E793" s="18" t="str">
-        <x:v>1. 调用 Android 不适用的 APNs 令牌接口并记录平台缺口
+        <x:v>1. 设置用于查询的当前用户资料
+2. 查询当前用户资料并验证属性
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
       <x:c r="F793" s="24" t="str">
@@ -21210,14 +21195,13 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C794" s="18" t="str">
-        <x:v>先 updateOwnUserInfo，再用 fetchUserInfoById 拉当前用户（全量字段，与 fetchOwnInfo 语义等价）</x:v>
+        <x:v>fetchUserInfoById：获取指定用户（当前用户与另一用户）的属性</x:v>
       </x:c>
       <x:c r="D794" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。</x:v>
       </x:c>
       <x:c r="E794" s="18" t="str">
-        <x:v>1. 设置用于查询验证的用户资料
-2. 按用户 ID 查询资料并验证全部字段
+        <x:v>1. 查询两个用户的资料并验证用户标识
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
       <x:c r="F794" s="24" t="str">
@@ -21235,14 +21219,13 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C795" s="18" t="str">
-        <x:v>先 updateOwnUserInfo，再用 fetchUserInfoByIdWithType 按类型拉取（仅 nick + sign；按类型返回时未必含 mail）</x:v>
+        <x:v>fetchUserInfoById：userIds 超过 100 个，预期失败</x:v>
       </x:c>
       <x:c r="D795" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。</x:v>
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。</x:v>
       </x:c>
       <x:c r="E795" s="18" t="str">
-        <x:v>1. 设置按类型查询所需的用户资料
-2. 按资料类型查询用户并验证昵称和签名
+        <x:v>1. 使用超过上限的用户列表查询资料并验证数量错误
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
       <x:c r="F795" s="24" t="str">
@@ -21260,15 +21243,13 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C796" s="18" t="str">
-        <x:v>一次更新后：先 fetchUserInfoById（全量），再 fetchUserInfoByIdWithType（nick+sign），字段一致</x:v>
+        <x:v>fetchUserInfoById：userIds 为空列表</x:v>
       </x:c>
       <x:c r="D796" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。</x:v>
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。</x:v>
       </x:c>
       <x:c r="E796" s="18" t="str">
-        <x:v>1. 设置统一的用户资料用于多接口查询
-2. 按用户 ID 查询全量资料并验证字段
-3. 按资料类型查询并验证部分字段一致
+        <x:v>1. 使用空用户列表查询资料并验证参数错误
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
       <x:c r="F796" s="24" t="str">
@@ -21286,14 +21267,13 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C797" s="18" t="str">
-        <x:v>fetchOwnInfo：更新当前用户属性后拉取自己的用户属性</x:v>
+        <x:v>fetchUserInfoByIdWithType：按属性类型拉取指定用户（nick + sign）</x:v>
       </x:c>
       <x:c r="D797" s="18" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。</x:v>
       </x:c>
       <x:c r="E797" s="18" t="str">
-        <x:v>1. 设置用于查询的当前用户资料
-2. 查询当前用户资料并验证属性
+        <x:v>1. 按昵称和签名类型查询用户资料
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
       <x:c r="F797" s="24" t="str">
@@ -21311,13 +21291,13 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C798" s="18" t="str">
-        <x:v>fetchUserInfoById：获取指定用户（当前用户与另一用户）的属性</x:v>
+        <x:v>updateOwnUserInfo：昵称超过 2k长度，预期失败</x:v>
       </x:c>
       <x:c r="D798" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。</x:v>
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。</x:v>
       </x:c>
       <x:c r="E798" s="18" t="str">
-        <x:v>1. 查询两个用户的资料并验证用户标识
+        <x:v>1. 提交超长昵称并验证长度错误
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
       <x:c r="F798" s="24" t="str">
@@ -21335,13 +21315,13 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C799" s="18" t="str">
-        <x:v>fetchUserInfoById：userIds 超过 100 个，预期失败</x:v>
+        <x:v>updateOwnUserInfo：昵称为空</x:v>
       </x:c>
       <x:c r="D799" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。</x:v>
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。</x:v>
       </x:c>
       <x:c r="E799" s="18" t="str">
-        <x:v>1. 使用超过上限的用户列表查询资料并验证数量错误
+        <x:v>1. 提交空昵称并验证空值处理结果
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
       <x:c r="F799" s="24" t="str">
@@ -21359,140 +21339,44 @@
         <x:v>普通</x:v>
       </x:c>
       <x:c r="C800" s="18" t="str">
-        <x:v>fetchUserInfoById：userIds 为空列表</x:v>
+        <x:v>updateOwnUserInfo：先设置再修改当前用户属性</x:v>
       </x:c>
       <x:c r="D800" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。</x:v>
+        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。</x:v>
       </x:c>
       <x:c r="E800" s="18" t="str">
-        <x:v>1. 使用空用户列表查询资料并验证参数错误
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
-      <x:c r="F800" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G800" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="801" ht="120" customHeight="1">
-      <x:c r="A801" s="21" t="str">
-        <x:v>UserInfo</x:v>
-      </x:c>
-      <x:c r="B801" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C801" s="18" t="str">
-        <x:v>fetchUserInfoByIdWithType：按属性类型拉取指定用户（nick + sign）</x:v>
-      </x:c>
-      <x:c r="D801" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。</x:v>
-      </x:c>
-      <x:c r="E801" s="18" t="str">
-        <x:v>1. 按昵称和签名类型查询用户资料
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
-      <x:c r="F801" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G801" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="802" ht="120" customHeight="1">
-      <x:c r="A802" s="21" t="str">
-        <x:v>UserInfo</x:v>
-      </x:c>
-      <x:c r="B802" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C802" s="18" t="str">
-        <x:v>updateOwnUserInfo：昵称超过 2k长度，预期失败</x:v>
-      </x:c>
-      <x:c r="D802" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；接口响应与事件断言工具已初始化。</x:v>
-      </x:c>
-      <x:c r="E802" s="18" t="str">
-        <x:v>1. 提交超长昵称并验证长度错误
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
-      <x:c r="F802" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G802" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="803" ht="120" customHeight="1">
-      <x:c r="A803" s="21" t="str">
-        <x:v>UserInfo</x:v>
-      </x:c>
-      <x:c r="B803" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C803" s="18" t="str">
-        <x:v>updateOwnUserInfo：昵称为空</x:v>
-      </x:c>
-      <x:c r="D803" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。</x:v>
-      </x:c>
-      <x:c r="E803" s="18" t="str">
-        <x:v>1. 提交空昵称并验证空值处理结果
-验证操作结果、关键字段和相关事件符合预期。</x:v>
-      </x:c>
-      <x:c r="F803" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G803" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="804" ht="120" customHeight="1">
-      <x:c r="A804" s="21" t="str">
-        <x:v>UserInfo</x:v>
-      </x:c>
-      <x:c r="B804" s="21" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C804" s="18" t="str">
-        <x:v>updateOwnUserInfo：先设置再修改当前用户属性</x:v>
-      </x:c>
-      <x:c r="D804" s="18" t="str">
-        <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。</x:v>
-      </x:c>
-      <x:c r="E804" s="18" t="str">
         <x:v>1. 设置当前用户昵称、签名和性别并验证结果
 2. 修改当前用户昵称和签名并验证更新结果
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F804" s="24" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G804" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="805" ht="120" customHeight="1">
-      <x:c r="A805" s="22" t="str">
+      <x:c r="F800" s="24" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G800" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="801" ht="120" customHeight="1">
+      <x:c r="A801" s="22" t="str">
         <x:v>UserInfo</x:v>
       </x:c>
-      <x:c r="B805" s="22" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="C805" s="19" t="str">
+      <x:c r="B801" s="22" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="C801" s="19" t="str">
         <x:v>updateOwnUserInfoWithType：按类型更新昵称（0 = NICKNAME）</x:v>
       </x:c>
-      <x:c r="D805" s="19" t="str">
+      <x:c r="D801" s="19" t="str">
         <x:v>WebSocket 测试桥接和被测 Flutter App 已连接，pytest fixtures 可正常工作。；设备A已启动并登录，账号状态可用。；用例涉及的用户关系、会话或群组基础数据已准备。；接口响应与事件断言工具已初始化。</x:v>
       </x:c>
-      <x:c r="E805" s="19" t="str">
+      <x:c r="E801" s="19" t="str">
         <x:v>1. 按昵称类型更新当前用户昵称并验证结果
 验证操作结果、关键字段和相关事件符合预期。</x:v>
       </x:c>
-      <x:c r="F805" s="26" t="str">
-        <x:v>普通</x:v>
-      </x:c>
-      <x:c r="G805" t="str">
+      <x:c r="F801" s="26" t="str">
+        <x:v>普通</x:v>
+      </x:c>
+      <x:c r="G801" t="str">
         <x:v>普通</x:v>
       </x:c>
     </x:row>
@@ -21502,7 +21386,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2c43345caf84746"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf41f69b0d57e47a7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
